--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A607B79-8FC2-4359-ACDD-70FFC6886FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48D8B60-00C0-438B-9F65-2B3B68325284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="19" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="2406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="2413">
   <si>
     <t>FirstName</t>
   </si>
@@ -7300,6 +7300,27 @@
   </si>
   <si>
     <t>Fee Simple - MoTT;Closed Road</t>
+  </si>
+  <si>
+    <t>Compensation to test lease errors</t>
+  </si>
+  <si>
+    <t>Testing lease- compensation errors</t>
+  </si>
+  <si>
+    <t>Automation Functional Testing - Note Test Property 1;Automation Functional Testing - Note Test Property 2;Automation Functional Testing - Note Test Property 3</t>
+  </si>
+  <si>
+    <t>Property - Edit note</t>
+  </si>
+  <si>
+    <t>Property - Create new notes</t>
+  </si>
+  <si>
+    <t>Lease compensation errors</t>
+  </si>
+  <si>
+    <t>Lease minimum for Notes</t>
   </si>
 </sst>
 </file>
@@ -7396,7 +7417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7482,6 +7503,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10649,7 +10671,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45951</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10887,7 +10909,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45951</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11112,7 +11134,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45951</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11685,7 +11707,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45951</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12028,7 +12050,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45951</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -15098,7 +15120,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CC3795-F36B-4D0F-8244-A4F4C3935686}">
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.44140625" bestFit="1" customWidth="1"/>
@@ -15635,6 +15657,57 @@
       </c>
       <c r="V9">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B10" s="37"/>
+      <c r="E10" t="s">
+        <v>490</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1821</v>
+      </c>
+      <c r="G10" s="4">
+        <v>45569</v>
+      </c>
+      <c r="K10" t="s">
+        <v>2407</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1576</v>
+      </c>
+      <c r="M10" s="53" t="s">
+        <v>1872</v>
+      </c>
+      <c r="N10" s="53" t="s">
+        <v>895</v>
+      </c>
+      <c r="O10" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P10" s="53" t="s">
+        <v>1814</v>
+      </c>
+      <c r="Q10" s="53" t="s">
+        <v>796</v>
+      </c>
+      <c r="R10" s="53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="53" t="s">
+        <v>1395</v>
+      </c>
+      <c r="T10" s="53" t="s">
+        <v>1815</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -16762,7 +16835,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45951</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -25968,7 +26041,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E0191B-A695-44B6-B8DB-539DF91B46C4}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" bestFit="1" customWidth="1"/>
@@ -26076,6 +26149,22 @@
         <v>2276</v>
       </c>
       <c r="B13" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B15" t="s">
         <v>2277</v>
       </c>
     </row>
@@ -28081,7 +28170,7 @@
         <v>1</v>
       </c>
       <c r="AW8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8">
         <v>1</v>
@@ -29133,7 +29222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:104" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:105" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2194</v>
       </c>
@@ -29258,7 +29347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:104" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:105" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2194</v>
       </c>
@@ -29383,15 +29472,260 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:104" x14ac:dyDescent="0.3">
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-    </row>
-    <row r="20" spans="1:104" x14ac:dyDescent="0.3">
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-    </row>
-    <row r="21" spans="1:104" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:105" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E19" t="s">
+        <v>490</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2379</v>
+      </c>
+      <c r="J19" s="4">
+        <v>45209</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>191</v>
+      </c>
+      <c r="P19" t="s">
+        <v>1803</v>
+      </c>
+      <c r="R19" t="s">
+        <v>1804</v>
+      </c>
+      <c r="T19" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>297</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>1</v>
+      </c>
+      <c r="AV19">
+        <v>4</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>2</v>
+      </c>
+      <c r="BC19">
+        <v>2</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="CQ19">
+        <v>0</v>
+      </c>
+      <c r="CS19">
+        <v>0</v>
+      </c>
+      <c r="CT19">
+        <v>0</v>
+      </c>
+      <c r="CU19">
+        <v>0</v>
+      </c>
+      <c r="CV19">
+        <v>0</v>
+      </c>
+      <c r="CW19">
+        <v>0</v>
+      </c>
+      <c r="CX19">
+        <v>0</v>
+      </c>
+      <c r="CY19">
+        <v>9</v>
+      </c>
+      <c r="CZ19">
+        <v>1</v>
+      </c>
+      <c r="DA19">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:105" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E20" t="s">
+        <v>490</v>
+      </c>
+      <c r="I20" t="s">
+        <v>2379</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>191</v>
+      </c>
+      <c r="P20" t="s">
+        <v>1803</v>
+      </c>
+      <c r="R20" t="s">
+        <v>1804</v>
+      </c>
+      <c r="T20" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>297</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="CQ20">
+        <v>0</v>
+      </c>
+      <c r="CS20">
+        <v>0</v>
+      </c>
+      <c r="CT20">
+        <v>0</v>
+      </c>
+      <c r="CU20">
+        <v>0</v>
+      </c>
+      <c r="CV20">
+        <v>0</v>
+      </c>
+      <c r="CW20">
+        <v>0</v>
+      </c>
+      <c r="CX20">
+        <v>0</v>
+      </c>
+      <c r="CY20">
+        <v>0</v>
+      </c>
+      <c r="CZ20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:105" x14ac:dyDescent="0.3">
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
     </row>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48D8B60-00C0-438B-9F65-2B3B68325284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D0B457-EFAA-456B-BDC0-A4B48E9B7F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="25" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -62,6 +62,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">DocumentsDetails!$A$1:$BA$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="2413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="2420">
   <si>
     <t>FirstName</t>
   </si>
@@ -7321,6 +7322,27 @@
   </si>
   <si>
     <t>Lease minimum for Notes</t>
+  </si>
+  <si>
+    <t>Insert a document on a Property and verify on Management Files</t>
+  </si>
+  <si>
+    <t>Insert a document on a Management Activity and verify on Management Files</t>
+  </si>
+  <si>
+    <t>Insert a document on a Management file and verified on related documents</t>
+  </si>
+  <si>
+    <t>Property with Digital Documents</t>
+  </si>
+  <si>
+    <t>027-928-837</t>
+  </si>
+  <si>
+    <t>Minimum MF to verify related documents</t>
+  </si>
+  <si>
+    <t>Automated Management File - Minimum File to review related documents</t>
   </si>
 </sst>
 </file>
@@ -7417,7 +7439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7503,7 +7525,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10671,7 +10692,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10909,7 +10930,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11134,7 +11155,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11707,7 +11728,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12050,7 +12071,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -15679,28 +15700,28 @@
       <c r="L10" t="s">
         <v>1576</v>
       </c>
-      <c r="M10" s="53" t="s">
+      <c r="M10" t="s">
         <v>1872</v>
       </c>
-      <c r="N10" s="53" t="s">
+      <c r="N10" t="s">
         <v>895</v>
       </c>
-      <c r="O10" s="53" t="s">
+      <c r="O10" t="s">
         <v>1813</v>
       </c>
-      <c r="P10" s="53" t="s">
+      <c r="P10" t="s">
         <v>1814</v>
       </c>
-      <c r="Q10" s="53" t="s">
+      <c r="Q10" t="s">
         <v>796</v>
       </c>
-      <c r="R10" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" s="53" t="s">
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
         <v>1395</v>
       </c>
-      <c r="T10" s="53" t="s">
+      <c r="T10" t="s">
         <v>1815</v>
       </c>
       <c r="U10">
@@ -16835,7 +16856,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -18883,7 +18904,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E382B1-281B-4434-81AA-04C8D5F3D2FB}">
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.21875" customWidth="1"/>
@@ -19452,6 +19473,14 @@
       </c>
       <c r="B38" t="s">
         <v>2243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="52" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2417</v>
       </c>
     </row>
   </sheetData>
@@ -19975,16 +20004,16 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718AA1BD-8944-4A5E-BDA4-69421020A1DE}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="51.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="51.109375" bestFit="1" customWidth="1"/>
@@ -20243,7 +20272,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -20366,6 +20395,35 @@
       </c>
       <c r="O11">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B12" t="s">
+        <v>490</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2419</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>38</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24233,10 +24291,10 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED69AB3B-3A11-477C-A201-8388519D3807}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="69.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
@@ -24426,6 +24484,27 @@
       </c>
       <c r="C17">
         <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B18">
+        <v>71</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>2415</v>
       </c>
     </row>
   </sheetData>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D0B457-EFAA-456B-BDC0-A4B48E9B7F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5437F9C-3AEC-42B3-930D-791A7DAA0D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="25" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="950" firstSheet="27" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -62,7 +62,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">DocumentsDetails!$A$1:$BA$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -83,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="2420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4276" uniqueCount="2421">
   <si>
     <t>FirstName</t>
   </si>
@@ -7343,6 +7342,9 @@
   </si>
   <si>
     <t>Automated Management File - Minimum File to review related documents</t>
+  </si>
+  <si>
+    <t>ManagementTotalProperties</t>
   </si>
 </sst>
 </file>
@@ -10692,7 +10694,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10930,7 +10932,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11155,7 +11157,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11728,7 +11730,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12071,7 +12073,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -16856,7 +16858,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -20004,7 +20006,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718AA1BD-8944-4A5E-BDA4-69421020A1DE}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.6640625" bestFit="1" customWidth="1"/>
@@ -20020,11 +20022,12 @@
     <col min="11" max="11" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.21875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>104</v>
       </c>
@@ -20065,13 +20068,16 @@
         <v>2220</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>2420</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>2330</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>2331</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1059</v>
       </c>
@@ -20117,8 +20123,11 @@
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1060</v>
       </c>
@@ -20164,8 +20173,11 @@
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1066</v>
       </c>
@@ -20188,13 +20200,16 @@
         <v>34</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1067</v>
       </c>
@@ -20217,13 +20232,16 @@
         <v>35</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2353</v>
       </c>
@@ -20246,13 +20264,16 @@
         <v>36</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2250</v>
       </c>
@@ -20275,13 +20296,16 @@
         <v>38</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2251</v>
       </c>
@@ -20309,8 +20333,11 @@
       <c r="O8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2332</v>
       </c>
@@ -20336,10 +20363,13 @@
         <v>5</v>
       </c>
       <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2333</v>
       </c>
@@ -20362,13 +20392,16 @@
         <v>35</v>
       </c>
       <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
         <v>8</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2354</v>
       </c>
@@ -20391,13 +20424,16 @@
         <v>35</v>
       </c>
       <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
         <v>8</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2418</v>
       </c>
@@ -20420,9 +20456,12 @@
         <v>38</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
         <v>0</v>
       </c>
     </row>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE6A178-DB61-401A-8BDA-CC7EF9F55680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92EF4A5-EE44-4736-BCB6-814720F85087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="25" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="29" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -7251,9 +7251,6 @@
     <t>Testing lease- compensation errors</t>
   </si>
   <si>
-    <t>Automation Functional Testing - Note Test Property 1;Automation Functional Testing - Note Test Property 2;Automation Functional Testing - Note Test Property 3</t>
-  </si>
-  <si>
     <t>Property - Edit note</t>
   </si>
   <si>
@@ -7378,6 +7375,9 @@
   </si>
   <si>
     <t>Access;Development</t>
+  </si>
+  <si>
+    <t>Automation Functional Testing - Note Test Property 1;Automation Functional Testing - Note Test Property 2;Automation Functional Testing - Note Test Property 3;Automation Functional Testing - Note Test Property 4</t>
   </si>
 </sst>
 </file>
@@ -7474,7 +7474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7560,12 +7560,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10733,7 +10727,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10971,7 +10965,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11196,7 +11190,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11769,7 +11763,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12112,7 +12106,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -16897,7 +16891,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -19038,7 +19032,7 @@
         <v>2366</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -19076,7 +19070,7 @@
         <v>2294</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -19222,7 +19216,7 @@
         <v>2381</v>
       </c>
       <c r="U12" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -19272,7 +19266,7 @@
         <v>2367</v>
       </c>
       <c r="U16" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
@@ -19376,7 +19370,7 @@
         <v>2377</v>
       </c>
       <c r="U26" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
@@ -19539,7 +19533,7 @@
         <v>2379</v>
       </c>
       <c r="U37" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -19552,10 +19546,10 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B39" t="s">
         <v>2397</v>
-      </c>
-      <c r="B39" t="s">
-        <v>2398</v>
       </c>
     </row>
   </sheetData>
@@ -20141,7 +20135,7 @@
         <v>2204</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>2311</v>
@@ -20508,13 +20502,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="B12" t="s">
         <v>490</v>
       </c>
       <c r="G12" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="I12" t="s">
         <v>1787</v>
@@ -20888,7 +20882,7 @@
         <v>1189</v>
       </c>
       <c r="D2" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="E2" t="s">
         <v>1213</v>
@@ -20903,7 +20897,7 @@
         <v>2158</v>
       </c>
       <c r="J2" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="K2" t="s">
         <v>1195</v>
@@ -20941,7 +20935,7 @@
         <v>1190</v>
       </c>
       <c r="D3" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="E3" t="s">
         <v>1191</v>
@@ -20956,7 +20950,7 @@
         <v>1194</v>
       </c>
       <c r="J3" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="K3" t="s">
         <v>2157</v>
@@ -21009,7 +21003,7 @@
         <v>1223</v>
       </c>
       <c r="J4" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="K4" t="s">
         <v>1225</v>
@@ -21047,7 +21041,7 @@
         <v>1278</v>
       </c>
       <c r="D5" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="E5" t="s">
         <v>1213</v>
@@ -21062,7 +21056,7 @@
         <v>2225</v>
       </c>
       <c r="J5" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -21109,7 +21103,7 @@
         <v>2341</v>
       </c>
       <c r="J6" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="K6" t="s">
         <v>2342</v>
@@ -21165,7 +21159,7 @@
         <v>2308</v>
       </c>
       <c r="J7" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="K7" t="s">
         <v>2317</v>
@@ -21218,7 +21212,7 @@
         <v>2309</v>
       </c>
       <c r="J8" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="K8" t="s">
         <v>2318</v>
@@ -24603,7 +24597,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="B18">
         <v>71</v>
@@ -24614,12 +24608,12 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
     </row>
   </sheetData>
@@ -26348,15 +26342,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="B14" t="s">
-        <v>2389</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="B15" t="s">
         <v>2261</v>
@@ -27601,161 +27595,161 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:97" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:97" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>1471</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" t="s">
         <v>495</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="4">
         <v>45495</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" t="s">
         <v>1558</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" t="s">
         <v>2360</v>
       </c>
-      <c r="J3" s="56">
+      <c r="J3" s="4">
         <v>44614</v>
       </c>
-      <c r="K3" s="56">
+      <c r="K3" s="4">
         <v>45373</v>
       </c>
-      <c r="L3" s="54">
+      <c r="L3" s="8">
         <v>4</v>
       </c>
-      <c r="M3" s="54">
+      <c r="M3" s="8">
         <v>1</v>
       </c>
-      <c r="P3" s="53" t="s">
+      <c r="P3" t="s">
         <v>658</v>
       </c>
-      <c r="T3" s="53" t="s">
+      <c r="T3" t="s">
         <v>1758</v>
       </c>
-      <c r="Y3" s="53" t="s">
+      <c r="Y3" t="s">
         <v>578</v>
       </c>
-      <c r="Z3" s="53" t="s">
+      <c r="Z3" t="s">
         <v>1658</v>
       </c>
-      <c r="AA3" s="53" t="s">
+      <c r="AA3" t="s">
         <v>266</v>
       </c>
-      <c r="AB3" s="53" t="s">
+      <c r="AB3" t="s">
         <v>264</v>
       </c>
-      <c r="AC3" s="53" t="s">
+      <c r="AC3" t="s">
         <v>1675</v>
       </c>
-      <c r="AD3" s="53" t="s">
+      <c r="AD3" t="s">
         <v>1674</v>
       </c>
-      <c r="AE3" s="53">
+      <c r="AE3">
         <v>24</v>
       </c>
-      <c r="AF3" s="53">
+      <c r="AF3">
         <v>1</v>
       </c>
-      <c r="AG3" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="53">
+      <c r="AG3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
         <v>9</v>
       </c>
-      <c r="AK3" s="53">
+      <c r="AK3">
         <v>1</v>
       </c>
-      <c r="AL3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="53">
-        <v>0</v>
-      </c>
-      <c r="BB3" s="53" t="s">
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="s">
         <v>579</v>
       </c>
-      <c r="BC3" s="53" t="s">
+      <c r="BC3" t="s">
         <v>580</v>
       </c>
-      <c r="BD3" s="53" t="s">
+      <c r="BD3" t="s">
         <v>581</v>
       </c>
-      <c r="BE3" s="53">
+      <c r="BE3">
         <v>3</v>
       </c>
-      <c r="BZ3" s="53" t="s">
+      <c r="BZ3" t="s">
         <v>266</v>
       </c>
-      <c r="CA3" s="53">
-        <v>0</v>
-      </c>
-      <c r="CB3" s="56">
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" s="4">
         <v>44897</v>
       </c>
-      <c r="CC3" s="53" t="s">
+      <c r="CC3" t="s">
         <v>582</v>
       </c>
-      <c r="CI3" s="53">
+      <c r="CI3">
         <v>6</v>
       </c>
-      <c r="CJ3" s="53" t="s">
+      <c r="CJ3" t="s">
         <v>583</v>
       </c>
-      <c r="CK3" s="53">
+      <c r="CK3">
         <v>3</v>
       </c>
-      <c r="CL3" s="53">
+      <c r="CL3">
         <v>1</v>
       </c>
-      <c r="CM3" s="53">
+      <c r="CM3">
         <v>5</v>
       </c>
-      <c r="CN3" s="53">
+      <c r="CN3">
         <v>1</v>
       </c>
-      <c r="CO3" s="53">
+      <c r="CO3">
         <v>6</v>
       </c>
-      <c r="CP3" s="53">
+      <c r="CP3">
         <v>1</v>
       </c>
-      <c r="CQ3" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR3" s="53">
+      <c r="CQ3">
+        <v>0</v>
+      </c>
+      <c r="CR3">
         <v>0</v>
       </c>
     </row>
@@ -27982,131 +27976,131 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:97" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
-        <v>2420</v>
-      </c>
-      <c r="E6" s="53" t="s">
+    <row r="6" spans="1:97" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2419</v>
+      </c>
+      <c r="E6" t="s">
         <v>490</v>
       </c>
-      <c r="I6" s="53" t="s">
+      <c r="I6" t="s">
         <v>2360</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="4">
         <v>45064</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="4">
         <v>45373</v>
       </c>
-      <c r="L6" s="54">
-        <v>0</v>
-      </c>
-      <c r="M6" s="54">
-        <v>0</v>
-      </c>
-      <c r="O6" s="53" t="s">
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
         <v>190</v>
       </c>
-      <c r="P6" s="53" t="s">
+      <c r="P6" t="s">
         <v>2382</v>
       </c>
-      <c r="R6" s="53" t="s">
+      <c r="R6" t="s">
         <v>1715</v>
       </c>
-      <c r="T6" s="53" t="s">
+      <c r="T6" t="s">
         <v>659</v>
       </c>
-      <c r="AE6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="53">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>1</v>
       </c>
-      <c r="AN6" s="53">
+      <c r="AN6">
         <v>4</v>
       </c>
-      <c r="AO6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="53">
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
         <v>2</v>
       </c>
-      <c r="AU6" s="53">
+      <c r="AU6">
         <v>2</v>
       </c>
-      <c r="BE6" s="53">
-        <v>0</v>
-      </c>
-      <c r="BF6" s="53" t="s">
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="s">
         <v>266</v>
       </c>
-      <c r="BG6" s="53">
+      <c r="BG6">
         <v>5000</v>
       </c>
-      <c r="BH6" s="56">
+      <c r="BH6" s="4">
         <v>44114</v>
       </c>
-      <c r="BI6" s="53" t="s">
+      <c r="BI6" t="s">
         <v>1964</v>
       </c>
-      <c r="CI6" s="53">
+      <c r="CI6">
         <v>1</v>
       </c>
-      <c r="CK6" s="53">
+      <c r="CK6">
         <v>1</v>
       </c>
-      <c r="CL6" s="53">
+      <c r="CL6">
         <v>1</v>
       </c>
-      <c r="CM6" s="53">
+      <c r="CM6">
         <v>1</v>
       </c>
-      <c r="CN6" s="53">
+      <c r="CN6">
         <v>1</v>
       </c>
-      <c r="CO6" s="53">
+      <c r="CO6">
         <v>1</v>
       </c>
-      <c r="CP6" s="53">
+      <c r="CP6">
         <v>1</v>
       </c>
-      <c r="CQ6" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR6" s="53">
+      <c r="CQ6">
+        <v>0</v>
+      </c>
+      <c r="CR6">
         <v>0</v>
       </c>
     </row>
@@ -29600,7 +29594,7 @@
     </row>
     <row r="19" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="B19" t="s">
         <v>1008</v>
@@ -29734,7 +29728,7 @@
     </row>
     <row r="20" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="E20" t="s">
         <v>490</v>
@@ -29853,7 +29847,7 @@
     </row>
     <row r="21" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="E21" t="s">
         <v>246</v>
@@ -29986,7 +29980,7 @@
     </row>
     <row r="22" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="E22" t="s">
         <v>246</v>
@@ -30097,7 +30091,7 @@
     </row>
     <row r="23" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="E23" t="s">
         <v>246</v>
@@ -30230,7 +30224,7 @@
     </row>
     <row r="24" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E24" t="s">
         <v>246</v>
@@ -30390,7 +30384,7 @@
     </row>
     <row r="25" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="E25" t="s">
         <v>246</v>
@@ -30515,7 +30509,7 @@
     </row>
     <row r="26" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="E26" t="s">
         <v>246</v>
@@ -30728,7 +30722,7 @@
     </row>
     <row r="27" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="E27" t="s">
         <v>246</v>
@@ -30852,7 +30846,7 @@
     </row>
     <row r="28" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="E28" t="s">
         <v>246</v>
@@ -30988,7 +30982,7 @@
     </row>
     <row r="29" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="F29" s="4"/>
       <c r="J29" s="4"/>
@@ -31101,7 +31095,7 @@
     </row>
     <row r="30" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="E30" t="s">
         <v>246</v>
@@ -31234,7 +31228,7 @@
     </row>
     <row r="31" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="F31" s="4"/>
       <c r="J31" s="4"/>
@@ -31342,230 +31336,230 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:97" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="53" t="s">
-        <v>2419</v>
-      </c>
-      <c r="L32" s="54">
-        <v>0</v>
-      </c>
-      <c r="M32" s="54">
-        <v>0</v>
-      </c>
-      <c r="P32" s="53" t="s">
+    <row r="32" spans="1:97" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2418</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0</v>
+      </c>
+      <c r="M32" s="8">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
         <v>658</v>
       </c>
-      <c r="AA32" s="53" t="s">
+      <c r="AA32" t="s">
         <v>297</v>
       </c>
-      <c r="AB32" s="53" t="s">
+      <c r="AB32" t="s">
         <v>297</v>
       </c>
-      <c r="AC32" s="53" t="s">
+      <c r="AC32" t="s">
         <v>297</v>
       </c>
-      <c r="AE32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="53">
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
         <v>5</v>
       </c>
-      <c r="AN32" s="53">
+      <c r="AN32">
         <v>1</v>
       </c>
-      <c r="AO32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT32" s="53">
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
         <v>3</v>
       </c>
-      <c r="AU32" s="53">
-        <v>0</v>
-      </c>
-      <c r="BE32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CI32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CK32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CL32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CM32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CN32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CO32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CP32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CQ32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR32" s="53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:96" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="53" t="s">
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="CI32">
+        <v>0</v>
+      </c>
+      <c r="CK32">
+        <v>0</v>
+      </c>
+      <c r="CL32">
+        <v>0</v>
+      </c>
+      <c r="CM32">
+        <v>0</v>
+      </c>
+      <c r="CN32">
+        <v>0</v>
+      </c>
+      <c r="CO32">
+        <v>0</v>
+      </c>
+      <c r="CP32">
+        <v>0</v>
+      </c>
+      <c r="CQ32">
+        <v>0</v>
+      </c>
+      <c r="CR32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>584</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" t="s">
         <v>490</v>
       </c>
-      <c r="I33" s="53" t="s">
+      <c r="I33" t="s">
         <v>2360</v>
       </c>
-      <c r="J33" s="56">
+      <c r="J33" s="4">
         <v>45064</v>
       </c>
-      <c r="K33" s="56">
+      <c r="K33" s="4">
         <v>45373</v>
       </c>
-      <c r="L33" s="54">
-        <v>0</v>
-      </c>
-      <c r="M33" s="54">
-        <v>0</v>
-      </c>
-      <c r="O33" s="53" t="s">
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
         <v>190</v>
       </c>
-      <c r="P33" s="53" t="s">
+      <c r="P33" t="s">
         <v>2382</v>
       </c>
-      <c r="R33" s="53" t="s">
+      <c r="R33" t="s">
         <v>1715</v>
       </c>
-      <c r="T33" s="53" t="s">
+      <c r="T33" t="s">
         <v>659</v>
       </c>
-      <c r="AE33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU33" s="53">
-        <v>0</v>
-      </c>
-      <c r="BE33" s="53">
-        <v>0</v>
-      </c>
-      <c r="BH33" s="56"/>
-      <c r="CI33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CK33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CL33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CM33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CN33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CO33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CP33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CQ33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR33" s="53">
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BH33" s="4"/>
+      <c r="CI33">
+        <v>0</v>
+      </c>
+      <c r="CK33">
+        <v>0</v>
+      </c>
+      <c r="CL33">
+        <v>0</v>
+      </c>
+      <c r="CM33">
+        <v>0</v>
+      </c>
+      <c r="CN33">
+        <v>0</v>
+      </c>
+      <c r="CO33">
+        <v>0</v>
+      </c>
+      <c r="CP33">
+        <v>0</v>
+      </c>
+      <c r="CQ33">
+        <v>0</v>
+      </c>
+      <c r="CR33">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A34" s="53" t="s">
-        <v>2421</v>
+      <c r="A34" t="s">
+        <v>2420</v>
       </c>
       <c r="E34" t="s">
         <v>490</v>
@@ -31573,22 +31567,22 @@
       <c r="I34" t="s">
         <v>2360</v>
       </c>
-      <c r="J34" s="56">
+      <c r="J34" s="4">
         <v>45064</v>
       </c>
-      <c r="K34" s="56">
+      <c r="K34" s="4">
         <v>45373</v>
       </c>
-      <c r="L34" s="54">
-        <v>0</v>
-      </c>
-      <c r="M34" s="54">
+      <c r="L34" s="8">
+        <v>0</v>
+      </c>
+      <c r="M34" s="8">
         <v>0</v>
       </c>
       <c r="O34" t="s">
         <v>192</v>
       </c>
-      <c r="P34" s="53" t="s">
+      <c r="P34" t="s">
         <v>1771</v>
       </c>
       <c r="R34" t="s">
@@ -31597,85 +31591,85 @@
       <c r="T34" t="s">
         <v>1758</v>
       </c>
-      <c r="AE34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="55">
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="2">
         <v>13</v>
       </c>
-      <c r="AH34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="53">
-        <v>0</v>
-      </c>
-      <c r="BE34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CI34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CK34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CL34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CM34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CN34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CO34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CP34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CQ34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR34" s="53">
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="CI34">
+        <v>0</v>
+      </c>
+      <c r="CK34">
+        <v>0</v>
+      </c>
+      <c r="CL34">
+        <v>0</v>
+      </c>
+      <c r="CM34">
+        <v>0</v>
+      </c>
+      <c r="CN34">
+        <v>0</v>
+      </c>
+      <c r="CO34">
+        <v>0</v>
+      </c>
+      <c r="CP34">
+        <v>0</v>
+      </c>
+      <c r="CQ34">
+        <v>0</v>
+      </c>
+      <c r="CR34">
         <v>0</v>
       </c>
     </row>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE6A178-DB61-401A-8BDA-CC7EF9F55680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE83F7F-CA8C-41F0-ABE1-C32A636E8FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="25" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4407" uniqueCount="2432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="2433">
   <si>
     <t>FirstName</t>
   </si>
@@ -7011,9 +7011,6 @@
     <t>Zabihollah BEHIN</t>
   </si>
   <si>
-    <t>Yung Cho</t>
-  </si>
-  <si>
     <t>PropertyActivityRequestorContactMngr</t>
   </si>
   <si>
@@ -7035,12 +7032,6 @@
     <t>PropertyActivityInvolvedPartiesExtContacts</t>
   </si>
   <si>
-    <t>ALBERT RICHMOND;Alfred Pancake;Andrea Krenn</t>
-  </si>
-  <si>
-    <t>April Funk</t>
-  </si>
-  <si>
     <t>Yoshiko Ito</t>
   </si>
   <si>
@@ -7368,9 +7359,6 @@
     <t>David H Demitor</t>
   </si>
   <si>
-    <t>Chien Yu Hsin</t>
-  </si>
-  <si>
     <t>Accommodation Agreement;Consultation Record</t>
   </si>
   <si>
@@ -7378,6 +7366,21 @@
   </si>
   <si>
     <t>Access;Development</t>
+  </si>
+  <si>
+    <t>002-256-525;90172682;015-768-082</t>
+  </si>
+  <si>
+    <t>ALBERT SYLVESTER RICHMOND;Alfred Garnette Pancake;Andrea Krenn</t>
+  </si>
+  <si>
+    <t>Chow Yung-Heng Henry</t>
+  </si>
+  <si>
+    <t>Chien Hsin Yue</t>
+  </si>
+  <si>
+    <t>April Holly Funk</t>
   </si>
 </sst>
 </file>
@@ -7474,7 +7477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7560,12 +7563,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7852,17 +7849,17 @@
   <cols>
     <col min="1" max="1" width="52.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="58.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="11.5546875" style="5" customWidth="1"/>
     <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="72.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="72.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -8249,17 +8246,17 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.5546875" customWidth="1"/>
-    <col min="2" max="7" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="32" bestFit="1" customWidth="1"/>
     <col min="18" max="23" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -8559,10 +8556,10 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8798,19 +8795,19 @@
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -9020,27 +9017,27 @@
   <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.77734375" customWidth="1"/>
-    <col min="12" max="12" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="33" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -9422,15 +9419,15 @@
   <cols>
     <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -9689,24 +9686,24 @@
   <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="59.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="60.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="63.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="63.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -10119,8 +10116,8 @@
     <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="63.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="63.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -10347,47 +10344,47 @@
   <dimension ref="A1:AY25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="57.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="41.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="41" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="24.44140625" customWidth="1"/>
-    <col min="18" max="18" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="21" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="46" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="45.5546875" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="37" bestFit="1" customWidth="1"/>
@@ -10396,7 +10393,7 @@
     <col min="48" max="48" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" s="38" customFormat="1" x14ac:dyDescent="0.3">
@@ -10733,7 +10730,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10971,7 +10968,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11196,7 +11193,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11769,7 +11766,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12112,7 +12109,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -13167,22 +13164,22 @@
   <cols>
     <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -13555,15 +13552,15 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="23" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="35" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="36" max="44" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="46" max="47" width="26.5546875" customWidth="1"/>
-    <col min="48" max="48" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -14016,15 +14013,15 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -14513,18 +14510,18 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14834,12 +14831,12 @@
   <cols>
     <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -15186,27 +15183,27 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" customWidth="1"/>
     <col min="7" max="7" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="37.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="61.77734375" customWidth="1"/>
-    <col min="12" max="12" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="61.6640625" customWidth="1"/>
+    <col min="12" max="12" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="50.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="39.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="122.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="83.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="83.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="42.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -15324,7 +15321,7 @@
         <v>886</v>
       </c>
       <c r="P2" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="Q2" t="s">
         <v>2137</v>
@@ -15365,7 +15362,7 @@
         <v>1002</v>
       </c>
       <c r="P3" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
       <c r="Q3" t="s">
         <v>2138</v>
@@ -15427,7 +15424,7 @@
         <v>886</v>
       </c>
       <c r="P4" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
       <c r="Q4" t="s">
         <v>2135</v>
@@ -15589,7 +15586,7 @@
         <v>886</v>
       </c>
       <c r="P7" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
       <c r="Q7" t="s">
         <v>2139</v>
@@ -15723,7 +15720,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2387</v>
+        <v>2384</v>
       </c>
       <c r="B10" s="37"/>
       <c r="E10" t="s">
@@ -15736,7 +15733,7 @@
         <v>45569</v>
       </c>
       <c r="K10" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="L10" t="s">
         <v>1560</v>
@@ -15783,12 +15780,12 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -16052,11 +16049,11 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -16169,13 +16166,13 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.77734375" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" customWidth="1"/>
     <col min="4" max="4" width="57.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -16328,11 +16325,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -16487,53 +16484,53 @@
   <dimension ref="A1:AX16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
     <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="57.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.21875" customWidth="1"/>
+    <col min="8" max="8" width="57.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.33203125" customWidth="1"/>
     <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.21875" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" customWidth="1"/>
     <col min="14" max="14" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.44140625" customWidth="1"/>
-    <col min="16" max="16" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.21875" customWidth="1"/>
-    <col min="18" max="18" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" customWidth="1"/>
+    <col min="18" max="18" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="30.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="40.44140625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="32.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="20.5546875" customWidth="1"/>
-    <col min="37" max="37" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="12" customWidth="1"/>
     <col min="45" max="45" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -16897,7 +16894,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -17723,7 +17720,7 @@
     </row>
     <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="B16" t="s">
         <v>791</v>
@@ -17732,7 +17729,7 @@
         <v>45744</v>
       </c>
       <c r="H16" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="J16" t="s">
         <v>1355</v>
@@ -17849,12 +17846,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="16" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="25" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="34" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="34" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.3">
@@ -18246,13 +18243,13 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -18368,12 +18365,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="78.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -18443,7 +18440,7 @@
   <cols>
     <col min="1" max="1" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18550,7 +18547,7 @@
     <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18576,7 +18573,7 @@
         <v>675</v>
       </c>
       <c r="B2" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="C2" t="s">
         <v>250</v>
@@ -18666,7 +18663,7 @@
         <v>891</v>
       </c>
       <c r="B8" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="C8" t="s">
         <v>892</v>
@@ -18697,7 +18694,7 @@
         <v>1088</v>
       </c>
       <c r="B10" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>1089</v>
@@ -18711,7 +18708,7 @@
         <v>1237</v>
       </c>
       <c r="B11" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="C11" t="s">
         <v>2135</v>
@@ -18739,7 +18736,7 @@
         <v>1340</v>
       </c>
       <c r="B13" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="C13" t="s">
         <v>1341</v>
@@ -18753,7 +18750,7 @@
         <v>1340</v>
       </c>
       <c r="B14" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="C14" t="s">
         <v>1342</v>
@@ -18948,32 +18945,30 @@
   <dimension ref="A1:U39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.21875" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" customWidth="1"/>
     <col min="7" max="7" width="30.109375" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="23.44140625" customWidth="1"/>
-    <col min="22" max="22" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -18993,13 +18988,13 @@
         <v>239</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1500</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2285</v>
@@ -19026,19 +19021,19 @@
         <v>2292</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>2360</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>2361</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>2362</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>2363</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>2364</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>2365</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>2366</v>
-      </c>
       <c r="U1" s="3" t="s">
-        <v>2402</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -19049,7 +19044,7 @@
         <v>4361431</v>
       </c>
       <c r="D2" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="I2">
         <v>48</v>
@@ -19076,7 +19071,7 @@
         <v>2294</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>2403</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -19084,7 +19079,7 @@
         <v>327</v>
       </c>
       <c r="H3" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -19092,7 +19087,7 @@
         <v>280</v>
       </c>
       <c r="D4" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
@@ -19100,7 +19095,7 @@
         <v>278</v>
       </c>
       <c r="B5" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -19149,7 +19144,7 @@
         <v>1821391</v>
       </c>
       <c r="D10" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="E10" t="s">
         <v>1338</v>
@@ -19192,7 +19187,7 @@
         <v>1317</v>
       </c>
       <c r="G12" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
       <c r="I12">
         <v>49</v>
@@ -19219,10 +19214,10 @@
         <v>2294</v>
       </c>
       <c r="Q12" t="s">
-        <v>2381</v>
+        <v>2378</v>
       </c>
       <c r="U12" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -19260,19 +19255,19 @@
         <v>1821391</v>
       </c>
       <c r="D16" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
       <c r="E16" t="s">
         <v>1747</v>
       </c>
       <c r="H16" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="Q16" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
       <c r="U16" t="s">
-        <v>2404</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
@@ -19370,13 +19365,13 @@
         <v>1760</v>
       </c>
       <c r="F26" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="H26" t="s">
-        <v>2377</v>
+        <v>2374</v>
       </c>
       <c r="U26" t="s">
-        <v>2405</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
@@ -19413,7 +19408,7 @@
         <v>1336</v>
       </c>
       <c r="H28" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
@@ -19421,7 +19416,7 @@
         <v>1337</v>
       </c>
       <c r="F29" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
@@ -19456,7 +19451,7 @@
       </c>
       <c r="B32" s="14"/>
       <c r="E32" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -19467,7 +19462,7 @@
         <v>2174</v>
       </c>
       <c r="F33" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="U33" s="14" t="s">
         <v>2174</v>
@@ -19521,6 +19516,9 @@
       <c r="P35" t="s">
         <v>2294</v>
       </c>
+      <c r="U35" t="s">
+        <v>2428</v>
+      </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="52" t="s">
@@ -19529,22 +19527,25 @@
       <c r="B36" t="s">
         <v>2229</v>
       </c>
+      <c r="U36" t="s">
+        <v>2229</v>
+      </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="52" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="B37" s="14"/>
       <c r="E37" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="U37" t="s">
-        <v>2406</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="B38" t="s">
         <v>2227</v>
@@ -19552,10 +19553,10 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
       <c r="B39" t="s">
-        <v>2398</v>
+        <v>2395</v>
       </c>
     </row>
   </sheetData>
@@ -19570,50 +19571,50 @@
   <dimension ref="A1:AD6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="38.5546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="27.44140625" customWidth="1"/>
     <col min="26" max="26" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="63.5546875" bestFit="1" customWidth="1"/>
     <col min="31" max="33" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="43" max="46" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="46" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -19852,7 +19853,7 @@
         <v>1271</v>
       </c>
       <c r="W4" t="s">
-        <v>2386</v>
+        <v>2383</v>
       </c>
       <c r="X4" t="s">
         <v>721</v>
@@ -20016,9 +20017,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -20083,20 +20084,20 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="66.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="51.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20141,13 +20142,13 @@
         <v>2204</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>2310</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>2311</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>2312</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -20273,7 +20274,7 @@
         <v>34</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -20316,7 +20317,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="B6" t="s">
         <v>490</v>
@@ -20398,7 +20399,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -20412,13 +20413,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="B9" t="s">
         <v>490</v>
       </c>
       <c r="G9" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="I9" t="s">
         <v>2221</v>
@@ -20433,7 +20434,7 @@
         <v>34</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -20444,13 +20445,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="B10" t="s">
         <v>490</v>
       </c>
       <c r="G10" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="I10" t="s">
         <v>2238</v>
@@ -20468,7 +20469,7 @@
         <v>1</v>
       </c>
       <c r="O10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -20476,13 +20477,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="B11" t="s">
         <v>490</v>
       </c>
       <c r="G11" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="I11" t="s">
         <v>2239</v>
@@ -20500,7 +20501,7 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -20508,13 +20509,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2399</v>
+        <v>2396</v>
       </c>
       <c r="B12" t="s">
         <v>490</v>
       </c>
       <c r="G12" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
       <c r="I12" t="s">
         <v>1787</v>
@@ -20550,13 +20551,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="68.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20699,8 +20700,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="24.6640625" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20801,23 +20802,23 @@
   <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="34.5546875" customWidth="1"/>
-    <col min="11" max="11" width="43.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="36.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20826,7 +20827,7 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1166</v>
@@ -20838,7 +20839,7 @@
         <v>1168</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1169</v>
@@ -20850,10 +20851,10 @@
         <v>1171</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1172</v>
@@ -20888,7 +20889,7 @@
         <v>1189</v>
       </c>
       <c r="D2" t="s">
-        <v>2429</v>
+        <v>2425</v>
       </c>
       <c r="E2" t="s">
         <v>1213</v>
@@ -20903,7 +20904,7 @@
         <v>2158</v>
       </c>
       <c r="J2" t="s">
-        <v>2422</v>
+        <v>2419</v>
       </c>
       <c r="K2" t="s">
         <v>1195</v>
@@ -20941,7 +20942,7 @@
         <v>1190</v>
       </c>
       <c r="D3" t="s">
-        <v>2430</v>
+        <v>2426</v>
       </c>
       <c r="E3" t="s">
         <v>1191</v>
@@ -20956,7 +20957,7 @@
         <v>1194</v>
       </c>
       <c r="J3" t="s">
-        <v>2423</v>
+        <v>2420</v>
       </c>
       <c r="K3" t="s">
         <v>2157</v>
@@ -21009,7 +21010,7 @@
         <v>1223</v>
       </c>
       <c r="J4" t="s">
-        <v>2424</v>
+        <v>2421</v>
       </c>
       <c r="K4" t="s">
         <v>1225</v>
@@ -21047,7 +21048,7 @@
         <v>1278</v>
       </c>
       <c r="D5" t="s">
-        <v>2431</v>
+        <v>2427</v>
       </c>
       <c r="E5" t="s">
         <v>1213</v>
@@ -21062,7 +21063,7 @@
         <v>2225</v>
       </c>
       <c r="J5" t="s">
-        <v>2425</v>
+        <v>2422</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -21088,7 +21089,7 @@
         <v>2297</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>2299</v>
@@ -21106,16 +21107,16 @@
         <v>2305</v>
       </c>
       <c r="I6" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="J6" t="s">
-        <v>2426</v>
+        <v>2423</v>
       </c>
       <c r="K6" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="L6" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -21141,7 +21142,7 @@
         <v>2297</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
         <v>2300</v>
@@ -21156,7 +21157,7 @@
         <v>45630</v>
       </c>
       <c r="G7" s="4">
-        <v>45395</v>
+        <v>45760</v>
       </c>
       <c r="H7" t="s">
         <v>2306</v>
@@ -21165,13 +21166,13 @@
         <v>2308</v>
       </c>
       <c r="J7" t="s">
-        <v>2427</v>
+        <v>2424</v>
       </c>
       <c r="K7" t="s">
-        <v>2317</v>
+        <v>2429</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -21215,16 +21216,16 @@
         <v>2307</v>
       </c>
       <c r="I8" t="s">
-        <v>2309</v>
+        <v>2430</v>
       </c>
       <c r="J8" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="K8" t="s">
-        <v>2318</v>
+        <v>2432</v>
       </c>
       <c r="L8" t="s">
-        <v>2320</v>
+        <v>2317</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -21260,11 +21261,11 @@
     <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="31.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -21356,16 +21357,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="B4" t="s">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="C4" s="4">
         <v>45300</v>
       </c>
       <c r="D4" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="E4" s="11">
         <v>9500.9699999999993</v>
@@ -21385,16 +21386,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="B5" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="C5" s="4">
         <v>45544</v>
       </c>
       <c r="D5" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
       <c r="E5" s="11">
         <v>155.84</v>
@@ -21414,16 +21415,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B6" t="s">
         <v>2321</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2324</v>
       </c>
       <c r="C6" s="4">
         <v>45576</v>
       </c>
       <c r="D6" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="E6" s="11">
         <v>15077554.890000001</v>
@@ -21443,7 +21444,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="B7" t="s">
         <v>1379</v>
@@ -21452,7 +21453,7 @@
         <v>45659</v>
       </c>
       <c r="D7" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="E7" s="11">
         <v>1780</v>
@@ -21472,16 +21473,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="B8" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
       <c r="C8" s="4">
         <v>45607</v>
       </c>
       <c r="D8" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="E8" s="11">
         <v>50</v>
@@ -21501,16 +21502,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="B9" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="C9" s="4">
         <v>45638</v>
       </c>
       <c r="D9" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="E9" s="11">
         <v>127.9</v>
@@ -21539,17 +21540,17 @@
   <dimension ref="A1:AW9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5546875" customWidth="1"/>
-    <col min="11" max="11" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="28.44140625" customWidth="1"/>
     <col min="15" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
@@ -21557,31 +21558,31 @@
     <col min="17" max="17" width="21.44140625" customWidth="1"/>
     <col min="18" max="18" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="18" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="23" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="21" bestFit="1" customWidth="1"/>
-    <col min="40" max="42" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="42" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="21" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="66.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22293,26 +22294,26 @@
     <col min="1" max="1" width="20.5546875" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.5546875" customWidth="1"/>
     <col min="10" max="10" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.44140625" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="18" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -23870,11 +23871,11 @@
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="64.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24410,8 +24411,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="69.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -24592,7 +24593,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="B17">
         <v>71</v>
@@ -24603,7 +24604,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2394</v>
+        <v>2391</v>
       </c>
       <c r="B18">
         <v>71</v>
@@ -24614,12 +24615,12 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2395</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2396</v>
+        <v>2393</v>
       </c>
     </row>
   </sheetData>
@@ -24633,38 +24634,38 @@
   <dimension ref="A1:BA74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="103.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="103.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="83" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="19.21875" customWidth="1"/>
-    <col min="8" max="9" width="19.21875" style="13" customWidth="1"/>
-    <col min="10" max="11" width="19.21875" customWidth="1"/>
-    <col min="12" max="12" width="19.21875" style="13" customWidth="1"/>
-    <col min="13" max="14" width="19.21875" customWidth="1"/>
-    <col min="15" max="15" width="19.21875" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.21875" customWidth="1"/>
-    <col min="17" max="17" width="20.21875" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="19.33203125" customWidth="1"/>
+    <col min="8" max="9" width="19.33203125" style="13" customWidth="1"/>
+    <col min="10" max="11" width="19.33203125" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="13" customWidth="1"/>
+    <col min="13" max="14" width="19.33203125" customWidth="1"/>
+    <col min="15" max="15" width="19.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="19.33203125" customWidth="1"/>
     <col min="20" max="20" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="31" width="19.21875" customWidth="1"/>
+    <col min="21" max="31" width="19.33203125" customWidth="1"/>
     <col min="32" max="32" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="19.21875" customWidth="1"/>
-    <col min="36" max="36" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="19.21875" customWidth="1"/>
+    <col min="33" max="35" width="19.33203125" customWidth="1"/>
+    <col min="36" max="36" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="19.33203125" customWidth="1"/>
     <col min="39" max="39" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="19.21875" customWidth="1"/>
+    <col min="40" max="41" width="19.33203125" customWidth="1"/>
     <col min="42" max="42" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.21875" customWidth="1"/>
-    <col min="45" max="45" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.21875" customWidth="1"/>
-    <col min="47" max="47" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.33203125" customWidth="1"/>
+    <col min="45" max="45" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.33203125" customWidth="1"/>
+    <col min="47" max="47" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="84.44140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -26174,7 +26175,7 @@
     </row>
     <row r="72" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="B72" t="s">
         <v>737</v>
@@ -26183,12 +26184,12 @@
         <v>489</v>
       </c>
       <c r="AV72" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="73" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
       <c r="B73" t="s">
         <v>455</v>
@@ -26197,13 +26198,13 @@
         <v>490</v>
       </c>
       <c r="F73" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="U73" t="s">
         <v>2245</v>
       </c>
       <c r="AT73" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="BA73">
         <v>2025</v>
@@ -26211,7 +26212,7 @@
     </row>
     <row r="74" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
       <c r="B74" t="s">
         <v>457</v>
@@ -26220,10 +26221,10 @@
         <v>491</v>
       </c>
       <c r="E74" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="T74" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
     </row>
   </sheetData>
@@ -26238,7 +26239,7 @@
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="255.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26348,15 +26349,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="B14" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2390</v>
+        <v>2387</v>
       </c>
       <c r="B15" t="s">
         <v>2261</v>
@@ -26373,48 +26374,48 @@
   <dimension ref="A1:AT7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.77734375" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
     <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="18.44140625" customWidth="1"/>
     <col min="12" max="12" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="18.77734375" customWidth="1"/>
-    <col min="21" max="21" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="18.6640625" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="20.21875" customWidth="1"/>
-    <col min="31" max="31" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="20.33203125" customWidth="1"/>
+    <col min="31" max="31" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="18.21875" customWidth="1"/>
+    <col min="37" max="37" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="18.33203125" customWidth="1"/>
     <col min="40" max="40" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="55.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -26935,97 +26936,97 @@
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.44140625" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="48.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.21875" customWidth="1"/>
-    <col min="9" max="9" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="22.44140625" customWidth="1"/>
     <col min="20" max="20" width="39.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="47" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="28.5546875" customWidth="1"/>
     <col min="30" max="30" width="39.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="25.44140625" customWidth="1"/>
-    <col min="34" max="34" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.21875" customWidth="1"/>
-    <col min="42" max="42" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.33203125" customWidth="1"/>
+    <col min="42" max="42" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="50" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="49.44140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="39.77734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="57.5546875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="67" max="67" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="18.5546875" customWidth="1"/>
-    <col min="69" max="69" width="61.21875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="61.33203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="42.21875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="42.33203125" bestFit="1" customWidth="1"/>
     <col min="74" max="74" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="37.77734375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="80" max="80" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="48.77734375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="48.6640625" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="85" max="85" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="86" max="86" width="41.44140625" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="53.21875" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="90" max="90" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="92" max="92" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="26.33203125" bestFit="1" customWidth="1"/>
     <col min="96" max="96" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="97" max="97" width="38.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -27601,161 +27602,161 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:97" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:97" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>1471</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" t="s">
         <v>495</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="4">
         <v>45495</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" t="s">
         <v>1558</v>
       </c>
-      <c r="I3" s="53" t="s">
-        <v>2360</v>
-      </c>
-      <c r="J3" s="56">
+      <c r="I3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="J3" s="4">
         <v>44614</v>
       </c>
-      <c r="K3" s="56">
+      <c r="K3" s="4">
         <v>45373</v>
       </c>
-      <c r="L3" s="54">
+      <c r="L3" s="8">
         <v>4</v>
       </c>
-      <c r="M3" s="54">
+      <c r="M3" s="8">
         <v>1</v>
       </c>
-      <c r="P3" s="53" t="s">
+      <c r="P3" t="s">
         <v>658</v>
       </c>
-      <c r="T3" s="53" t="s">
+      <c r="T3" t="s">
         <v>1758</v>
       </c>
-      <c r="Y3" s="53" t="s">
+      <c r="Y3" t="s">
         <v>578</v>
       </c>
-      <c r="Z3" s="53" t="s">
+      <c r="Z3" t="s">
         <v>1658</v>
       </c>
-      <c r="AA3" s="53" t="s">
+      <c r="AA3" t="s">
         <v>266</v>
       </c>
-      <c r="AB3" s="53" t="s">
+      <c r="AB3" t="s">
         <v>264</v>
       </c>
-      <c r="AC3" s="53" t="s">
+      <c r="AC3" t="s">
         <v>1675</v>
       </c>
-      <c r="AD3" s="53" t="s">
+      <c r="AD3" t="s">
         <v>1674</v>
       </c>
-      <c r="AE3" s="53">
+      <c r="AE3">
         <v>24</v>
       </c>
-      <c r="AF3" s="53">
+      <c r="AF3">
         <v>1</v>
       </c>
-      <c r="AG3" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="53">
+      <c r="AG3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
         <v>9</v>
       </c>
-      <c r="AK3" s="53">
+      <c r="AK3">
         <v>1</v>
       </c>
-      <c r="AL3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="53">
-        <v>0</v>
-      </c>
-      <c r="BB3" s="53" t="s">
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="s">
         <v>579</v>
       </c>
-      <c r="BC3" s="53" t="s">
+      <c r="BC3" t="s">
         <v>580</v>
       </c>
-      <c r="BD3" s="53" t="s">
+      <c r="BD3" t="s">
         <v>581</v>
       </c>
-      <c r="BE3" s="53">
+      <c r="BE3">
         <v>3</v>
       </c>
-      <c r="BZ3" s="53" t="s">
+      <c r="BZ3" t="s">
         <v>266</v>
       </c>
-      <c r="CA3" s="53">
-        <v>0</v>
-      </c>
-      <c r="CB3" s="56">
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" s="4">
         <v>44897</v>
       </c>
-      <c r="CC3" s="53" t="s">
+      <c r="CC3" t="s">
         <v>582</v>
       </c>
-      <c r="CI3" s="53">
+      <c r="CI3">
         <v>6</v>
       </c>
-      <c r="CJ3" s="53" t="s">
+      <c r="CJ3" t="s">
         <v>583</v>
       </c>
-      <c r="CK3" s="53">
+      <c r="CK3">
         <v>3</v>
       </c>
-      <c r="CL3" s="53">
+      <c r="CL3">
         <v>1</v>
       </c>
-      <c r="CM3" s="53">
+      <c r="CM3">
         <v>5</v>
       </c>
-      <c r="CN3" s="53">
+      <c r="CN3">
         <v>1</v>
       </c>
-      <c r="CO3" s="53">
+      <c r="CO3">
         <v>6</v>
       </c>
-      <c r="CP3" s="53">
+      <c r="CP3">
         <v>1</v>
       </c>
-      <c r="CQ3" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR3" s="53">
+      <c r="CQ3">
+        <v>0</v>
+      </c>
+      <c r="CR3">
         <v>0</v>
       </c>
     </row>
@@ -27982,131 +27983,131 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:97" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
-        <v>2420</v>
-      </c>
-      <c r="E6" s="53" t="s">
+    <row r="6" spans="1:97" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2417</v>
+      </c>
+      <c r="E6" t="s">
         <v>490</v>
       </c>
-      <c r="I6" s="53" t="s">
-        <v>2360</v>
-      </c>
-      <c r="J6" s="56">
+      <c r="I6" t="s">
+        <v>2357</v>
+      </c>
+      <c r="J6" s="4">
         <v>45064</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="4">
         <v>45373</v>
       </c>
-      <c r="L6" s="54">
-        <v>0</v>
-      </c>
-      <c r="M6" s="54">
-        <v>0</v>
-      </c>
-      <c r="O6" s="53" t="s">
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
         <v>190</v>
       </c>
-      <c r="P6" s="53" t="s">
-        <v>2382</v>
-      </c>
-      <c r="R6" s="53" t="s">
+      <c r="P6" t="s">
+        <v>2379</v>
+      </c>
+      <c r="R6" t="s">
         <v>1715</v>
       </c>
-      <c r="T6" s="53" t="s">
+      <c r="T6" t="s">
         <v>659</v>
       </c>
-      <c r="AE6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="53">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>1</v>
       </c>
-      <c r="AN6" s="53">
+      <c r="AN6">
         <v>4</v>
       </c>
-      <c r="AO6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="53">
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
         <v>2</v>
       </c>
-      <c r="AU6" s="53">
+      <c r="AU6">
         <v>2</v>
       </c>
-      <c r="BE6" s="53">
-        <v>0</v>
-      </c>
-      <c r="BF6" s="53" t="s">
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="s">
         <v>266</v>
       </c>
-      <c r="BG6" s="53">
+      <c r="BG6">
         <v>5000</v>
       </c>
-      <c r="BH6" s="56">
+      <c r="BH6" s="4">
         <v>44114</v>
       </c>
-      <c r="BI6" s="53" t="s">
+      <c r="BI6" t="s">
         <v>1964</v>
       </c>
-      <c r="CI6" s="53">
+      <c r="CI6">
         <v>1</v>
       </c>
-      <c r="CK6" s="53">
+      <c r="CK6">
         <v>1</v>
       </c>
-      <c r="CL6" s="53">
+      <c r="CL6">
         <v>1</v>
       </c>
-      <c r="CM6" s="53">
+      <c r="CM6">
         <v>1</v>
       </c>
-      <c r="CN6" s="53">
+      <c r="CN6">
         <v>1</v>
       </c>
-      <c r="CO6" s="53">
+      <c r="CO6">
         <v>1</v>
       </c>
-      <c r="CP6" s="53">
+      <c r="CP6">
         <v>1</v>
       </c>
-      <c r="CQ6" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR6" s="53">
+      <c r="CQ6">
+        <v>0</v>
+      </c>
+      <c r="CR6">
         <v>0</v>
       </c>
     </row>
@@ -28374,7 +28375,7 @@
         <v>490</v>
       </c>
       <c r="I9" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="J9" s="4">
         <v>45209</v>
@@ -28499,7 +28500,7 @@
         <v>490</v>
       </c>
       <c r="I10" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="J10" s="4">
         <v>45209</v>
@@ -28630,7 +28631,7 @@
         <v>190</v>
       </c>
       <c r="P11" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R11" t="s">
         <v>1715</v>
@@ -28752,7 +28753,7 @@
         <v>190</v>
       </c>
       <c r="P12" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R12" t="s">
         <v>1715</v>
@@ -28877,7 +28878,7 @@
         <v>190</v>
       </c>
       <c r="P13" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R13" t="s">
         <v>1715</v>
@@ -28999,7 +29000,7 @@
         <v>190</v>
       </c>
       <c r="P14" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R14" t="s">
         <v>1715</v>
@@ -29121,7 +29122,7 @@
         <v>190</v>
       </c>
       <c r="P15" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R15" t="s">
         <v>1715</v>
@@ -29249,7 +29250,7 @@
         <v>190</v>
       </c>
       <c r="P16" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R16" t="s">
         <v>1715</v>
@@ -29374,7 +29375,7 @@
         <v>190</v>
       </c>
       <c r="P17" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R17" t="s">
         <v>1715</v>
@@ -29499,7 +29500,7 @@
         <v>190</v>
       </c>
       <c r="P18" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="R18" t="s">
         <v>1715</v>
@@ -29600,7 +29601,7 @@
     </row>
     <row r="19" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2392</v>
+        <v>2389</v>
       </c>
       <c r="B19" t="s">
         <v>1008</v>
@@ -29615,7 +29616,7 @@
         <v>490</v>
       </c>
       <c r="I19" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="J19" s="4">
         <v>45209</v>
@@ -29734,13 +29735,13 @@
     </row>
     <row r="20" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="E20" t="s">
         <v>490</v>
       </c>
       <c r="I20" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
@@ -29853,7 +29854,7 @@
     </row>
     <row r="21" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2408</v>
+        <v>2405</v>
       </c>
       <c r="E21" t="s">
         <v>246</v>
@@ -29986,7 +29987,7 @@
     </row>
     <row r="22" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2413</v>
+        <v>2410</v>
       </c>
       <c r="E22" t="s">
         <v>246</v>
@@ -30097,7 +30098,7 @@
     </row>
     <row r="23" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
       <c r="E23" t="s">
         <v>246</v>
@@ -30230,7 +30231,7 @@
     </row>
     <row r="24" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2410</v>
+        <v>2407</v>
       </c>
       <c r="E24" t="s">
         <v>246</v>
@@ -30390,7 +30391,7 @@
     </row>
     <row r="25" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2414</v>
+        <v>2411</v>
       </c>
       <c r="E25" t="s">
         <v>246</v>
@@ -30515,7 +30516,7 @@
     </row>
     <row r="26" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2411</v>
+        <v>2408</v>
       </c>
       <c r="E26" t="s">
         <v>246</v>
@@ -30728,7 +30729,7 @@
     </row>
     <row r="27" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2415</v>
+        <v>2412</v>
       </c>
       <c r="E27" t="s">
         <v>246</v>
@@ -30852,7 +30853,7 @@
     </row>
     <row r="28" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2412</v>
+        <v>2409</v>
       </c>
       <c r="E28" t="s">
         <v>246</v>
@@ -30988,7 +30989,7 @@
     </row>
     <row r="29" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
       <c r="F29" s="4"/>
       <c r="J29" s="4"/>
@@ -31101,7 +31102,7 @@
     </row>
     <row r="30" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2417</v>
+        <v>2414</v>
       </c>
       <c r="E30" t="s">
         <v>246</v>
@@ -31234,7 +31235,7 @@
     </row>
     <row r="31" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
       <c r="F31" s="4"/>
       <c r="J31" s="4"/>
@@ -31342,253 +31343,253 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:97" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="53" t="s">
-        <v>2419</v>
-      </c>
-      <c r="L32" s="54">
-        <v>0</v>
-      </c>
-      <c r="M32" s="54">
-        <v>0</v>
-      </c>
-      <c r="P32" s="53" t="s">
+    <row r="32" spans="1:97" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0</v>
+      </c>
+      <c r="M32" s="8">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
         <v>658</v>
       </c>
-      <c r="AA32" s="53" t="s">
+      <c r="AA32" t="s">
         <v>297</v>
       </c>
-      <c r="AB32" s="53" t="s">
+      <c r="AB32" t="s">
         <v>297</v>
       </c>
-      <c r="AC32" s="53" t="s">
+      <c r="AC32" t="s">
         <v>297</v>
       </c>
-      <c r="AE32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="53">
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
         <v>5</v>
       </c>
-      <c r="AN32" s="53">
+      <c r="AN32">
         <v>1</v>
       </c>
-      <c r="AO32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS32" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT32" s="53">
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
         <v>3</v>
       </c>
-      <c r="AU32" s="53">
-        <v>0</v>
-      </c>
-      <c r="BE32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CI32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CK32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CL32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CM32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CN32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CO32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CP32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CQ32" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR32" s="53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:96" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="53" t="s">
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="CI32">
+        <v>0</v>
+      </c>
+      <c r="CK32">
+        <v>0</v>
+      </c>
+      <c r="CL32">
+        <v>0</v>
+      </c>
+      <c r="CM32">
+        <v>0</v>
+      </c>
+      <c r="CN32">
+        <v>0</v>
+      </c>
+      <c r="CO32">
+        <v>0</v>
+      </c>
+      <c r="CP32">
+        <v>0</v>
+      </c>
+      <c r="CQ32">
+        <v>0</v>
+      </c>
+      <c r="CR32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>584</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" t="s">
         <v>490</v>
       </c>
-      <c r="I33" s="53" t="s">
-        <v>2360</v>
-      </c>
-      <c r="J33" s="56">
+      <c r="I33" t="s">
+        <v>2357</v>
+      </c>
+      <c r="J33" s="4">
         <v>45064</v>
       </c>
-      <c r="K33" s="56">
+      <c r="K33" s="4">
         <v>45373</v>
       </c>
-      <c r="L33" s="54">
-        <v>0</v>
-      </c>
-      <c r="M33" s="54">
-        <v>0</v>
-      </c>
-      <c r="O33" s="53" t="s">
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
         <v>190</v>
       </c>
-      <c r="P33" s="53" t="s">
-        <v>2382</v>
-      </c>
-      <c r="R33" s="53" t="s">
+      <c r="P33" t="s">
+        <v>2379</v>
+      </c>
+      <c r="R33" t="s">
         <v>1715</v>
       </c>
-      <c r="T33" s="53" t="s">
+      <c r="T33" t="s">
         <v>659</v>
       </c>
-      <c r="AE33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="55">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT33" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU33" s="53">
-        <v>0</v>
-      </c>
-      <c r="BE33" s="53">
-        <v>0</v>
-      </c>
-      <c r="BH33" s="56"/>
-      <c r="CI33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CK33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CL33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CM33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CN33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CO33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CP33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CQ33" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR33" s="53">
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BH33" s="4"/>
+      <c r="CI33">
+        <v>0</v>
+      </c>
+      <c r="CK33">
+        <v>0</v>
+      </c>
+      <c r="CL33">
+        <v>0</v>
+      </c>
+      <c r="CM33">
+        <v>0</v>
+      </c>
+      <c r="CN33">
+        <v>0</v>
+      </c>
+      <c r="CO33">
+        <v>0</v>
+      </c>
+      <c r="CP33">
+        <v>0</v>
+      </c>
+      <c r="CQ33">
+        <v>0</v>
+      </c>
+      <c r="CR33">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A34" s="53" t="s">
-        <v>2421</v>
+      <c r="A34" t="s">
+        <v>2418</v>
       </c>
       <c r="E34" t="s">
         <v>490</v>
       </c>
       <c r="I34" t="s">
-        <v>2360</v>
-      </c>
-      <c r="J34" s="56">
+        <v>2357</v>
+      </c>
+      <c r="J34" s="4">
         <v>45064</v>
       </c>
-      <c r="K34" s="56">
+      <c r="K34" s="4">
         <v>45373</v>
       </c>
-      <c r="L34" s="54">
-        <v>0</v>
-      </c>
-      <c r="M34" s="54">
+      <c r="L34" s="8">
+        <v>0</v>
+      </c>
+      <c r="M34" s="8">
         <v>0</v>
       </c>
       <c r="O34" t="s">
         <v>192</v>
       </c>
-      <c r="P34" s="53" t="s">
+      <c r="P34" t="s">
         <v>1771</v>
       </c>
       <c r="R34" t="s">
@@ -31597,85 +31598,85 @@
       <c r="T34" t="s">
         <v>1758</v>
       </c>
-      <c r="AE34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="55">
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="2">
         <v>13</v>
       </c>
-      <c r="AH34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="53">
-        <v>0</v>
-      </c>
-      <c r="BE34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CI34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CK34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CL34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CM34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CN34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CO34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CP34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CQ34" s="53">
-        <v>0</v>
-      </c>
-      <c r="CR34" s="53">
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="CI34">
+        <v>0</v>
+      </c>
+      <c r="CK34">
+        <v>0</v>
+      </c>
+      <c r="CL34">
+        <v>0</v>
+      </c>
+      <c r="CM34">
+        <v>0</v>
+      </c>
+      <c r="CN34">
+        <v>0</v>
+      </c>
+      <c r="CO34">
+        <v>0</v>
+      </c>
+      <c r="CP34">
+        <v>0</v>
+      </c>
+      <c r="CQ34">
+        <v>0</v>
+      </c>
+      <c r="CR34">
         <v>0</v>
       </c>
     </row>
@@ -31692,8 +31693,8 @@
   <cols>
     <col min="1" max="1" width="33.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -31793,16 +31794,16 @@
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.77734375" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="103.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="103.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -31981,16 +31982,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE83F7F-CA8C-41F0-ABE1-C32A636E8FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592CDA47-D6A6-4165-BCB0-9D09518CEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -6972,9 +6972,6 @@
     <t>220 Horn</t>
   </si>
   <si>
-    <t>949 patullo</t>
-  </si>
-  <si>
     <t>Create new Activity Tab for MF</t>
   </si>
   <si>
@@ -7368,9 +7365,6 @@
     <t>Access;Development</t>
   </si>
   <si>
-    <t>002-256-525;90172682;015-768-082</t>
-  </si>
-  <si>
     <t>ALBERT SYLVESTER RICHMOND;Alfred Garnette Pancake;Andrea Krenn</t>
   </si>
   <si>
@@ -7381,6 +7375,12 @@
   </si>
   <si>
     <t>April Holly Funk</t>
+  </si>
+  <si>
+    <t>949 pattullo</t>
+  </si>
+  <si>
+    <t>002-256-525;90172682;002-406-349</t>
   </si>
 </sst>
 </file>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -15321,7 +15321,7 @@
         <v>886</v>
       </c>
       <c r="P2" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="Q2" t="s">
         <v>2137</v>
@@ -15362,7 +15362,7 @@
         <v>1002</v>
       </c>
       <c r="P3" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="Q3" t="s">
         <v>2138</v>
@@ -15424,7 +15424,7 @@
         <v>886</v>
       </c>
       <c r="P4" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="Q4" t="s">
         <v>2135</v>
@@ -15586,7 +15586,7 @@
         <v>886</v>
       </c>
       <c r="P7" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="Q7" t="s">
         <v>2139</v>
@@ -15720,7 +15720,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="B10" s="37"/>
       <c r="E10" t="s">
@@ -15733,7 +15733,7 @@
         <v>45569</v>
       </c>
       <c r="K10" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="L10" t="s">
         <v>1560</v>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -17720,7 +17720,7 @@
     </row>
     <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="B16" t="s">
         <v>791</v>
@@ -17729,7 +17729,7 @@
         <v>45744</v>
       </c>
       <c r="H16" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="J16" t="s">
         <v>1355</v>
@@ -18573,7 +18573,7 @@
         <v>675</v>
       </c>
       <c r="B2" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="C2" t="s">
         <v>250</v>
@@ -18663,7 +18663,7 @@
         <v>891</v>
       </c>
       <c r="B8" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="C8" t="s">
         <v>892</v>
@@ -18694,7 +18694,7 @@
         <v>1088</v>
       </c>
       <c r="B10" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>1089</v>
@@ -18708,7 +18708,7 @@
         <v>1237</v>
       </c>
       <c r="B11" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="C11" t="s">
         <v>2135</v>
@@ -18736,7 +18736,7 @@
         <v>1340</v>
       </c>
       <c r="B13" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="C13" t="s">
         <v>1341</v>
@@ -18750,7 +18750,7 @@
         <v>1340</v>
       </c>
       <c r="B14" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="C14" t="s">
         <v>1342</v>
@@ -18988,13 +18988,13 @@
         <v>239</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1500</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2285</v>
@@ -19021,19 +19021,19 @@
         <v>2292</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>2359</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>2360</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>2361</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>2362</v>
       </c>
-      <c r="T1" s="3" t="s">
-        <v>2363</v>
-      </c>
       <c r="U1" s="3" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -19044,7 +19044,7 @@
         <v>4361431</v>
       </c>
       <c r="D2" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="I2">
         <v>48</v>
@@ -19071,7 +19071,7 @@
         <v>2294</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -19079,7 +19079,7 @@
         <v>327</v>
       </c>
       <c r="H3" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -19087,7 +19087,7 @@
         <v>280</v>
       </c>
       <c r="D4" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
@@ -19095,7 +19095,7 @@
         <v>278</v>
       </c>
       <c r="B5" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -19144,7 +19144,7 @@
         <v>1821391</v>
       </c>
       <c r="D10" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="E10" t="s">
         <v>1338</v>
@@ -19187,7 +19187,7 @@
         <v>1317</v>
       </c>
       <c r="G12" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="I12">
         <v>49</v>
@@ -19214,10 +19214,10 @@
         <v>2294</v>
       </c>
       <c r="Q12" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="U12" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -19255,19 +19255,19 @@
         <v>1821391</v>
       </c>
       <c r="D16" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="E16" t="s">
         <v>1747</v>
       </c>
       <c r="H16" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="Q16" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="U16" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
@@ -19365,13 +19365,13 @@
         <v>1760</v>
       </c>
       <c r="F26" t="s">
+        <v>2372</v>
+      </c>
+      <c r="H26" t="s">
         <v>2373</v>
       </c>
-      <c r="H26" t="s">
-        <v>2374</v>
-      </c>
       <c r="U26" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
@@ -19408,7 +19408,7 @@
         <v>1336</v>
       </c>
       <c r="H28" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
@@ -19416,7 +19416,7 @@
         <v>1337</v>
       </c>
       <c r="F29" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="B32" s="14"/>
       <c r="E32" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -19462,7 +19462,7 @@
         <v>2174</v>
       </c>
       <c r="F33" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="U33" s="14" t="s">
         <v>2174</v>
@@ -19487,7 +19487,7 @@
         <v>90172682</v>
       </c>
       <c r="D35" t="s">
-        <v>2296</v>
+        <v>2431</v>
       </c>
       <c r="E35" t="s">
         <v>2228</v>
@@ -19517,7 +19517,7 @@
         <v>2294</v>
       </c>
       <c r="U35" t="s">
-        <v>2428</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.3">
@@ -19533,19 +19533,19 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="52" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="B37" s="14"/>
       <c r="E37" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="U37" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B38" t="s">
         <v>2227</v>
@@ -19553,10 +19553,10 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B39" t="s">
         <v>2394</v>
-      </c>
-      <c r="B39" t="s">
-        <v>2395</v>
       </c>
     </row>
   </sheetData>
@@ -19853,7 +19853,7 @@
         <v>1271</v>
       </c>
       <c r="W4" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="X4" t="s">
         <v>721</v>
@@ -20142,13 +20142,13 @@
         <v>2204</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>2309</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>2310</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>2311</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -20317,7 +20317,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="B6" t="s">
         <v>490</v>
@@ -20413,13 +20413,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="B9" t="s">
         <v>490</v>
       </c>
       <c r="G9" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="I9" t="s">
         <v>2221</v>
@@ -20445,13 +20445,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="B10" t="s">
         <v>490</v>
       </c>
       <c r="G10" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="I10" t="s">
         <v>2238</v>
@@ -20477,13 +20477,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="B11" t="s">
         <v>490</v>
       </c>
       <c r="G11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="I11" t="s">
         <v>2239</v>
@@ -20509,13 +20509,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="B12" t="s">
         <v>490</v>
       </c>
       <c r="G12" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="I12" t="s">
         <v>1787</v>
@@ -20827,7 +20827,7 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1166</v>
@@ -20839,7 +20839,7 @@
         <v>1168</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1169</v>
@@ -20851,10 +20851,10 @@
         <v>1171</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1172</v>
@@ -20889,7 +20889,7 @@
         <v>1189</v>
       </c>
       <c r="D2" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="E2" t="s">
         <v>1213</v>
@@ -20904,7 +20904,7 @@
         <v>2158</v>
       </c>
       <c r="J2" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="K2" t="s">
         <v>1195</v>
@@ -20942,7 +20942,7 @@
         <v>1190</v>
       </c>
       <c r="D3" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="E3" t="s">
         <v>1191</v>
@@ -20957,7 +20957,7 @@
         <v>1194</v>
       </c>
       <c r="J3" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="K3" t="s">
         <v>2157</v>
@@ -21010,7 +21010,7 @@
         <v>1223</v>
       </c>
       <c r="J4" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="K4" t="s">
         <v>1225</v>
@@ -21048,7 +21048,7 @@
         <v>1278</v>
       </c>
       <c r="D5" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="E5" t="s">
         <v>1213</v>
@@ -21063,7 +21063,7 @@
         <v>2225</v>
       </c>
       <c r="J5" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -21086,16 +21086,16 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="D6" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="E6" t="s">
         <v>1213</v>
@@ -21104,19 +21104,19 @@
         <v>45623</v>
       </c>
       <c r="H6" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="I6" t="s">
+        <v>2337</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2422</v>
+      </c>
+      <c r="K6" t="s">
         <v>2338</v>
       </c>
-      <c r="J6" t="s">
-        <v>2423</v>
-      </c>
-      <c r="K6" t="s">
-        <v>2339</v>
-      </c>
       <c r="L6" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -21139,16 +21139,16 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D7" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="E7" t="s">
         <v>495</v>
@@ -21160,19 +21160,19 @@
         <v>45760</v>
       </c>
       <c r="H7" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="I7" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="J7" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="K7" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -21195,16 +21195,16 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="D8" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E8" t="s">
         <v>1213</v>
@@ -21213,19 +21213,19 @@
         <v>45631</v>
       </c>
       <c r="H8" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="I8" t="s">
+        <v>2428</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2429</v>
+      </c>
+      <c r="K8" t="s">
         <v>2430</v>
       </c>
-      <c r="J8" t="s">
-        <v>2431</v>
-      </c>
-      <c r="K8" t="s">
-        <v>2432</v>
-      </c>
       <c r="L8" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -21357,16 +21357,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B4" t="s">
         <v>2318</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2319</v>
       </c>
       <c r="C4" s="4">
         <v>45300</v>
       </c>
       <c r="D4" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="E4" s="11">
         <v>9500.9699999999993</v>
@@ -21386,16 +21386,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="B5" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="C5" s="4">
         <v>45544</v>
       </c>
       <c r="D5" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="E5" s="11">
         <v>155.84</v>
@@ -21415,16 +21415,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="B6" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="C6" s="4">
         <v>45576</v>
       </c>
       <c r="D6" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="E6" s="11">
         <v>15077554.890000001</v>
@@ -21444,7 +21444,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="B7" t="s">
         <v>1379</v>
@@ -21453,7 +21453,7 @@
         <v>45659</v>
       </c>
       <c r="D7" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="E7" s="11">
         <v>1780</v>
@@ -21473,16 +21473,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="B8" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="C8" s="4">
         <v>45607</v>
       </c>
       <c r="D8" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="E8" s="11">
         <v>50</v>
@@ -21502,16 +21502,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B9" t="s">
         <v>2328</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2329</v>
       </c>
       <c r="C9" s="4">
         <v>45638</v>
       </c>
       <c r="D9" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="E9" s="11">
         <v>127.9</v>
@@ -24593,7 +24593,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B17">
         <v>71</v>
@@ -24604,7 +24604,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="B18">
         <v>71</v>
@@ -24615,12 +24615,12 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
     </row>
   </sheetData>
@@ -26175,7 +26175,7 @@
     </row>
     <row r="72" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="B72" t="s">
         <v>737</v>
@@ -26184,12 +26184,12 @@
         <v>489</v>
       </c>
       <c r="AV72" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="73" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B73" t="s">
         <v>455</v>
@@ -26198,13 +26198,13 @@
         <v>490</v>
       </c>
       <c r="F73" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="U73" t="s">
         <v>2245</v>
       </c>
       <c r="AT73" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="BA73">
         <v>2025</v>
@@ -26212,7 +26212,7 @@
     </row>
     <row r="74" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B74" t="s">
         <v>457</v>
@@ -26221,10 +26221,10 @@
         <v>491</v>
       </c>
       <c r="E74" t="s">
+        <v>2352</v>
+      </c>
+      <c r="T74" t="s">
         <v>2353</v>
-      </c>
-      <c r="T74" t="s">
-        <v>2354</v>
       </c>
     </row>
   </sheetData>
@@ -26349,15 +26349,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="B14" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="B15" t="s">
         <v>2261</v>
@@ -27616,7 +27616,7 @@
         <v>1558</v>
       </c>
       <c r="I3" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J3" s="4">
         <v>44614</v>
@@ -27985,13 +27985,13 @@
     </row>
     <row r="6" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="E6" t="s">
         <v>490</v>
       </c>
       <c r="I6" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J6" s="4">
         <v>45064</v>
@@ -28009,7 +28009,7 @@
         <v>190</v>
       </c>
       <c r="P6" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R6" t="s">
         <v>1715</v>
@@ -28375,7 +28375,7 @@
         <v>490</v>
       </c>
       <c r="I9" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J9" s="4">
         <v>45209</v>
@@ -28500,7 +28500,7 @@
         <v>490</v>
       </c>
       <c r="I10" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J10" s="4">
         <v>45209</v>
@@ -28631,7 +28631,7 @@
         <v>190</v>
       </c>
       <c r="P11" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R11" t="s">
         <v>1715</v>
@@ -28753,7 +28753,7 @@
         <v>190</v>
       </c>
       <c r="P12" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R12" t="s">
         <v>1715</v>
@@ -28878,7 +28878,7 @@
         <v>190</v>
       </c>
       <c r="P13" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R13" t="s">
         <v>1715</v>
@@ -29000,7 +29000,7 @@
         <v>190</v>
       </c>
       <c r="P14" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R14" t="s">
         <v>1715</v>
@@ -29122,7 +29122,7 @@
         <v>190</v>
       </c>
       <c r="P15" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R15" t="s">
         <v>1715</v>
@@ -29250,7 +29250,7 @@
         <v>190</v>
       </c>
       <c r="P16" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R16" t="s">
         <v>1715</v>
@@ -29375,7 +29375,7 @@
         <v>190</v>
       </c>
       <c r="P17" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R17" t="s">
         <v>1715</v>
@@ -29500,7 +29500,7 @@
         <v>190</v>
       </c>
       <c r="P18" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R18" t="s">
         <v>1715</v>
@@ -29601,7 +29601,7 @@
     </row>
     <row r="19" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="B19" t="s">
         <v>1008</v>
@@ -29616,7 +29616,7 @@
         <v>490</v>
       </c>
       <c r="I19" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J19" s="4">
         <v>45209</v>
@@ -29735,13 +29735,13 @@
     </row>
     <row r="20" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="E20" t="s">
         <v>490</v>
       </c>
       <c r="I20" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
@@ -29854,7 +29854,7 @@
     </row>
     <row r="21" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="E21" t="s">
         <v>246</v>
@@ -29987,7 +29987,7 @@
     </row>
     <row r="22" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E22" t="s">
         <v>246</v>
@@ -30098,7 +30098,7 @@
     </row>
     <row r="23" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="E23" t="s">
         <v>246</v>
@@ -30231,7 +30231,7 @@
     </row>
     <row r="24" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="E24" t="s">
         <v>246</v>
@@ -30391,7 +30391,7 @@
     </row>
     <row r="25" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="E25" t="s">
         <v>246</v>
@@ -30516,7 +30516,7 @@
     </row>
     <row r="26" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="E26" t="s">
         <v>246</v>
@@ -30729,7 +30729,7 @@
     </row>
     <row r="27" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="E27" t="s">
         <v>246</v>
@@ -30853,7 +30853,7 @@
     </row>
     <row r="28" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="E28" t="s">
         <v>246</v>
@@ -30989,7 +30989,7 @@
     </row>
     <row r="29" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="F29" s="4"/>
       <c r="J29" s="4"/>
@@ -31102,7 +31102,7 @@
     </row>
     <row r="30" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="E30" t="s">
         <v>246</v>
@@ -31235,7 +31235,7 @@
     </row>
     <row r="31" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="F31" s="4"/>
       <c r="J31" s="4"/>
@@ -31345,7 +31345,7 @@
     </row>
     <row r="32" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
@@ -31455,7 +31455,7 @@
         <v>490</v>
       </c>
       <c r="I33" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J33" s="4">
         <v>45064</v>
@@ -31473,7 +31473,7 @@
         <v>190</v>
       </c>
       <c r="P33" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="R33" t="s">
         <v>1715</v>
@@ -31566,13 +31566,13 @@
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="E34" t="s">
         <v>490</v>
       </c>
       <c r="I34" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J34" s="4">
         <v>45064</v>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592CDA47-D6A6-4165-BCB0-9D09518CEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C91D6A-C260-45BD-A3EE-C6D4F062DF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -7287,9 +7287,6 @@
     <t>010-764-135;015-069-940;007-095-333</t>
   </si>
   <si>
-    <t>005-565-383;015-069-940;-131.339444, 52.308056</t>
-  </si>
-  <si>
     <t>026-172-674</t>
   </si>
   <si>
@@ -7381,6 +7378,9 @@
   </si>
   <si>
     <t>002-256-525;90172682;002-406-349</t>
+  </si>
+  <si>
+    <t>005-565-383;001-646-435;-131.339444, 52.308056</t>
   </si>
 </sst>
 </file>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -19217,7 +19217,7 @@
         <v>2377</v>
       </c>
       <c r="U12" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -19371,7 +19371,7 @@
         <v>2373</v>
       </c>
       <c r="U26" t="s">
-        <v>2401</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
@@ -19487,7 +19487,7 @@
         <v>90172682</v>
       </c>
       <c r="D35" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="E35" t="s">
         <v>2228</v>
@@ -19517,7 +19517,7 @@
         <v>2294</v>
       </c>
       <c r="U35" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.3">
@@ -19540,7 +19540,7 @@
         <v>2375</v>
       </c>
       <c r="U37" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -20889,7 +20889,7 @@
         <v>1189</v>
       </c>
       <c r="D2" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="E2" t="s">
         <v>1213</v>
@@ -20904,7 +20904,7 @@
         <v>2158</v>
       </c>
       <c r="J2" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="K2" t="s">
         <v>1195</v>
@@ -20942,7 +20942,7 @@
         <v>1190</v>
       </c>
       <c r="D3" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="E3" t="s">
         <v>1191</v>
@@ -20957,7 +20957,7 @@
         <v>1194</v>
       </c>
       <c r="J3" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="K3" t="s">
         <v>2157</v>
@@ -21010,7 +21010,7 @@
         <v>1223</v>
       </c>
       <c r="J4" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="K4" t="s">
         <v>1225</v>
@@ -21048,7 +21048,7 @@
         <v>1278</v>
       </c>
       <c r="D5" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="E5" t="s">
         <v>1213</v>
@@ -21063,7 +21063,7 @@
         <v>2225</v>
       </c>
       <c r="J5" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -21110,7 +21110,7 @@
         <v>2337</v>
       </c>
       <c r="J6" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="K6" t="s">
         <v>2338</v>
@@ -21166,10 +21166,10 @@
         <v>2307</v>
       </c>
       <c r="J7" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="K7" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="L7" s="14" t="s">
         <v>2315</v>
@@ -21216,13 +21216,13 @@
         <v>2306</v>
       </c>
       <c r="I8" t="s">
+        <v>2427</v>
+      </c>
+      <c r="J8" t="s">
         <v>2428</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>2429</v>
-      </c>
-      <c r="K8" t="s">
-        <v>2430</v>
       </c>
       <c r="L8" t="s">
         <v>2316</v>
@@ -27985,7 +27985,7 @@
     </row>
     <row r="6" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="E6" t="s">
         <v>490</v>
@@ -29854,7 +29854,7 @@
     </row>
     <row r="21" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="E21" t="s">
         <v>246</v>
@@ -29987,7 +29987,7 @@
     </row>
     <row r="22" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="E22" t="s">
         <v>246</v>
@@ -30098,7 +30098,7 @@
     </row>
     <row r="23" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="E23" t="s">
         <v>246</v>
@@ -30231,7 +30231,7 @@
     </row>
     <row r="24" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="E24" t="s">
         <v>246</v>
@@ -30391,7 +30391,7 @@
     </row>
     <row r="25" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E25" t="s">
         <v>246</v>
@@ -30516,7 +30516,7 @@
     </row>
     <row r="26" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="E26" t="s">
         <v>246</v>
@@ -30729,7 +30729,7 @@
     </row>
     <row r="27" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="E27" t="s">
         <v>246</v>
@@ -30853,7 +30853,7 @@
     </row>
     <row r="28" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="E28" t="s">
         <v>246</v>
@@ -30989,7 +30989,7 @@
     </row>
     <row r="29" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="F29" s="4"/>
       <c r="J29" s="4"/>
@@ -31102,7 +31102,7 @@
     </row>
     <row r="30" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="E30" t="s">
         <v>246</v>
@@ -31235,7 +31235,7 @@
     </row>
     <row r="31" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="F31" s="4"/>
       <c r="J31" s="4"/>
@@ -31345,7 +31345,7 @@
     </row>
     <row r="32" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
@@ -31354,7 +31354,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>658</v>
+        <v>2378</v>
       </c>
       <c r="AA32" t="s">
         <v>297</v>
@@ -31566,7 +31566,7 @@
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="E34" t="s">
         <v>490</v>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592CDA47-D6A6-4165-BCB0-9D09518CEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9842984-1CC4-44F6-AE3B-C9565752CB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <sheet name="Notes" sheetId="10" r:id="rId44"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">DocumentsDetails!$A$1:$BA$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">DocumentsDetails!$A$1:$BB$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="2433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4418" uniqueCount="2442">
   <si>
     <t>FirstName</t>
   </si>
@@ -7381,6 +7381,33 @@
   </si>
   <si>
     <t>002-256-525;90172682;002-406-349</t>
+  </si>
+  <si>
+    <t>DocumentName</t>
+  </si>
+  <si>
+    <t>Brief Note document</t>
+  </si>
+  <si>
+    <t>Correspondence here</t>
+  </si>
+  <si>
+    <t>Appraisals from Van</t>
+  </si>
+  <si>
+    <t>Notty notes</t>
+  </si>
+  <si>
+    <t>Admision 2025-12-01</t>
+  </si>
+  <si>
+    <t>Props declarations</t>
+  </si>
+  <si>
+    <t>MOTT plan on Victoria</t>
+  </si>
+  <si>
+    <t>PropertySearchProject</t>
   </si>
 </sst>
 </file>
@@ -10730,7 +10757,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45995</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10968,7 +10995,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45995</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11193,7 +11220,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45995</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11766,7 +11793,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45995</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12109,7 +12136,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45995</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -16894,7 +16921,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45995</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -18942,7 +18969,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E382B1-281B-4434-81AA-04C8D5F3D2FB}">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -18962,16 +18989,17 @@
     <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.44140625" customWidth="1"/>
-    <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.44140625" customWidth="1"/>
+    <col min="23" max="23" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -19033,10 +19061,13 @@
         <v>2362</v>
       </c>
       <c r="U1" s="3" t="s">
+        <v>2441</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>2398</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>275</v>
       </c>
@@ -19070,11 +19101,11 @@
       <c r="P2" t="s">
         <v>2294</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="V2" s="14" t="s">
         <v>2399</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>327</v>
       </c>
@@ -19082,7 +19113,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>280</v>
       </c>
@@ -19090,7 +19121,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>278</v>
       </c>
@@ -19098,7 +19129,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>281</v>
       </c>
@@ -19106,7 +19137,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1631</v>
       </c>
@@ -19117,7 +19148,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>273</v>
       </c>
@@ -19125,7 +19156,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>274</v>
       </c>
@@ -19133,7 +19164,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1487</v>
       </c>
@@ -19174,7 +19205,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>396</v>
       </c>
@@ -19182,7 +19213,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1317</v>
       </c>
@@ -19216,11 +19247,11 @@
       <c r="Q12" t="s">
         <v>2377</v>
       </c>
-      <c r="U12" t="s">
+      <c r="V12" t="s">
         <v>2403</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1315</v>
       </c>
@@ -19228,7 +19259,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1318</v>
       </c>
@@ -19236,7 +19267,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1316</v>
       </c>
@@ -19244,7 +19275,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>689</v>
       </c>
@@ -19266,33 +19297,33 @@
       <c r="Q16" t="s">
         <v>2363</v>
       </c>
-      <c r="U16" t="s">
+      <c r="V16" t="s">
         <v>2400</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1319</v>
       </c>
       <c r="B17" t="s">
         <v>1612</v>
       </c>
-      <c r="U17" t="s">
+      <c r="V17" t="s">
         <v>1612</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1320</v>
       </c>
       <c r="B18" t="s">
         <v>1616</v>
       </c>
-      <c r="U18" t="s">
+      <c r="V18" t="s">
         <v>1616</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>697</v>
       </c>
@@ -19300,7 +19331,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1321</v>
       </c>
@@ -19308,29 +19339,29 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1322</v>
       </c>
       <c r="B21" t="s">
         <v>843</v>
       </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1323</v>
       </c>
       <c r="B22" t="s">
         <v>1619</v>
       </c>
-      <c r="U22" t="s">
+      <c r="V22" t="s">
         <v>1619</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1324</v>
       </c>
@@ -19338,7 +19369,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1325</v>
       </c>
@@ -19346,7 +19377,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1326</v>
       </c>
@@ -19357,7 +19388,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1334</v>
       </c>
@@ -19370,11 +19401,11 @@
       <c r="H26" t="s">
         <v>2373</v>
       </c>
-      <c r="U26" t="s">
+      <c r="V26" t="s">
         <v>2401</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1335</v>
       </c>
@@ -19403,7 +19434,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1336</v>
       </c>
@@ -19411,7 +19442,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1337</v>
       </c>
@@ -19419,7 +19450,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1486</v>
       </c>
@@ -19436,7 +19467,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A31" s="52" t="s">
         <v>1501</v>
       </c>
@@ -19445,7 +19476,7 @@
       </c>
       <c r="H31" s="14"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="52" t="s">
         <v>2170</v>
       </c>
@@ -19454,7 +19485,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="52" t="s">
         <v>2173</v>
       </c>
@@ -19464,11 +19495,11 @@
       <c r="F33" t="s">
         <v>2371</v>
       </c>
-      <c r="U33" s="14" t="s">
+      <c r="V33" s="14" t="s">
         <v>2174</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="52" t="s">
         <v>2183</v>
       </c>
@@ -19476,7 +19507,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="52" t="s">
         <v>2211</v>
       </c>
@@ -19516,22 +19547,22 @@
       <c r="P35" t="s">
         <v>2294</v>
       </c>
-      <c r="U35" t="s">
+      <c r="V35" t="s">
         <v>2432</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="52" t="s">
         <v>2212</v>
       </c>
       <c r="B36" t="s">
         <v>2229</v>
       </c>
-      <c r="U36" t="s">
+      <c r="V36" t="s">
         <v>2229</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="52" t="s">
         <v>2341</v>
       </c>
@@ -19539,11 +19570,11 @@
       <c r="E37" t="s">
         <v>2375</v>
       </c>
-      <c r="U37" t="s">
+      <c r="V37" t="s">
         <v>2402</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
         <v>2344</v>
       </c>
@@ -19551,7 +19582,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
         <v>2393</v>
       </c>
@@ -24631,44 +24662,45 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2665AEC9-C942-4A65-984C-CAD52F4E2CCE}">
-  <dimension ref="A1:BA74"/>
+  <dimension ref="A1:BB74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="103.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="83" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="19.33203125" customWidth="1"/>
-    <col min="8" max="9" width="19.33203125" style="13" customWidth="1"/>
-    <col min="10" max="11" width="19.33203125" customWidth="1"/>
-    <col min="12" max="12" width="19.33203125" style="13" customWidth="1"/>
-    <col min="13" max="14" width="19.33203125" customWidth="1"/>
-    <col min="15" max="15" width="19.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="19.33203125" customWidth="1"/>
-    <col min="20" max="20" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="31" width="19.33203125" customWidth="1"/>
-    <col min="32" max="32" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="19.33203125" customWidth="1"/>
-    <col min="36" max="36" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="19.33203125" customWidth="1"/>
-    <col min="39" max="39" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="19.33203125" customWidth="1"/>
-    <col min="42" max="42" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.33203125" customWidth="1"/>
-    <col min="45" max="45" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.33203125" customWidth="1"/>
-    <col min="47" max="47" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="84.44140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="10" width="19.33203125" style="13" customWidth="1"/>
+    <col min="11" max="12" width="19.33203125" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" style="13" customWidth="1"/>
+    <col min="14" max="15" width="19.33203125" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.33203125" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="19.33203125" customWidth="1"/>
+    <col min="21" max="21" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="32" width="19.33203125" customWidth="1"/>
+    <col min="33" max="33" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="19.33203125" customWidth="1"/>
+    <col min="37" max="37" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="19.33203125" customWidth="1"/>
+    <col min="40" max="40" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="19.33203125" customWidth="1"/>
+    <col min="43" max="43" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.33203125" customWidth="1"/>
+    <col min="46" max="46" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.33203125" customWidth="1"/>
+    <col min="48" max="48" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="84.44140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -24679,157 +24711,160 @@
         <v>504</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1900</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>1906</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>1907</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="AW1" s="12" t="s">
+      <c r="AX1" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>CONCATENATE("Lease &amp; Licenses - ",B2)</f>
         <v>Lease &amp; Licenses - Appraisals/Reviews</v>
@@ -24840,11 +24875,11 @@
       <c r="C2" t="s">
         <v>489</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A10" si="0">CONCATENATE("Lease &amp; Licenses - ",B3)</f>
         <v>Lease &amp; Licenses - BC assessment search</v>
@@ -24855,20 +24890,20 @@
       <c r="C3" t="s">
         <v>490</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>487</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>30</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AU3" t="s">
         <v>488</v>
       </c>
-      <c r="AZ3">
+      <c r="BA3">
         <v>2000</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Canada lands survey</v>
@@ -24879,14 +24914,14 @@
       <c r="C4" t="s">
         <v>491</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>496</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>1879</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Certificate of Insurance (H0111)</v>
@@ -24897,11 +24932,11 @@
       <c r="C5" t="s">
         <v>492</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AW5" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Company search</v>
@@ -24912,11 +24947,11 @@
       <c r="C6" t="s">
         <v>493</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AW6" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Conveyance closing documents (ex: PTT forms, Form A transfer etc.)</v>
@@ -24927,11 +24962,11 @@
       <c r="C7" t="s">
         <v>494</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>1880</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Professional reports (ex: engineering/environmental etc.)</v>
@@ -24942,11 +24977,11 @@
       <c r="C8" t="s">
         <v>495</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="AW8" t="s">
         <v>1881</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Tax notices and assessments</v>
@@ -24957,11 +24992,11 @@
       <c r="C9" t="s">
         <v>489</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AW9" t="s">
         <v>1884</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Title search / Historical title</v>
@@ -24972,17 +25007,17 @@
       <c r="C10" t="s">
         <v>490</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AF10" t="s">
         <v>1882</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="AH10" t="s">
         <v>1883</v>
       </c>
-      <c r="AX10" t="s">
+      <c r="AY10" t="s">
         <v>1885</v>
       </c>
     </row>
-    <row r="11" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>1875</v>
       </c>
@@ -24992,17 +25027,20 @@
       <c r="C11" s="23" t="s">
         <v>492</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="D11" s="23" t="s">
+        <v>2434</v>
+      </c>
       <c r="I11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="AV11" s="23" t="s">
+      <c r="J11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="AW11" s="23" t="s">
         <v>1886</v>
       </c>
-      <c r="AW11" s="36"/>
-    </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AX11" s="36"/>
+    </row>
+    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f t="shared" ref="A12:A17" si="1">CONCATENATE("Research File - ",B12)</f>
         <v>Research File - Condition of entry (H0443)</v>
@@ -25013,11 +25051,11 @@
       <c r="C12" t="s">
         <v>493</v>
       </c>
-      <c r="AV12" t="s">
+      <c r="AW12" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f t="shared" si="1"/>
         <v>Research File - Crown grant</v>
@@ -25028,11 +25066,11 @@
       <c r="C13" t="s">
         <v>494</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f t="shared" si="1"/>
         <v>Research File - District road register</v>
@@ -25043,17 +25081,17 @@
       <c r="C14" t="s">
         <v>495</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>66</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>498</v>
       </c>
-      <c r="AS14" t="s">
+      <c r="AT14" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f t="shared" si="1"/>
         <v>Research File - Field notes</v>
@@ -25064,17 +25102,17 @@
       <c r="C15" t="s">
         <v>489</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>496</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>500</v>
       </c>
-      <c r="V15" t="s">
+      <c r="W15" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" si="1"/>
         <v>Research File - First nations consultation</v>
@@ -25085,11 +25123,11 @@
       <c r="C16" t="s">
         <v>490</v>
       </c>
-      <c r="AV16" t="s">
+      <c r="AW16" t="s">
         <v>1887</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" si="1"/>
         <v>Research File - Form 12</v>
@@ -25100,20 +25138,20 @@
       <c r="C17" t="s">
         <v>491</v>
       </c>
-      <c r="O17" s="13">
+      <c r="P17" s="13">
         <v>45245</v>
       </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>1888</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>1889</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AW17" t="s">
         <v>1890</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" ref="A18:A20" si="2">CONCATENATE("Research File - ",B18)</f>
         <v>Research File - Gazette</v>
@@ -25124,35 +25162,35 @@
       <c r="C18" t="s">
         <v>492</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>36509</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>1891</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>36778</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>1892</v>
       </c>
-      <c r="W18" s="9" t="s">
+      <c r="X18" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
         <v>1893</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>503</v>
       </c>
-      <c r="AO18" s="4"/>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
-      <c r="AS18" t="s">
+      <c r="AR18" s="4"/>
+      <c r="AT18" t="s">
         <v>1894</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" si="2"/>
         <v>Research File - Historical file</v>
@@ -25163,23 +25201,23 @@
       <c r="C19" t="s">
         <v>493</v>
       </c>
-      <c r="L19" s="13">
+      <c r="M19" s="13">
         <v>47045</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>1895</v>
       </c>
-      <c r="AF19" t="s">
+      <c r="AG19" t="s">
         <v>1896</v>
       </c>
-      <c r="AU19" t="s">
+      <c r="AV19" t="s">
         <v>1897</v>
       </c>
-      <c r="AW19" s="13">
+      <c r="AX19" s="13">
         <v>42988</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" si="2"/>
         <v>Research File - Lease / License agreement</v>
@@ -25190,11 +25228,11 @@
       <c r="C20" t="s">
         <v>495</v>
       </c>
-      <c r="AV20" t="s">
+      <c r="AW20" t="s">
         <v>1898</v>
       </c>
     </row>
-    <row r="21" spans="1:52" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>1873</v>
       </c>
@@ -25204,46 +25242,43 @@
       <c r="C21" s="23" t="s">
         <v>494</v>
       </c>
-      <c r="H21" s="36"/>
+      <c r="D21" s="23" t="s">
+        <v>2435</v>
+      </c>
       <c r="I21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="AV21" s="23" t="s">
+      <c r="J21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="AW21" s="23" t="s">
         <v>1899</v>
       </c>
-      <c r="AW21" s="36"/>
-    </row>
-    <row r="22" spans="1:52" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
+      <c r="AX21" s="36"/>
+    </row>
+    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>1234</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" t="s">
         <v>455</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" t="s">
         <v>495</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="G22" t="s">
         <v>1232</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="U22" s="23" t="s">
+      <c r="V22" t="s">
         <v>66</v>
       </c>
-      <c r="AT22" s="23" t="s">
+      <c r="AU22" t="s">
         <v>1233</v>
       </c>
-      <c r="AW22" s="36"/>
-      <c r="AZ22" s="23">
+      <c r="BA22">
         <v>1993</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>CONCATENATE("Acquisition File - ",B23)</f>
         <v>Acquisition File - Affidavit of service</v>
@@ -25254,11 +25289,11 @@
       <c r="C23" t="s">
         <v>489</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AW23" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>CONCATENATE("Acquisition File - ",B24)</f>
         <v>Acquisition File - Agricultural Land Commission (ALC)</v>
@@ -25269,14 +25304,14 @@
       <c r="C24" t="s">
         <v>490</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>1901</v>
       </c>
-      <c r="AV24" t="s">
+      <c r="AW24" t="s">
         <v>1902</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>CONCATENATE("Acquisition File - ",B25)</f>
         <v>Acquisition File - Form 5 - Approval of expropriation</v>
@@ -25287,11 +25322,11 @@
       <c r="C25" t="s">
         <v>491</v>
       </c>
-      <c r="AV25" t="s">
+      <c r="AW25" t="s">
         <v>1903</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>CONCATENATE("Acquisition File - ",B26)</f>
         <v>Acquisition File - Compensation cheque</v>
@@ -25302,11 +25337,11 @@
       <c r="C26" t="s">
         <v>492</v>
       </c>
-      <c r="AV26" t="s">
+      <c r="AW26" t="s">
         <v>1904</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f t="shared" ref="A27:A33" si="3">CONCATENATE("Acquisition File - ",B27)</f>
         <v>Acquisition File - Compensation requisition (H-120)</v>
@@ -25317,11 +25352,11 @@
       <c r="C27" t="s">
         <v>493</v>
       </c>
-      <c r="AV27" t="s">
+      <c r="AW27" t="s">
         <v>1905</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Land Act Tenure/Reserves</v>
@@ -25332,17 +25367,17 @@
       <c r="C28" t="s">
         <v>494</v>
       </c>
-      <c r="AP28" t="s">
+      <c r="AQ28" t="s">
         <v>1908</v>
       </c>
-      <c r="AQ28" t="s">
+      <c r="AR28" t="s">
         <v>1909</v>
       </c>
-      <c r="AV28" t="s">
+      <c r="AW28" t="s">
         <v>1910</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Legal correspondence (ex: to AG/external lawyers)</v>
@@ -25353,11 +25388,11 @@
       <c r="C29" t="s">
         <v>495</v>
       </c>
-      <c r="AV29" t="s">
+      <c r="AW29" t="s">
         <v>1911</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Legal survey plan</v>
@@ -25368,17 +25403,17 @@
       <c r="C30" t="s">
         <v>489</v>
       </c>
-      <c r="W30" t="s">
+      <c r="X30" t="s">
         <v>1912</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>1913</v>
       </c>
-      <c r="AI30" t="s">
+      <c r="AJ30" t="s">
         <v>1914</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - LTSA documents and plans (except title search)</v>
@@ -25389,11 +25424,11 @@
       <c r="C31" t="s">
         <v>490</v>
       </c>
-      <c r="AV31" t="s">
+      <c r="AW31" t="s">
         <v>1915</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Ministerial order</v>
@@ -25404,23 +25439,23 @@
       <c r="C32" t="s">
         <v>491</v>
       </c>
-      <c r="I32" s="13">
+      <c r="J32" s="13">
         <v>36850</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="Z32" t="s">
         <v>1916</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>1917</v>
       </c>
-      <c r="AN32" t="s">
+      <c r="AO32" t="s">
         <v>1918</v>
       </c>
-      <c r="AS32" t="s">
+      <c r="AT32" t="s">
         <v>1919</v>
       </c>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Form 7 - Notice of abandonement</v>
@@ -25431,11 +25466,11 @@
       <c r="C33" t="s">
         <v>492</v>
       </c>
-      <c r="AV33" t="s">
+      <c r="AW33" t="s">
         <v>1920</v>
       </c>
     </row>
-    <row r="34" spans="1:49" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>1876</v>
       </c>
@@ -25445,17 +25480,20 @@
       <c r="C34" s="23" t="s">
         <v>493</v>
       </c>
-      <c r="H34" s="36"/>
+      <c r="D34" s="23" t="s">
+        <v>2436</v>
+      </c>
       <c r="I34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="AV34" s="23" t="s">
+      <c r="J34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="AW34" s="23" t="s">
         <v>1921</v>
       </c>
-      <c r="AW34" s="36"/>
-    </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="AX34" s="36"/>
+    </row>
+    <row r="35" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f>_xlfn.CONCAT("Project -",B35)</f>
         <v>Project -Briefing notes</v>
@@ -25466,11 +25504,11 @@
       <c r="C35" t="s">
         <v>494</v>
       </c>
-      <c r="AV35" t="s">
+      <c r="AW35" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f t="shared" ref="A36:A43" si="4">_xlfn.CONCAT("Project -",B36)</f>
         <v>Project -Correspondence</v>
@@ -25481,23 +25519,23 @@
       <c r="C36" t="s">
         <v>495</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>752</v>
       </c>
-      <c r="H36" s="13">
+      <c r="I36" s="13">
         <v>46862</v>
       </c>
-      <c r="AE36" t="s">
+      <c r="AF36" t="s">
         <v>753</v>
       </c>
-      <c r="AN36" t="s">
+      <c r="AO36" t="s">
         <v>1922</v>
       </c>
-      <c r="AV36" t="s">
+      <c r="AW36" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f t="shared" si="4"/>
         <v>Project -Financial records (invoices, journal vouchers, received cheques etc.)</v>
@@ -25508,11 +25546,11 @@
       <c r="C37" t="s">
         <v>489</v>
       </c>
-      <c r="AV37" t="s">
+      <c r="AW37" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" si="4"/>
         <v>Project -MoTI plan</v>
@@ -25523,26 +25561,26 @@
       <c r="C38" t="s">
         <v>490</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>756</v>
       </c>
-      <c r="W38" t="s">
+      <c r="X38" t="s">
         <v>1923</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AA38" t="s">
         <v>1924</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>1925</v>
       </c>
-      <c r="AO38" s="13">
+      <c r="AP38" s="13">
         <v>43757</v>
       </c>
-      <c r="AR38" t="s">
+      <c r="AS38" t="s">
         <v>1926</v>
       </c>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f t="shared" si="4"/>
         <v>Project -Other</v>
@@ -25553,17 +25591,17 @@
       <c r="C39" t="s">
         <v>491</v>
       </c>
-      <c r="AH39">
+      <c r="AI39">
         <v>7190089</v>
       </c>
-      <c r="AN39" t="s">
+      <c r="AO39" t="s">
         <v>1927</v>
       </c>
-      <c r="AV39" t="s">
+      <c r="AW39" t="s">
         <v>1928</v>
       </c>
     </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f t="shared" si="4"/>
         <v>Project -PA plans / Design drawings</v>
@@ -25574,26 +25612,26 @@
       <c r="C40" t="s">
         <v>492</v>
       </c>
-      <c r="W40">
+      <c r="X40">
         <v>2347987</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AB40" t="s">
         <v>757</v>
       </c>
-      <c r="AI40" t="s">
+      <c r="AJ40" t="s">
         <v>1929</v>
       </c>
-      <c r="AJ40" t="s">
+      <c r="AK40" t="s">
         <v>1930</v>
       </c>
-      <c r="AL40" t="s">
+      <c r="AM40" t="s">
         <v>1931</v>
       </c>
-      <c r="AM40" t="s">
+      <c r="AN40" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f t="shared" si="4"/>
         <v>Project -Photos / Images / Video</v>
@@ -25604,35 +25642,35 @@
       <c r="C41" t="s">
         <v>493</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>1933</v>
       </c>
-      <c r="H41" s="13">
+      <c r="I41" s="13">
         <v>32301</v>
       </c>
-      <c r="W41" t="s">
+      <c r="X41" t="s">
         <v>758</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="AA41" t="s">
         <v>759</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AB41" t="s">
         <v>760</v>
       </c>
-      <c r="AE41" t="s">
+      <c r="AF41" t="s">
         <v>1934</v>
       </c>
-      <c r="AN41" t="s">
+      <c r="AO41" t="s">
         <v>1935</v>
       </c>
-      <c r="AO41" s="4"/>
       <c r="AP41" s="4"/>
       <c r="AQ41" s="4"/>
-      <c r="AV41" t="s">
+      <c r="AR41" s="4"/>
+      <c r="AW41" t="s">
         <v>1936</v>
       </c>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f t="shared" si="4"/>
         <v>Project -Spending authority approval (SAA)</v>
@@ -25643,11 +25681,11 @@
       <c r="C42" t="s">
         <v>494</v>
       </c>
-      <c r="AV42" t="s">
+      <c r="AW42" t="s">
         <v>1937</v>
       </c>
     </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f t="shared" si="4"/>
         <v>Project -Surplus property declaration</v>
@@ -25658,11 +25696,11 @@
       <c r="C43" t="s">
         <v>495</v>
       </c>
-      <c r="AV43" t="s">
+      <c r="AW43" t="s">
         <v>1938</v>
       </c>
     </row>
-    <row r="44" spans="1:49" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
         <v>1874</v>
       </c>
@@ -25672,17 +25710,20 @@
       <c r="C44" s="23" t="s">
         <v>489</v>
       </c>
-      <c r="H44" s="36"/>
+      <c r="D44" s="23" t="s">
+        <v>2437</v>
+      </c>
       <c r="I44" s="36"/>
-      <c r="L44" s="36"/>
-      <c r="O44" s="36"/>
-      <c r="Q44" s="36"/>
-      <c r="AV44" s="23" t="s">
+      <c r="J44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="AW44" s="23" t="s">
         <v>1144</v>
       </c>
-      <c r="AW44" s="36"/>
-    </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="AX44" s="36"/>
+    </row>
+    <row r="45" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f>_xlfn.CONCAT("Disposition File -",B45)</f>
         <v>Disposition File -Certificate of Compliance</v>
@@ -25693,11 +25734,11 @@
       <c r="C45" t="s">
         <v>490</v>
       </c>
-      <c r="AV45" t="s">
+      <c r="AW45" t="s">
         <v>1273</v>
       </c>
     </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" ref="A46:A53" si="5">_xlfn.CONCAT("Disposition File -",B46)</f>
         <v>Disposition File -Enhanced Referral Records</v>
@@ -25708,11 +25749,11 @@
       <c r="C46" t="s">
         <v>491</v>
       </c>
-      <c r="AV46" t="s">
+      <c r="AW46" t="s">
         <v>1939</v>
       </c>
     </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -First Nations Strength of Claim Report</v>
@@ -25723,11 +25764,11 @@
       <c r="C47" t="s">
         <v>492</v>
       </c>
-      <c r="AV47" t="s">
+      <c r="AW47" t="s">
         <v>1940</v>
       </c>
     </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Miscellaneous notes (LTSA)</v>
@@ -25738,11 +25779,11 @@
       <c r="C48" t="s">
         <v>493</v>
       </c>
-      <c r="AG48" t="s">
+      <c r="AH48" t="s">
         <v>1941</v>
       </c>
     </row>
-    <row r="49" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Notice of claims/Litigation documents</v>
@@ -25753,11 +25794,11 @@
       <c r="C49" t="s">
         <v>494</v>
       </c>
-      <c r="AV49" t="s">
+      <c r="AW49" t="s">
         <v>1942</v>
       </c>
     </row>
-    <row r="50" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Order in Council (OIC)</v>
@@ -25768,23 +25809,23 @@
       <c r="C50" t="s">
         <v>495</v>
       </c>
-      <c r="AB50">
+      <c r="AC50">
         <v>89997</v>
       </c>
-      <c r="AC50" t="s">
+      <c r="AD50" t="s">
         <v>1943</v>
       </c>
-      <c r="AD50" t="s">
+      <c r="AE50" t="s">
         <v>1944</v>
       </c>
-      <c r="AS50" t="s">
+      <c r="AT50" t="s">
         <v>1945</v>
       </c>
-      <c r="AZ50">
+      <c r="BA50">
         <v>1997</v>
       </c>
     </row>
-    <row r="51" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Purchase and Sale Agreement</v>
@@ -25795,11 +25836,11 @@
       <c r="C51" t="s">
         <v>489</v>
       </c>
-      <c r="AV51" t="s">
+      <c r="AW51" t="s">
         <v>1946</v>
       </c>
     </row>
-    <row r="52" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Record of negotiation</v>
@@ -25810,11 +25851,11 @@
       <c r="C52" t="s">
         <v>490</v>
       </c>
-      <c r="AV52" t="s">
+      <c r="AW52" t="s">
         <v>1947</v>
       </c>
     </row>
-    <row r="53" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Release of claims</v>
@@ -25825,11 +25866,11 @@
       <c r="C53" t="s">
         <v>491</v>
       </c>
-      <c r="AV53" t="s">
+      <c r="AW53" t="s">
         <v>1948</v>
       </c>
     </row>
-    <row r="54" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>1877</v>
       </c>
@@ -25839,25 +25880,28 @@
       <c r="C54" s="23" t="s">
         <v>492</v>
       </c>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36">
+      <c r="D54" s="23" t="s">
+        <v>2438</v>
+      </c>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36">
         <v>36800</v>
       </c>
-      <c r="L54" s="36"/>
-      <c r="O54" s="36"/>
-      <c r="Q54" s="36"/>
-      <c r="Z54" s="23" t="s">
+      <c r="M54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="R54" s="36"/>
+      <c r="AA54" s="23" t="s">
         <v>1949</v>
       </c>
-      <c r="AS54" s="23" t="s">
+      <c r="AT54" s="23" t="s">
         <v>1950</v>
       </c>
-      <c r="AW54" s="36"/>
-      <c r="AY54" s="23" t="s">
+      <c r="AX54" s="36"/>
+      <c r="AZ54" s="23" t="s">
         <v>1951</v>
       </c>
     </row>
-    <row r="55" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f>_xlfn.CONCAT("Property Management -",B55)</f>
         <v>Property Management -Approval/sign-off</v>
@@ -25868,11 +25912,11 @@
       <c r="C55" t="s">
         <v>493</v>
       </c>
-      <c r="AV55" t="s">
+      <c r="AW55" t="s">
         <v>1952</v>
       </c>
     </row>
-    <row r="56" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f t="shared" ref="A56:A64" si="6">_xlfn.CONCAT("Property Management -",B56)</f>
         <v>Property Management -Form 8 - Notice of advanced payment </v>
@@ -25883,11 +25927,11 @@
       <c r="C56" t="s">
         <v>494</v>
       </c>
-      <c r="AV56" t="s">
+      <c r="AW56" t="s">
         <v>1963</v>
       </c>
     </row>
-    <row r="57" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Form 1 - Notice of expropriation </v>
@@ -25898,11 +25942,11 @@
       <c r="C57" t="s">
         <v>495</v>
       </c>
-      <c r="AV57" t="s">
+      <c r="AW57" t="s">
         <v>1962</v>
       </c>
     </row>
-    <row r="58" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Notice of possible entry (H0224)</v>
@@ -25913,11 +25957,11 @@
       <c r="C58" t="s">
         <v>489</v>
       </c>
-      <c r="AV58" t="s">
+      <c r="AW58" t="s">
         <v>1953</v>
       </c>
     </row>
-    <row r="59" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Other Land Agreement (Indemnity Letter, Letter of Intended Use, Assumption Agreement, etc)</v>
@@ -25928,11 +25972,11 @@
       <c r="C59" t="s">
         <v>490</v>
       </c>
-      <c r="AV59" t="s">
+      <c r="AW59" t="s">
         <v>1954</v>
       </c>
     </row>
-    <row r="60" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Owner agreement/offer</v>
@@ -25943,11 +25987,11 @@
       <c r="C60" t="s">
         <v>491</v>
       </c>
-      <c r="AV60" t="s">
+      <c r="AW60" t="s">
         <v>1961</v>
       </c>
     </row>
-    <row r="61" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Privy council</v>
@@ -25958,11 +26002,11 @@
       <c r="C61" t="s">
         <v>492</v>
       </c>
-      <c r="BA61">
+      <c r="BB61">
         <v>1979</v>
       </c>
     </row>
-    <row r="62" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Temporary license for construction access (H0074)</v>
@@ -25973,11 +26017,11 @@
       <c r="C62" t="s">
         <v>493</v>
       </c>
-      <c r="AV62" t="s">
+      <c r="AW62" t="s">
         <v>1960</v>
       </c>
     </row>
-    <row r="63" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Transfer of administration</v>
@@ -25988,23 +26032,23 @@
       <c r="C63" t="s">
         <v>494</v>
       </c>
-      <c r="I63" s="13">
+      <c r="J63" s="13">
         <v>32874</v>
       </c>
-      <c r="Z63" t="s">
+      <c r="AA63" t="s">
         <v>1955</v>
       </c>
-      <c r="AN63" t="s">
+      <c r="AO63" t="s">
         <v>1956</v>
       </c>
-      <c r="AS63" t="s">
+      <c r="AT63" t="s">
         <v>1380</v>
       </c>
-      <c r="AY63" t="s">
+      <c r="AZ63" t="s">
         <v>1957</v>
       </c>
     </row>
-    <row r="64" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Form 9 - Vesting notice (Form 9)</v>
@@ -26015,11 +26059,11 @@
       <c r="C64" t="s">
         <v>495</v>
       </c>
-      <c r="AV64" t="s">
+      <c r="AW64" t="s">
         <v>1959</v>
       </c>
     </row>
-    <row r="65" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>1878</v>
       </c>
@@ -26029,17 +26073,20 @@
       <c r="C65" s="23" t="s">
         <v>489</v>
       </c>
-      <c r="H65" s="36"/>
+      <c r="D65" s="23" t="s">
+        <v>2439</v>
+      </c>
       <c r="I65" s="36"/>
-      <c r="L65" s="36"/>
-      <c r="O65" s="36"/>
-      <c r="Q65" s="36"/>
-      <c r="AV65" s="23" t="s">
+      <c r="J65" s="36"/>
+      <c r="M65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="R65" s="36"/>
+      <c r="AW65" s="23" t="s">
         <v>1958</v>
       </c>
-      <c r="AW65" s="36"/>
-    </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AX65" s="36"/>
+    </row>
+    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <f>_xlfn.CONCAT("Management File -",B66)</f>
         <v>Management File -Certificate of Compliance</v>
@@ -26050,11 +26097,11 @@
       <c r="C66" t="s">
         <v>490</v>
       </c>
-      <c r="AV66" t="s">
+      <c r="AW66" t="s">
         <v>2243</v>
       </c>
     </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A70" si="7">_xlfn.CONCAT("Management File -",B67)</f>
         <v>Management File -Company search</v>
@@ -26065,11 +26112,11 @@
       <c r="C67" t="s">
         <v>491</v>
       </c>
-      <c r="AV67" t="s">
+      <c r="AW67" t="s">
         <v>2244</v>
       </c>
     </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f>_xlfn.CONCAT("Management File -",B68)</f>
         <v>Management File -Correspondence</v>
@@ -26080,23 +26127,23 @@
       <c r="C68" t="s">
         <v>494</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>2250</v>
       </c>
-      <c r="H68" s="13">
+      <c r="I68" s="13">
         <v>32928</v>
       </c>
-      <c r="AE68" t="s">
+      <c r="AF68" t="s">
         <v>2255</v>
       </c>
-      <c r="AN68" t="s">
+      <c r="AO68" t="s">
         <v>2256</v>
       </c>
-      <c r="AV68" t="s">
+      <c r="AW68" t="s">
         <v>2258</v>
       </c>
     </row>
-    <row r="69" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f t="shared" si="7"/>
         <v>Management File -District road register</v>
@@ -26107,17 +26154,17 @@
       <c r="C69" t="s">
         <v>492</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>30</v>
       </c>
-      <c r="S69" t="s">
+      <c r="T69" t="s">
         <v>2245</v>
       </c>
-      <c r="AS69" t="s">
+      <c r="AT69" t="s">
         <v>2246</v>
       </c>
     </row>
-    <row r="70" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f t="shared" si="7"/>
         <v>Management File -Field notes</v>
@@ -26128,17 +26175,17 @@
       <c r="C70" t="s">
         <v>493</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>2247</v>
       </c>
-      <c r="M70" t="s">
+      <c r="N70" t="s">
         <v>2248</v>
       </c>
-      <c r="V70" t="s">
+      <c r="W70" t="s">
         <v>2249</v>
       </c>
     </row>
-    <row r="71" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>2242</v>
       </c>
@@ -26148,32 +26195,35 @@
       <c r="C71" s="23" t="s">
         <v>495</v>
       </c>
-      <c r="H71" s="36"/>
+      <c r="D71" s="23" t="s">
+        <v>2440</v>
+      </c>
       <c r="I71" s="36"/>
-      <c r="L71" s="36"/>
-      <c r="N71" s="23" t="s">
+      <c r="J71" s="36"/>
+      <c r="M71" s="36"/>
+      <c r="O71" s="23" t="s">
         <v>2251</v>
       </c>
-      <c r="O71" s="36"/>
-      <c r="Q71" s="36"/>
-      <c r="W71" s="23" t="s">
+      <c r="P71" s="36"/>
+      <c r="R71" s="36"/>
+      <c r="X71" s="23" t="s">
         <v>2252</v>
       </c>
-      <c r="Z71" s="23" t="s">
+      <c r="AA71" s="23" t="s">
         <v>2253</v>
       </c>
-      <c r="AA71" s="23" t="s">
+      <c r="AB71" s="23" t="s">
         <v>2254</v>
       </c>
-      <c r="AO71" s="36">
+      <c r="AP71" s="36">
         <v>45616</v>
       </c>
-      <c r="AR71" s="23" t="s">
+      <c r="AS71" s="23" t="s">
         <v>2257</v>
       </c>
-      <c r="AW71" s="36"/>
-    </row>
-    <row r="72" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AX71" s="36"/>
+    </row>
+    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>2346</v>
       </c>
@@ -26183,11 +26233,11 @@
       <c r="C72" t="s">
         <v>489</v>
       </c>
-      <c r="AV72" t="s">
+      <c r="AW72" t="s">
         <v>2349</v>
       </c>
     </row>
-    <row r="73" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>2347</v>
       </c>
@@ -26197,20 +26247,20 @@
       <c r="C73" t="s">
         <v>490</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>2350</v>
       </c>
-      <c r="U73" t="s">
+      <c r="V73" t="s">
         <v>2245</v>
       </c>
-      <c r="AT73" t="s">
+      <c r="AU73" t="s">
         <v>2351</v>
       </c>
-      <c r="BA73">
+      <c r="BB73">
         <v>2025</v>
       </c>
     </row>
-    <row r="74" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>2348</v>
       </c>
@@ -26220,15 +26270,15 @@
       <c r="C74" t="s">
         <v>491</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>2352</v>
       </c>
-      <c r="T74" t="s">
+      <c r="U74" t="s">
         <v>2353</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BA71" xr:uid="{2665AEC9-C942-4A65-984C-CAD52F4E2CCE}"/>
+  <autoFilter ref="A1:BB71" xr:uid="{2665AEC9-C942-4A65-984C-CAD52F4E2CCE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9842984-1CC4-44F6-AE3B-C9565752CB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76CFF24A-761C-4CF9-BD8F-7FFB1C75A529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4418" uniqueCount="2442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4417" uniqueCount="2441">
   <si>
     <t>FirstName</t>
   </si>
@@ -4756,9 +4756,6 @@
   </si>
   <si>
     <t>LeaseCancellationReason</t>
-  </si>
-  <si>
-    <t>Create lease with cancelled status.</t>
   </si>
   <si>
     <t>LeaseTerminationReason</t>
@@ -7933,7 +7930,7 @@
         <v>165</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -7975,7 +7972,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -8101,7 +8098,7 @@
         <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -8140,7 +8137,7 @@
         <v>3</v>
       </c>
       <c r="O6" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -8217,13 +8214,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C9" t="s">
         <v>2160</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2162</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2161</v>
       </c>
       <c r="D9" t="str">
         <f>CONCATENATE(C9," ",B9)</f>
@@ -8236,16 +8233,16 @@
         <v>191</v>
       </c>
       <c r="G9" t="s">
+        <v>2162</v>
+      </c>
+      <c r="H9" t="s">
         <v>2163</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>2164</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>2165</v>
-      </c>
-      <c r="J9" t="s">
-        <v>2166</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>197</v>
@@ -8291,99 +8288,99 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2028</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2029</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2030</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>2031</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2032</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>2033</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>2034</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>2035</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>2036</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>2037</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>2038</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>2039</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>2040</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>2041</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>2042</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>2043</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>2044</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>2045</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>2046</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>2047</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>2048</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>2050</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>2051</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>2052</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>2053</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>2054</v>
       </c>
-      <c r="AC1" s="3" t="s">
-        <v>2055</v>
-      </c>
       <c r="AD1" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="AE1" s="3" t="s">
         <v>1626</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>1627</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B2" t="s">
         <v>790</v>
@@ -8478,7 +8475,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B3" t="s">
         <v>791</v>
@@ -8601,7 +8598,7 @@
         <v>167</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>587</v>
@@ -8609,24 +8606,24 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="s">
         <v>598</v>
       </c>
       <c r="E2" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B3" t="s">
         <v>588</v>
@@ -8643,7 +8640,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -8660,7 +8657,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -8672,7 +8669,7 @@
         <v>595</v>
       </c>
       <c r="E5" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -8711,7 +8708,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B8" t="s">
         <v>588</v>
@@ -8723,12 +8720,12 @@
         <v>590</v>
       </c>
       <c r="E8" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -8745,7 +8742,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -8762,7 +8759,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -8779,7 +8776,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B12" t="s">
         <v>588</v>
@@ -8796,7 +8793,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B13" t="s">
         <v>588</v>
@@ -9074,67 +9071,67 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1716</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>1717</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>1718</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>1719</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>1720</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1721</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>1722</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>1724</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>1723</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>1748</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>1749</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>1725</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>1726</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>1727</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>1750</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="U1" s="3" t="s">
         <v>1751</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>1728</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>1729</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>1730</v>
-      </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>1752</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -9142,10 +9139,10 @@
         <v>555</v>
       </c>
       <c r="B2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C2" t="s">
         <v>1738</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1739</v>
       </c>
       <c r="D2" s="4">
         <v>44614</v>
@@ -9166,7 +9163,7 @@
         <v>2500</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="K2" s="17">
         <f>I2*0.05</f>
@@ -9183,7 +9180,7 @@
         <v>1500.5</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P2" s="16"/>
       <c r="Q2" s="17">
@@ -9197,7 +9194,7 @@
         <v>200.79</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="U2" s="6">
         <v>10.029999999999999</v>
@@ -9211,10 +9208,10 @@
         <v>555</v>
       </c>
       <c r="B3" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="C3" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="D3" s="4">
         <v>44704</v>
@@ -9235,7 +9232,7 @@
         <v>3500</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17">
@@ -9243,13 +9240,13 @@
         <v>3500</v>
       </c>
       <c r="M3" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="N3" s="6">
         <v>1500.99</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17">
@@ -9258,7 +9255,7 @@
       </c>
       <c r="S3" s="6"/>
       <c r="T3" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
@@ -9268,10 +9265,10 @@
         <v>555</v>
       </c>
       <c r="B4" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="C4" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="D4" s="4">
         <v>44744</v>
@@ -9292,7 +9289,7 @@
         <v>3000</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="K4" s="17"/>
       <c r="L4" s="17">
@@ -9301,13 +9298,13 @@
       </c>
       <c r="N4" s="6"/>
       <c r="O4" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17"/>
       <c r="S4" s="6"/>
       <c r="T4" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -9317,10 +9314,10 @@
         <v>555</v>
       </c>
       <c r="B5" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="C5" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="D5" s="4">
         <v>45119</v>
@@ -9341,7 +9338,7 @@
         <v>120000</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="K5" s="17">
         <f t="shared" ref="K5" si="2">I5*0.05</f>
@@ -9353,13 +9350,13 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17"/>
       <c r="S5" s="6"/>
       <c r="T5" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -9369,10 +9366,10 @@
         <v>629</v>
       </c>
       <c r="B6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C6" t="s">
         <v>1738</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1739</v>
       </c>
       <c r="D6" s="4">
         <v>44614</v>
@@ -9393,7 +9390,7 @@
         <v>3000</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17">
@@ -9407,7 +9404,7 @@
         <v>150.78</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="P6" s="16">
         <v>8</v>
@@ -9423,7 +9420,7 @@
         <v>1000</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="U6" s="6">
         <v>20</v>
@@ -9468,7 +9465,7 @@
         <v>633</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>634</v>
@@ -9477,7 +9474,7 @@
         <v>635</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>622</v>
@@ -9486,10 +9483,10 @@
         <v>636</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>1734</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -9503,7 +9500,7 @@
         <v>638</v>
       </c>
       <c r="D2" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E2" s="6">
         <v>1500.5</v>
@@ -9524,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -9538,7 +9535,7 @@
         <v>640</v>
       </c>
       <c r="D3" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E3" s="6">
         <v>200.79</v>
@@ -9559,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -9573,7 +9570,7 @@
         <v>643</v>
       </c>
       <c r="D4" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E4" s="6">
         <v>3000</v>
@@ -9594,7 +9591,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -9608,7 +9605,7 @@
         <v>644</v>
       </c>
       <c r="D5" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="E5" s="6">
         <v>13</v>
@@ -9629,7 +9626,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -9643,7 +9640,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="E6" s="6">
         <v>126000</v>
@@ -9664,7 +9661,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -9678,7 +9675,7 @@
         <v>657</v>
       </c>
       <c r="D7" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E7" s="6">
         <v>3000</v>
@@ -9699,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
   </sheetData>
@@ -9803,7 +9800,7 @@
         <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="F2" t="s">
         <v>248</v>
@@ -9812,7 +9809,7 @@
         <v>249</v>
       </c>
       <c r="H2" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="I2" s="4">
         <v>44625</v>
@@ -9859,7 +9856,7 @@
         <v>246</v>
       </c>
       <c r="D3" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="I3" s="4"/>
       <c r="M3" s="4"/>
@@ -9912,13 +9909,13 @@
         <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="G5" t="s">
         <v>254</v>
       </c>
       <c r="H5" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="L5" t="s">
         <v>255</v>
@@ -9953,7 +9950,7 @@
         <v>246</v>
       </c>
       <c r="D6" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="M6" s="4"/>
       <c r="O6" t="b">
@@ -10178,7 +10175,7 @@
         <v>289</v>
       </c>
       <c r="C2" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="D2" t="s">
         <v>264</v>
@@ -10201,7 +10198,7 @@
         <v>290</v>
       </c>
       <c r="C3" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="D3" t="s">
         <v>266</v>
@@ -10339,7 +10336,7 @@
         <v>1228</v>
       </c>
       <c r="C9" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="D9" t="s">
         <v>266</v>
@@ -10356,7 +10353,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
   </sheetData>
@@ -10449,31 +10446,31 @@
         <v>704</v>
       </c>
       <c r="I1" s="38" t="s">
+        <v>1969</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>1970</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="K1" s="38" t="s">
         <v>1971</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="L1" s="38" t="s">
         <v>1972</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="M1" s="38" t="s">
         <v>1973</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="N1" s="38" t="s">
         <v>1974</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="O1" s="38" t="s">
         <v>1975</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="P1" s="38" t="s">
         <v>1976</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="Q1" s="38" t="s">
         <v>1977</v>
-      </c>
-      <c r="Q1" s="38" t="s">
-        <v>1978</v>
       </c>
       <c r="R1" s="38" t="s">
         <v>665</v>
@@ -10485,16 +10482,16 @@
         <v>667</v>
       </c>
       <c r="U1" s="38" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="V1" s="38" t="s">
         <v>668</v>
       </c>
       <c r="W1" s="38" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="X1" s="38" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="Y1" s="38" t="s">
         <v>766</v>
@@ -10548,34 +10545,34 @@
         <v>827</v>
       </c>
       <c r="AP1" s="38" t="s">
+        <v>1779</v>
+      </c>
+      <c r="AQ1" s="38" t="s">
         <v>1780</v>
       </c>
-      <c r="AQ1" s="38" t="s">
+      <c r="AR1" s="38" t="s">
         <v>1781</v>
       </c>
-      <c r="AR1" s="38" t="s">
-        <v>1782</v>
-      </c>
       <c r="AS1" s="38" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="AT1" s="38" t="s">
+        <v>2005</v>
+      </c>
+      <c r="AU1" s="38" t="s">
         <v>2006</v>
       </c>
-      <c r="AU1" s="38" t="s">
-        <v>2007</v>
-      </c>
       <c r="AV1" s="38" t="s">
+        <v>2269</v>
+      </c>
+      <c r="AW1" s="38" t="s">
         <v>2270</v>
       </c>
-      <c r="AW1" s="38" t="s">
+      <c r="AX1" s="38" t="s">
         <v>2271</v>
       </c>
-      <c r="AX1" s="38" t="s">
+      <c r="AY1" s="38" t="s">
         <v>2272</v>
-      </c>
-      <c r="AY1" s="38" t="s">
-        <v>2273</v>
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.3">
@@ -10601,19 +10598,19 @@
         <v>677</v>
       </c>
       <c r="I2" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="J2" t="s">
         <v>561</v>
       </c>
       <c r="K2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M2" t="s">
         <v>1979</v>
-      </c>
-      <c r="L2" t="s">
-        <v>2141</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1980</v>
       </c>
       <c r="N2" s="4">
         <v>45170</v>
@@ -10637,7 +10634,7 @@
         <v>246</v>
       </c>
       <c r="U2" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="V2" t="s">
         <v>679</v>
@@ -10658,7 +10655,7 @@
         <v>2</v>
       </c>
       <c r="AD2" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="AE2" t="s">
         <v>1313</v>
@@ -10729,35 +10726,35 @@
         <v>5500202</v>
       </c>
       <c r="D3" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E3" s="18">
         <v>550020201</v>
       </c>
       <c r="F3" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="G3" t="s">
         <v>890</v>
       </c>
       <c r="I3" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J3" t="s">
         <v>1981</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>1982</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>1983</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>1984</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1985</v>
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45995</v>
+        <v>46042</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10775,7 +10772,7 @@
         <v>676</v>
       </c>
       <c r="U3" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="V3" t="s">
         <v>724</v>
@@ -10911,7 +10908,7 @@
         <v>2</v>
       </c>
       <c r="AD4" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="AE4" t="s">
         <v>1434</v>
@@ -10995,7 +10992,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>45995</v>
+        <v>46042</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11207,20 +11204,20 @@
         <v>5500202</v>
       </c>
       <c r="D7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E7" s="18">
         <v>550020201</v>
       </c>
       <c r="F7" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="G7" t="s">
         <v>890</v>
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>45995</v>
+        <v>46042</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11479,7 +11476,7 @@
         <v>2</v>
       </c>
       <c r="AD9" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="AE9" t="s">
         <v>250</v>
@@ -11780,20 +11777,20 @@
         <v>5500202</v>
       </c>
       <c r="D12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E12" s="18">
         <v>550020201</v>
       </c>
       <c r="F12" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="G12" t="s">
         <v>890</v>
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>45995</v>
+        <v>46042</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -11822,7 +11819,7 @@
         <v>1</v>
       </c>
       <c r="AD12" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="AE12" t="s">
         <v>1312</v>
@@ -12123,20 +12120,20 @@
         <v>5500202</v>
       </c>
       <c r="D15" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E15" s="18">
         <v>550020201</v>
       </c>
       <c r="F15" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="G15" t="s">
         <v>890</v>
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>45995</v>
+        <v>46042</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -12482,13 +12479,13 @@
         <v>5500202</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E19" s="51">
         <v>550020201</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="G19" s="46" t="s">
         <v>1251</v>
@@ -12572,7 +12569,7 @@
       </c>
       <c r="C20" s="44"/>
       <c r="R20" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="V20" t="s">
         <v>679</v>
@@ -12813,7 +12810,7 @@
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B23" t="s">
         <v>246</v>
@@ -12837,7 +12834,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="V23" t="s">
         <v>724</v>
@@ -12914,7 +12911,7 @@
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B24" t="s">
         <v>246</v>
@@ -12935,19 +12932,19 @@
         <v>1251</v>
       </c>
       <c r="I24" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="J24" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="K24" t="s">
         <v>561</v>
       </c>
       <c r="L24" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="M24" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="N24" s="4">
         <v>45036</v>
@@ -12962,10 +12959,10 @@
         <v>45829</v>
       </c>
       <c r="R24" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="S24" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="T24" t="s">
         <v>723</v>
@@ -12974,7 +12971,7 @@
         <v>724</v>
       </c>
       <c r="W24" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="Y24" t="s">
         <v>191</v>
@@ -12995,13 +12992,13 @@
         <v>686</v>
       </c>
       <c r="AE24" t="s">
+        <v>1988</v>
+      </c>
+      <c r="AF24" t="s">
         <v>1989</v>
       </c>
-      <c r="AF24" t="s">
+      <c r="AG24" t="s">
         <v>1990</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>1991</v>
       </c>
       <c r="AH24">
         <v>16</v>
@@ -13058,7 +13055,7 @@
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B25" t="s">
         <v>246</v>
@@ -13076,22 +13073,22 @@
         <v>855</v>
       </c>
       <c r="G25" t="s">
+        <v>1997</v>
+      </c>
+      <c r="I25" t="s">
         <v>1998</v>
-      </c>
-      <c r="I25" t="s">
-        <v>1999</v>
       </c>
       <c r="J25" t="s">
         <v>561</v>
       </c>
       <c r="K25" t="s">
+        <v>1982</v>
+      </c>
+      <c r="L25" t="s">
         <v>1983</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>1984</v>
-      </c>
-      <c r="M25" t="s">
-        <v>1985</v>
       </c>
       <c r="N25" s="4">
         <v>45432</v>
@@ -13106,13 +13103,13 @@
         <v>45737</v>
       </c>
       <c r="R25" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="W25" t="s">
         <v>7</v>
       </c>
       <c r="X25" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="Y25" t="s">
         <v>192</v>
@@ -13595,142 +13592,142 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2056</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2057</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2058</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>2059</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2060</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>2061</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>2062</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>2063</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>2064</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>2065</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>2066</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>2067</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>2068</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>2069</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>2070</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>2071</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>2072</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>2073</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>2074</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>2075</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>2076</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>2077</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>2078</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>2079</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>2080</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>2081</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>2082</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>2083</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>2084</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>2085</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>2086</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>2087</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>2088</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>2089</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>2090</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>2091</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>2092</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>2093</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>2094</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>2095</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>2096</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>2097</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>2098</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>2099</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>2100</v>
-      </c>
-      <c r="AU1" s="3" t="s">
-        <v>2101</v>
       </c>
       <c r="AV1" s="3" t="s">
         <v>788</v>
@@ -14883,7 +14880,7 @@
         <v>829</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>830</v>
@@ -15333,10 +15330,10 @@
         <v>45241</v>
       </c>
       <c r="K2" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="L2" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M2" t="s">
         <v>884</v>
@@ -15348,10 +15345,10 @@
         <v>886</v>
       </c>
       <c r="P2" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="Q2" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -15389,10 +15386,10 @@
         <v>1002</v>
       </c>
       <c r="P3" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="Q3" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -15439,7 +15436,7 @@
         <v>1250</v>
       </c>
       <c r="L4" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M4" t="s">
         <v>884</v>
@@ -15451,10 +15448,10 @@
         <v>886</v>
       </c>
       <c r="P4" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="Q4" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -15474,7 +15471,7 @@
     </row>
     <row r="5" spans="1:22" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B5" s="39">
         <v>56700.89</v>
@@ -15489,28 +15486,28 @@
         <v>490</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="G5" s="27">
         <v>45569</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="N5" s="23" t="s">
         <v>885</v>
       </c>
       <c r="O5" s="23" t="s">
+        <v>1796</v>
+      </c>
+      <c r="P5" s="23" t="s">
         <v>1797</v>
-      </c>
-      <c r="P5" s="23" t="s">
-        <v>1798</v>
       </c>
       <c r="Q5" s="23" t="s">
         <v>786</v>
@@ -15522,7 +15519,7 @@
         <v>1379</v>
       </c>
       <c r="T5" s="23" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="U5" s="23">
         <v>6</v>
@@ -15533,7 +15530,7 @@
     </row>
     <row r="6" spans="1:22" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -15551,10 +15548,10 @@
         <v>1002</v>
       </c>
       <c r="P6" s="23" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="R6" s="23" t="b">
         <v>1</v>
@@ -15568,7 +15565,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B7" s="37">
         <v>56789.98</v>
@@ -15598,10 +15595,10 @@
         <v>45241</v>
       </c>
       <c r="K7" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="L7" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M7" t="s">
         <v>884</v>
@@ -15613,10 +15610,10 @@
         <v>886</v>
       </c>
       <c r="P7" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="Q7" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -15636,7 +15633,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B8" s="37">
         <v>10000</v>
@@ -15655,34 +15652,34 @@
         <v>44845</v>
       </c>
       <c r="K8" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="L8" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M8" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="N8" t="s">
+        <v>2010</v>
+      </c>
+      <c r="O8" t="s">
         <v>2011</v>
       </c>
-      <c r="O8" t="s">
-        <v>2012</v>
-      </c>
       <c r="P8" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="Q8" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
       </c>
       <c r="S8" t="s">
+        <v>2012</v>
+      </c>
+      <c r="T8" t="s">
         <v>2013</v>
-      </c>
-      <c r="T8" t="s">
-        <v>2014</v>
       </c>
       <c r="U8">
         <v>11</v>
@@ -15693,7 +15690,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B9" s="37">
         <v>2000</v>
@@ -15709,22 +15706,22 @@
         <v>45650</v>
       </c>
       <c r="K9" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="L9" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M9" t="s">
+        <v>2016</v>
+      </c>
+      <c r="N9" t="s">
         <v>2017</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>2018</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>2019</v>
-      </c>
-      <c r="P9" t="s">
-        <v>2020</v>
       </c>
       <c r="Q9" t="s">
         <v>834</v>
@@ -15733,10 +15730,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="T9" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="U9">
         <v>12</v>
@@ -15747,35 +15744,35 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="B10" s="37"/>
       <c r="E10" t="s">
         <v>490</v>
       </c>
       <c r="F10" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="G10" s="4">
         <v>45569</v>
       </c>
       <c r="K10" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="L10" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M10" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="N10" t="s">
         <v>885</v>
       </c>
       <c r="O10" t="s">
+        <v>1796</v>
+      </c>
+      <c r="P10" t="s">
         <v>1797</v>
-      </c>
-      <c r="P10" t="s">
-        <v>1798</v>
       </c>
       <c r="Q10" t="s">
         <v>786</v>
@@ -15787,7 +15784,7 @@
         <v>1379</v>
       </c>
       <c r="T10" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -15931,10 +15928,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B7" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C7">
         <v>5000</v>
@@ -15952,10 +15949,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="C8">
         <v>1200.8900000000001</v>
@@ -15970,10 +15967,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B9" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="C9">
         <v>50500</v>
@@ -15991,7 +15988,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B10" t="s">
         <v>1004</v>
@@ -16009,7 +16006,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B11" t="s">
         <v>883</v>
@@ -16029,7 +16026,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B12" t="s">
         <v>881</v>
@@ -16049,7 +16046,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B13" t="s">
         <v>882</v>
@@ -16088,16 +16085,16 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2275</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2277</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2276</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -16111,7 +16108,7 @@
         <v>1086</v>
       </c>
       <c r="D2" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="E2" s="4">
         <v>44623</v>
@@ -16128,7 +16125,7 @@
         <v>1087</v>
       </c>
       <c r="D3" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="E3" s="4">
         <v>44084</v>
@@ -16145,7 +16142,7 @@
         <v>1097</v>
       </c>
       <c r="D4" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="E4" s="4">
         <v>36443</v>
@@ -16162,7 +16159,7 @@
         <v>1099</v>
       </c>
       <c r="D5" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E5" s="4">
         <v>42986</v>
@@ -16179,7 +16176,7 @@
         <v>1260</v>
       </c>
       <c r="D6" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -16921,7 +16918,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>45995</v>
+        <v>46042</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -17506,7 +17503,7 @@
     </row>
     <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="B14" t="s">
         <v>791</v>
@@ -17515,7 +17512,7 @@
         <v>45744</v>
       </c>
       <c r="H14" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="J14" t="s">
         <v>1355</v>
@@ -17566,13 +17563,13 @@
         <v>1</v>
       </c>
       <c r="AF14" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="AG14" t="s">
         <v>588</v>
       </c>
       <c r="AH14" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="AI14" t="s">
         <v>834</v>
@@ -17625,7 +17622,7 @@
     </row>
     <row r="15" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B15" t="s">
         <v>791</v>
@@ -17634,7 +17631,7 @@
         <v>45744</v>
       </c>
       <c r="H15" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="J15" t="s">
         <v>1305</v>
@@ -17747,7 +17744,7 @@
     </row>
     <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="B16" t="s">
         <v>791</v>
@@ -17756,7 +17753,7 @@
         <v>45744</v>
       </c>
       <c r="H16" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="J16" t="s">
         <v>1355</v>
@@ -17807,13 +17804,13 @@
         <v>1</v>
       </c>
       <c r="AF16" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="AG16" t="s">
         <v>588</v>
       </c>
       <c r="AH16" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="AI16" t="s">
         <v>834</v>
@@ -17886,16 +17883,16 @@
         <v>104</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>2102</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>2103</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>2104</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>2105</v>
       </c>
       <c r="F1" s="19" t="s">
         <v>1327</v>
@@ -17910,85 +17907,85 @@
         <v>1330</v>
       </c>
       <c r="J1" s="19" t="s">
+        <v>2105</v>
+      </c>
+      <c r="K1" s="19" t="s">
         <v>2106</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="L1" s="19" t="s">
         <v>2107</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="19" t="s">
         <v>2108</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="N1" s="19" t="s">
         <v>2109</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="O1" s="19" t="s">
         <v>2110</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="P1" s="19" t="s">
         <v>2111</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="Q1" s="19" t="s">
         <v>2112</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="R1" s="19" t="s">
         <v>2113</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="S1" s="19" t="s">
         <v>2114</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="T1" s="19" t="s">
         <v>2115</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="U1" s="19" t="s">
         <v>2116</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="V1" s="19" t="s">
         <v>2117</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="W1" s="19" t="s">
         <v>2118</v>
       </c>
-      <c r="W1" s="19" t="s">
+      <c r="X1" s="19" t="s">
         <v>2119</v>
       </c>
-      <c r="X1" s="19" t="s">
+      <c r="Y1" s="19" t="s">
         <v>2120</v>
       </c>
-      <c r="Y1" s="19" t="s">
+      <c r="Z1" s="19" t="s">
         <v>2121</v>
       </c>
-      <c r="Z1" s="19" t="s">
+      <c r="AA1" s="19" t="s">
         <v>2122</v>
       </c>
-      <c r="AA1" s="19" t="s">
+      <c r="AB1" s="19" t="s">
         <v>2123</v>
       </c>
-      <c r="AB1" s="19" t="s">
+      <c r="AC1" s="19" t="s">
         <v>2124</v>
       </c>
-      <c r="AC1" s="19" t="s">
+      <c r="AD1" s="19" t="s">
         <v>2125</v>
       </c>
-      <c r="AD1" s="19" t="s">
+      <c r="AE1" s="19" t="s">
         <v>2126</v>
       </c>
-      <c r="AE1" s="19" t="s">
+      <c r="AF1" s="19" t="s">
         <v>2127</v>
       </c>
-      <c r="AF1" s="19" t="s">
+      <c r="AG1" s="19" t="s">
         <v>2128</v>
       </c>
-      <c r="AG1" s="19" t="s">
+      <c r="AH1" s="19" t="s">
         <v>2129</v>
       </c>
-      <c r="AH1" s="19" t="s">
+      <c r="AI1" s="19" t="s">
         <v>2130</v>
       </c>
-      <c r="AI1" s="19" t="s">
+      <c r="AJ1" s="19" t="s">
         <v>2131</v>
-      </c>
-      <c r="AJ1" s="19" t="s">
-        <v>2132</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
@@ -18504,7 +18501,7 @@
         <v>1416</v>
       </c>
       <c r="B3" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -18540,7 +18537,7 @@
         <v>1416</v>
       </c>
       <c r="B6" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="C6" t="s">
         <v>588</v>
@@ -18600,7 +18597,7 @@
         <v>675</v>
       </c>
       <c r="B2" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="C2" t="s">
         <v>250</v>
@@ -18690,7 +18687,7 @@
         <v>891</v>
       </c>
       <c r="B8" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="C8" t="s">
         <v>892</v>
@@ -18721,7 +18718,7 @@
         <v>1088</v>
       </c>
       <c r="B10" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>1089</v>
@@ -18735,10 +18732,10 @@
         <v>1237</v>
       </c>
       <c r="B11" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="C11" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="D11" t="s">
         <v>588</v>
@@ -18763,7 +18760,7 @@
         <v>1340</v>
       </c>
       <c r="B13" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="C13" t="s">
         <v>1341</v>
@@ -18777,7 +18774,7 @@
         <v>1340</v>
       </c>
       <c r="B14" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="C14" t="s">
         <v>1342</v>
@@ -18845,7 +18842,7 @@
         <v>682</v>
       </c>
       <c r="C18" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -18870,10 +18867,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B20" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="C20" t="s">
         <v>1204</v>
@@ -18887,13 +18884,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B21" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="C21" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="D21" t="s">
         <v>588</v>
@@ -18901,13 +18898,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B22" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="C22" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="D22" t="s">
         <v>588</v>
@@ -18915,10 +18912,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B23" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="C23" t="s">
         <v>1204</v>
@@ -18932,10 +18929,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B24" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="C24" t="s">
         <v>685</v>
@@ -18946,10 +18943,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B25" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="C25" t="s">
         <v>1204</v>
@@ -19016,55 +19013,55 @@
         <v>239</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1500</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>2284</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2285</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>2287</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>2290</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>2358</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>2285</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>2286</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>2288</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>2289</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>2290</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>2291</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>2292</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>2359</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>2360</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>2361</v>
       </c>
-      <c r="T1" s="3" t="s">
-        <v>2362</v>
-      </c>
       <c r="U1" s="3" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -19075,7 +19072,7 @@
         <v>4361431</v>
       </c>
       <c r="D2" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="I2">
         <v>48</v>
@@ -19087,7 +19084,7 @@
         <v>23.888000000000002</v>
       </c>
       <c r="L2" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="M2">
         <v>123</v>
@@ -19099,10 +19096,10 @@
         <v>14.875999999999999</v>
       </c>
       <c r="P2" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -19110,7 +19107,7 @@
         <v>327</v>
       </c>
       <c r="H3" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -19118,7 +19115,7 @@
         <v>280</v>
       </c>
       <c r="D4" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -19126,7 +19123,7 @@
         <v>278</v>
       </c>
       <c r="B5" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -19134,18 +19131,18 @@
         <v>281</v>
       </c>
       <c r="B6" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B7" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="D7" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -19153,7 +19150,7 @@
         <v>273</v>
       </c>
       <c r="B8" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -19161,7 +19158,7 @@
         <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -19169,13 +19166,13 @@
         <v>1487</v>
       </c>
       <c r="B10" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="C10">
         <v>1821391</v>
       </c>
       <c r="D10" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="E10" t="s">
         <v>1338</v>
@@ -19190,19 +19187,19 @@
         <v>37</v>
       </c>
       <c r="L10" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="M10">
         <v>123</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="O10">
         <v>47</v>
       </c>
       <c r="P10" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -19210,7 +19207,7 @@
         <v>396</v>
       </c>
       <c r="B11" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -19218,7 +19215,7 @@
         <v>1317</v>
       </c>
       <c r="G12" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="I12">
         <v>49</v>
@@ -19230,7 +19227,7 @@
         <v>21.26</v>
       </c>
       <c r="L12" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="M12">
         <v>123</v>
@@ -19242,13 +19239,13 @@
         <v>40.9</v>
       </c>
       <c r="P12" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="Q12" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="V12" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -19256,7 +19253,7 @@
         <v>1315</v>
       </c>
       <c r="B13" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -19264,7 +19261,7 @@
         <v>1318</v>
       </c>
       <c r="B14" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -19272,7 +19269,7 @@
         <v>1316</v>
       </c>
       <c r="B15" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -19280,25 +19277,25 @@
         <v>689</v>
       </c>
       <c r="B16" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="C16">
         <v>1821391</v>
       </c>
       <c r="D16" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="E16" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H16" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="Q16" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="V16" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
@@ -19306,10 +19303,10 @@
         <v>1319</v>
       </c>
       <c r="B17" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="V17" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
@@ -19317,10 +19314,10 @@
         <v>1320</v>
       </c>
       <c r="B18" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="V18" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
@@ -19328,7 +19325,7 @@
         <v>697</v>
       </c>
       <c r="B19" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
@@ -19336,7 +19333,7 @@
         <v>1321</v>
       </c>
       <c r="B20" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
@@ -19355,10 +19352,10 @@
         <v>1323</v>
       </c>
       <c r="B22" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="V22" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
@@ -19366,7 +19363,7 @@
         <v>1324</v>
       </c>
       <c r="B23" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
@@ -19374,7 +19371,7 @@
         <v>1325</v>
       </c>
       <c r="B24" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
@@ -19382,10 +19379,10 @@
         <v>1326</v>
       </c>
       <c r="B25" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D25" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
@@ -19393,16 +19390,16 @@
         <v>1334</v>
       </c>
       <c r="E26" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="F26" t="s">
+        <v>2371</v>
+      </c>
+      <c r="H26" t="s">
         <v>2372</v>
       </c>
-      <c r="H26" t="s">
-        <v>2373</v>
-      </c>
       <c r="V26" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
@@ -19419,7 +19416,7 @@
         <v>51.6</v>
       </c>
       <c r="L27" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="M27">
         <v>123</v>
@@ -19431,7 +19428,7 @@
         <v>22.4</v>
       </c>
       <c r="P27" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
@@ -19439,7 +19436,7 @@
         <v>1336</v>
       </c>
       <c r="H28" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
@@ -19447,7 +19444,7 @@
         <v>1337</v>
       </c>
       <c r="F29" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
@@ -19455,7 +19452,7 @@
         <v>1486</v>
       </c>
       <c r="B30" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C30">
         <v>90054549</v>
@@ -19464,7 +19461,7 @@
         <v>1488</v>
       </c>
       <c r="E30" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
@@ -19472,56 +19469,56 @@
         <v>1501</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="H31" s="14"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="52" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="B32" s="14"/>
       <c r="E32" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="52" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B33" s="14" t="s">
         <v>2173</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>2174</v>
-      </c>
       <c r="F33" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="V33" s="14" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="52" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="B34" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="52" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="B35" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="C35">
         <v>90172682</v>
       </c>
       <c r="D35" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="E35" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="I35">
         <v>49</v>
@@ -19533,7 +19530,7 @@
         <v>19.010000000000002</v>
       </c>
       <c r="L35" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="M35">
         <v>123</v>
@@ -19545,49 +19542,49 @@
         <v>8.3040000000000003</v>
       </c>
       <c r="P35" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="V35" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="52" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="B36" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="V36" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="52" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B37" s="14"/>
       <c r="E37" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="V37" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="B38" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B39" t="s">
         <v>2393</v>
-      </c>
-      <c r="B39" t="s">
-        <v>2394</v>
       </c>
     </row>
   </sheetData>
@@ -19653,91 +19650,91 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1599</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1600</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>256</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>1562</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>1563</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1564</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>2268</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>1565</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>2269</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>1566</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>1567</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>1569</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>1570</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>1571</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>1568</v>
-      </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>1572</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>1573</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>1574</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>1575</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>1576</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>1577</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>1578</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>1579</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>1580</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>1581</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>1582</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>1583</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>1584</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>1585</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
@@ -19798,7 +19795,7 @@
         <v>267</v>
       </c>
       <c r="V3" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="W3" t="s">
         <v>787</v>
@@ -19827,28 +19824,28 @@
         <v>392</v>
       </c>
       <c r="B4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C4" t="s">
         <v>1601</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>1602</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1603</v>
       </c>
       <c r="F4" t="s">
         <v>393</v>
       </c>
       <c r="G4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H4" t="s">
         <v>1604</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1605</v>
       </c>
       <c r="J4" t="s">
         <v>394</v>
       </c>
       <c r="K4" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -19857,16 +19854,16 @@
         <v>3</v>
       </c>
       <c r="N4" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="O4" t="s">
         <v>190</v>
       </c>
       <c r="P4" t="s">
+        <v>1587</v>
+      </c>
+      <c r="Q4" t="s">
         <v>1588</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>1589</v>
       </c>
       <c r="R4" t="s">
         <v>264</v>
@@ -19875,7 +19872,7 @@
         <v>266</v>
       </c>
       <c r="T4" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="U4" t="s">
         <v>395</v>
@@ -19884,7 +19881,7 @@
         <v>1271</v>
       </c>
       <c r="W4" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="X4" t="s">
         <v>721</v>
@@ -19896,7 +19893,7 @@
         <v>1</v>
       </c>
       <c r="AB4" s="32" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="AC4" t="s">
         <v>269</v>
@@ -19946,7 +19943,7 @@
         <v>721</v>
       </c>
       <c r="Y5" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="Z5" s="30">
         <v>89.87</v>
@@ -20011,7 +20008,7 @@
         <v>1367</v>
       </c>
       <c r="V6" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="W6" t="s">
         <v>1368</v>
@@ -20058,49 +20055,49 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1591</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1592</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B2" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="C2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C3" t="s">
         <v>1593</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B4" t="s">
         <v>1595</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1596</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
   </sheetData>
@@ -20137,49 +20134,49 @@
         <v>104</v>
       </c>
       <c r="B1" s="38" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2193</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2194</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2195</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>2196</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2197</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>2198</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>2199</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>2200</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>2201</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>2202</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>2203</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>2204</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>2308</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>2309</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>2310</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -20193,25 +20190,25 @@
         <v>5500100</v>
       </c>
       <c r="D2" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="E2" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="F2" t="s">
         <v>890</v>
       </c>
       <c r="G2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="H2" t="s">
         <v>2206</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>2207</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>2208</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2209</v>
       </c>
       <c r="K2">
         <v>19</v>
@@ -20243,25 +20240,25 @@
         <v>5504830</v>
       </c>
       <c r="D3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2230</v>
+      </c>
+      <c r="F3" t="s">
         <v>2216</v>
       </c>
-      <c r="E3" t="s">
-        <v>2231</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>2214</v>
+      </c>
+      <c r="H3" t="s">
         <v>2217</v>
       </c>
-      <c r="G3" t="s">
-        <v>2215</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>2218</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>2219</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2220</v>
       </c>
       <c r="K3">
         <v>21</v>
@@ -20290,10 +20287,10 @@
         <v>246</v>
       </c>
       <c r="G4" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="I4" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -20322,10 +20319,10 @@
         <v>678</v>
       </c>
       <c r="G5" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="I5" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -20348,16 +20345,16 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="B6" t="s">
         <v>490</v>
       </c>
       <c r="G6" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="I6" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -20380,16 +20377,16 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B7" t="s">
         <v>490</v>
       </c>
       <c r="G7" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="I7" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -20412,16 +20409,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B8" t="s">
         <v>490</v>
       </c>
       <c r="G8" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="I8" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -20444,16 +20441,16 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B9" t="s">
         <v>490</v>
       </c>
       <c r="G9" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="I9" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -20476,16 +20473,16 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="B10" t="s">
         <v>490</v>
       </c>
       <c r="G10" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="I10" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -20508,16 +20505,16 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="B11" t="s">
         <v>490</v>
       </c>
       <c r="G11" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="I11" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -20540,16 +20537,16 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="B12" t="s">
         <v>490</v>
       </c>
       <c r="G12" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="I12" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -20626,7 +20623,7 @@
         <v>1163</v>
       </c>
       <c r="B2" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C2" t="s">
         <v>264</v>
@@ -20858,7 +20855,7 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1166</v>
@@ -20870,7 +20867,7 @@
         <v>1168</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1169</v>
@@ -20882,10 +20879,10 @@
         <v>1171</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1172</v>
@@ -20920,7 +20917,7 @@
         <v>1189</v>
       </c>
       <c r="D2" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="E2" t="s">
         <v>1213</v>
@@ -20932,10 +20929,10 @@
         <v>1192</v>
       </c>
       <c r="I2" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="J2" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="K2" t="s">
         <v>1195</v>
@@ -20973,7 +20970,7 @@
         <v>1190</v>
       </c>
       <c r="D3" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="E3" t="s">
         <v>1191</v>
@@ -20988,10 +20985,10 @@
         <v>1194</v>
       </c>
       <c r="J3" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="K3" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="L3" t="s">
         <v>1197</v>
@@ -21041,7 +21038,7 @@
         <v>1223</v>
       </c>
       <c r="J4" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="K4" t="s">
         <v>1225</v>
@@ -21079,7 +21076,7 @@
         <v>1278</v>
       </c>
       <c r="D5" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="E5" t="s">
         <v>1213</v>
@@ -21091,10 +21088,10 @@
         <v>1279</v>
       </c>
       <c r="I5" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="J5" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -21117,16 +21114,16 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="D6" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="E6" t="s">
         <v>1213</v>
@@ -21135,19 +21132,19 @@
         <v>45623</v>
       </c>
       <c r="H6" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="I6" t="s">
+        <v>2336</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2421</v>
+      </c>
+      <c r="K6" t="s">
         <v>2337</v>
       </c>
-      <c r="J6" t="s">
-        <v>2422</v>
-      </c>
-      <c r="K6" t="s">
-        <v>2338</v>
-      </c>
       <c r="L6" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -21170,16 +21167,16 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="D7" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="E7" t="s">
         <v>495</v>
@@ -21191,19 +21188,19 @@
         <v>45760</v>
       </c>
       <c r="H7" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="I7" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="J7" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="K7" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -21226,16 +21223,16 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="D8" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="E8" t="s">
         <v>1213</v>
@@ -21244,19 +21241,19 @@
         <v>45631</v>
       </c>
       <c r="H8" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="I8" t="s">
+        <v>2427</v>
+      </c>
+      <c r="J8" t="s">
         <v>2428</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>2429</v>
       </c>
-      <c r="K8" t="s">
-        <v>2430</v>
-      </c>
       <c r="L8" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -21388,16 +21385,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B4" t="s">
         <v>2317</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2318</v>
       </c>
       <c r="C4" s="4">
         <v>45300</v>
       </c>
       <c r="D4" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="E4" s="11">
         <v>9500.9699999999993</v>
@@ -21417,16 +21414,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B5" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="C5" s="4">
         <v>45544</v>
       </c>
       <c r="D5" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="E5" s="11">
         <v>155.84</v>
@@ -21446,16 +21443,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B6" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="C6" s="4">
         <v>45576</v>
       </c>
       <c r="D6" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="E6" s="11">
         <v>15077554.890000001</v>
@@ -21475,7 +21472,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B7" t="s">
         <v>1379</v>
@@ -21484,7 +21481,7 @@
         <v>45659</v>
       </c>
       <c r="D7" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="E7" s="11">
         <v>1780</v>
@@ -21504,16 +21501,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B8" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="C8" s="4">
         <v>45607</v>
       </c>
       <c r="D8" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="E8" s="11">
         <v>50</v>
@@ -21533,16 +21530,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B9" t="s">
         <v>2327</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2328</v>
       </c>
       <c r="C9" s="4">
         <v>45638</v>
       </c>
       <c r="D9" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="E9" s="11">
         <v>127.9</v>
@@ -21637,7 +21634,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -22828,7 +22825,7 @@
         <v>1047</v>
       </c>
       <c r="U8" s="16" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="V8" s="4">
         <v>44083</v>
@@ -23938,10 +23935,10 @@
         <v>1482</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>1489</v>
@@ -23958,10 +23955,10 @@
         <v>1483</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>246</v>
@@ -23978,10 +23975,10 @@
         <v>1483</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>246</v>
@@ -23998,10 +23995,10 @@
         <v>1482</v>
       </c>
       <c r="C5" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D5" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E5" t="s">
         <v>1489</v>
@@ -24018,10 +24015,10 @@
         <v>1483</v>
       </c>
       <c r="C6" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D6" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E6" t="s">
         <v>246</v>
@@ -24038,10 +24035,10 @@
         <v>1483</v>
       </c>
       <c r="C7" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="D7" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E7" t="s">
         <v>246</v>
@@ -24072,7 +24069,7 @@
         <v>1483</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -24086,7 +24083,7 @@
         <v>1483</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -24100,10 +24097,10 @@
         <v>1482</v>
       </c>
       <c r="C11" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="D11" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E11" t="s">
         <v>1489</v>
@@ -24120,10 +24117,10 @@
         <v>1482</v>
       </c>
       <c r="C12" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="D12" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E12" t="s">
         <v>1489</v>
@@ -24140,10 +24137,10 @@
         <v>1483</v>
       </c>
       <c r="C13" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="D13" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E13" t="s">
         <v>246</v>
@@ -24160,10 +24157,10 @@
         <v>1482</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E14" s="22" t="s">
         <v>1489</v>
@@ -24180,10 +24177,10 @@
         <v>1482</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1647</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>1648</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>1489</v>
@@ -24200,10 +24197,10 @@
         <v>1483</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E16" s="22" t="s">
         <v>246</v>
@@ -24220,7 +24217,7 @@
         <v>1482</v>
       </c>
       <c r="C17" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -24231,7 +24228,7 @@
         <v>1482</v>
       </c>
       <c r="C18" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -24242,7 +24239,7 @@
         <v>1483</v>
       </c>
       <c r="C19" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="J19" s="11"/>
     </row>
@@ -24254,7 +24251,7 @@
         <v>1482</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -24268,7 +24265,7 @@
         <v>1482</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -24282,7 +24279,7 @@
         <v>1483</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -24296,7 +24293,7 @@
         <v>1482</v>
       </c>
       <c r="C23" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -24315,7 +24312,7 @@
         <v>1483</v>
       </c>
       <c r="C25" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -24326,7 +24323,7 @@
         <v>1482</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -24340,7 +24337,7 @@
         <v>1483</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -24354,7 +24351,7 @@
         <v>1483</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -24368,7 +24365,7 @@
         <v>1482</v>
       </c>
       <c r="C29" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -24379,7 +24376,7 @@
         <v>1482</v>
       </c>
       <c r="C30" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -24392,13 +24389,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>1482</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -24406,13 +24403,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>1482</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -24420,7 +24417,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B34" s="22" t="s">
         <v>1483</v>
@@ -24602,7 +24599,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B15">
         <v>65</v>
@@ -24613,7 +24610,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B16">
         <v>70</v>
@@ -24624,7 +24621,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B17">
         <v>71</v>
@@ -24635,7 +24632,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="B18">
         <v>71</v>
@@ -24646,12 +24643,12 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
     </row>
   </sheetData>
@@ -24711,10 +24708,10 @@
         <v>504</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>446</v>
@@ -24828,10 +24825,10 @@
         <v>434</v>
       </c>
       <c r="AQ1" s="3" t="s">
+        <v>1905</v>
+      </c>
+      <c r="AR1" s="3" t="s">
         <v>1906</v>
-      </c>
-      <c r="AR1" s="3" t="s">
-        <v>1907</v>
       </c>
       <c r="AS1" s="3" t="s">
         <v>435</v>
@@ -24918,7 +24915,7 @@
         <v>496</v>
       </c>
       <c r="U4" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.3">
@@ -24963,7 +24960,7 @@
         <v>494</v>
       </c>
       <c r="AW7" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.3">
@@ -24978,7 +24975,7 @@
         <v>495</v>
       </c>
       <c r="AW8" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.3">
@@ -24993,7 +24990,7 @@
         <v>489</v>
       </c>
       <c r="AW9" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.3">
@@ -25008,18 +25005,18 @@
         <v>490</v>
       </c>
       <c r="AF10" t="s">
+        <v>1881</v>
+      </c>
+      <c r="AH10" t="s">
         <v>1882</v>
       </c>
-      <c r="AH10" t="s">
-        <v>1883</v>
-      </c>
       <c r="AY10" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="11" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>456</v>
@@ -25028,7 +25025,7 @@
         <v>492</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36"/>
@@ -25036,7 +25033,7 @@
       <c r="P11" s="36"/>
       <c r="R11" s="36"/>
       <c r="AW11" s="23" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="AX11" s="36"/>
     </row>
@@ -25124,7 +25121,7 @@
         <v>490</v>
       </c>
       <c r="AW16" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.3">
@@ -25142,13 +25139,13 @@
         <v>45245</v>
       </c>
       <c r="X17" t="s">
+        <v>1887</v>
+      </c>
+      <c r="AB17" t="s">
         <v>1888</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AW17" t="s">
         <v>1889</v>
-      </c>
-      <c r="AW17" t="s">
-        <v>1890</v>
       </c>
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.3">
@@ -25166,19 +25163,19 @@
         <v>36509</v>
       </c>
       <c r="Q18" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="R18" s="13">
         <v>36778</v>
       </c>
       <c r="S18" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="X18" s="9" t="s">
         <v>502</v>
       </c>
       <c r="Y18" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="AB18" t="s">
         <v>503</v>
@@ -25187,7 +25184,7 @@
       <c r="AQ18" s="4"/>
       <c r="AR18" s="4"/>
       <c r="AT18" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="19" spans="1:53" x14ac:dyDescent="0.3">
@@ -25205,13 +25202,13 @@
         <v>47045</v>
       </c>
       <c r="O19" t="s">
+        <v>1894</v>
+      </c>
+      <c r="AG19" t="s">
         <v>1895</v>
       </c>
-      <c r="AG19" t="s">
+      <c r="AV19" t="s">
         <v>1896</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>1897</v>
       </c>
       <c r="AX19" s="13">
         <v>42988</v>
@@ -25223,18 +25220,18 @@
         <v>Research File - Lease / License agreement</v>
       </c>
       <c r="B20" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="C20" t="s">
         <v>495</v>
       </c>
       <c r="AW20" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="21" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>468</v>
@@ -25243,7 +25240,7 @@
         <v>494</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="I21" s="36"/>
       <c r="J21" s="36"/>
@@ -25251,7 +25248,7 @@
       <c r="P21" s="36"/>
       <c r="R21" s="36"/>
       <c r="AW21" s="23" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="AX21" s="36"/>
     </row>
@@ -25299,16 +25296,16 @@
         <v>Acquisition File - Agricultural Land Commission (ALC)</v>
       </c>
       <c r="B24" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C24" t="s">
         <v>490</v>
       </c>
       <c r="E24" t="s">
+        <v>1900</v>
+      </c>
+      <c r="AW24" t="s">
         <v>1901</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="25" spans="1:53" x14ac:dyDescent="0.3">
@@ -25317,13 +25314,13 @@
         <v>Acquisition File - Form 5 - Approval of expropriation</v>
       </c>
       <c r="B25" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="C25" t="s">
         <v>491</v>
       </c>
       <c r="AW25" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="26" spans="1:53" x14ac:dyDescent="0.3">
@@ -25338,7 +25335,7 @@
         <v>492</v>
       </c>
       <c r="AW26" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.3">
@@ -25347,13 +25344,13 @@
         <v>Acquisition File - Compensation requisition (H-120)</v>
       </c>
       <c r="B27" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="C27" t="s">
         <v>493</v>
       </c>
       <c r="AW27" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.3">
@@ -25362,19 +25359,19 @@
         <v>Acquisition File - Land Act Tenure/Reserves</v>
       </c>
       <c r="B28" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="C28" t="s">
         <v>494</v>
       </c>
       <c r="AQ28" t="s">
+        <v>1907</v>
+      </c>
+      <c r="AR28" t="s">
         <v>1908</v>
       </c>
-      <c r="AR28" t="s">
+      <c r="AW28" t="s">
         <v>1909</v>
-      </c>
-      <c r="AW28" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.3">
@@ -25389,7 +25386,7 @@
         <v>495</v>
       </c>
       <c r="AW29" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="30" spans="1:53" x14ac:dyDescent="0.3">
@@ -25404,13 +25401,13 @@
         <v>489</v>
       </c>
       <c r="X30" t="s">
+        <v>1911</v>
+      </c>
+      <c r="AB30" t="s">
         <v>1912</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AJ30" t="s">
         <v>1913</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="31" spans="1:53" x14ac:dyDescent="0.3">
@@ -25425,7 +25422,7 @@
         <v>490</v>
       </c>
       <c r="AW31" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="32" spans="1:53" x14ac:dyDescent="0.3">
@@ -25443,16 +25440,16 @@
         <v>36850</v>
       </c>
       <c r="Z32" t="s">
+        <v>1915</v>
+      </c>
+      <c r="AA32" t="s">
         <v>1916</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AO32" t="s">
         <v>1917</v>
       </c>
-      <c r="AO32" t="s">
+      <c r="AT32" t="s">
         <v>1918</v>
-      </c>
-      <c r="AT32" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="33" spans="1:50" x14ac:dyDescent="0.3">
@@ -25461,18 +25458,18 @@
         <v>Acquisition File - Form 7 - Notice of abandonement</v>
       </c>
       <c r="B33" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="C33" t="s">
         <v>492</v>
       </c>
       <c r="AW33" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="34" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>737</v>
@@ -25481,7 +25478,7 @@
         <v>493</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="I34" s="36"/>
       <c r="J34" s="36"/>
@@ -25489,7 +25486,7 @@
       <c r="P34" s="36"/>
       <c r="R34" s="36"/>
       <c r="AW34" s="23" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AX34" s="36"/>
     </row>
@@ -25529,7 +25526,7 @@
         <v>753</v>
       </c>
       <c r="AO36" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="AW36" t="s">
         <v>754</v>
@@ -25541,7 +25538,7 @@
         <v>Project -Financial records (invoices, journal vouchers, received cheques etc.)</v>
       </c>
       <c r="B37" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="C37" t="s">
         <v>489</v>
@@ -25565,19 +25562,19 @@
         <v>756</v>
       </c>
       <c r="X38" t="s">
+        <v>1922</v>
+      </c>
+      <c r="AA38" t="s">
         <v>1923</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>1924</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>1925</v>
       </c>
       <c r="AP38" s="13">
         <v>43757</v>
       </c>
       <c r="AS38" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="39" spans="1:50" x14ac:dyDescent="0.3">
@@ -25595,10 +25592,10 @@
         <v>7190089</v>
       </c>
       <c r="AO39" t="s">
+        <v>1926</v>
+      </c>
+      <c r="AW39" t="s">
         <v>1927</v>
-      </c>
-      <c r="AW39" t="s">
-        <v>1928</v>
       </c>
     </row>
     <row r="40" spans="1:50" x14ac:dyDescent="0.3">
@@ -25619,16 +25616,16 @@
         <v>757</v>
       </c>
       <c r="AJ40" t="s">
+        <v>1928</v>
+      </c>
+      <c r="AK40" t="s">
         <v>1929</v>
       </c>
-      <c r="AK40" t="s">
+      <c r="AM40" t="s">
         <v>1930</v>
       </c>
-      <c r="AM40" t="s">
+      <c r="AN40" t="s">
         <v>1931</v>
-      </c>
-      <c r="AN40" t="s">
-        <v>1932</v>
       </c>
     </row>
     <row r="41" spans="1:50" x14ac:dyDescent="0.3">
@@ -25643,7 +25640,7 @@
         <v>493</v>
       </c>
       <c r="G41" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="I41" s="13">
         <v>32301</v>
@@ -25658,16 +25655,16 @@
         <v>760</v>
       </c>
       <c r="AF41" t="s">
+        <v>1933</v>
+      </c>
+      <c r="AO41" t="s">
         <v>1934</v>
-      </c>
-      <c r="AO41" t="s">
-        <v>1935</v>
       </c>
       <c r="AP41" s="4"/>
       <c r="AQ41" s="4"/>
       <c r="AR41" s="4"/>
       <c r="AW41" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="42" spans="1:50" x14ac:dyDescent="0.3">
@@ -25682,7 +25679,7 @@
         <v>494</v>
       </c>
       <c r="AW42" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="43" spans="1:50" x14ac:dyDescent="0.3">
@@ -25697,12 +25694,12 @@
         <v>495</v>
       </c>
       <c r="AW43" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="44" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>456</v>
@@ -25711,7 +25708,7 @@
         <v>489</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="I44" s="36"/>
       <c r="J44" s="36"/>
@@ -25729,7 +25726,7 @@
         <v>Disposition File -Certificate of Compliance</v>
       </c>
       <c r="B45" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="C45" t="s">
         <v>490</v>
@@ -25744,13 +25741,13 @@
         <v>Disposition File -Enhanced Referral Records</v>
       </c>
       <c r="B46" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="C46" t="s">
         <v>491</v>
       </c>
       <c r="AW46" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="47" spans="1:50" x14ac:dyDescent="0.3">
@@ -25759,13 +25756,13 @@
         <v>Disposition File -First Nations Strength of Claim Report</v>
       </c>
       <c r="B47" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="C47" t="s">
         <v>492</v>
       </c>
       <c r="AW47" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.3">
@@ -25780,7 +25777,7 @@
         <v>493</v>
       </c>
       <c r="AH48" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="49" spans="1:54" x14ac:dyDescent="0.3">
@@ -25795,7 +25792,7 @@
         <v>494</v>
       </c>
       <c r="AW49" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="50" spans="1:54" x14ac:dyDescent="0.3">
@@ -25813,13 +25810,13 @@
         <v>89997</v>
       </c>
       <c r="AD50" t="s">
+        <v>1942</v>
+      </c>
+      <c r="AE50" t="s">
         <v>1943</v>
       </c>
-      <c r="AE50" t="s">
+      <c r="AT50" t="s">
         <v>1944</v>
-      </c>
-      <c r="AT50" t="s">
-        <v>1945</v>
       </c>
       <c r="BA50">
         <v>1997</v>
@@ -25831,13 +25828,13 @@
         <v>Disposition File -Purchase and Sale Agreement</v>
       </c>
       <c r="B51" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="C51" t="s">
         <v>489</v>
       </c>
       <c r="AW51" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="52" spans="1:54" x14ac:dyDescent="0.3">
@@ -25852,7 +25849,7 @@
         <v>490</v>
       </c>
       <c r="AW52" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="53" spans="1:54" x14ac:dyDescent="0.3">
@@ -25867,12 +25864,12 @@
         <v>491</v>
       </c>
       <c r="AW53" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="54" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>740</v>
@@ -25881,7 +25878,7 @@
         <v>492</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="36">
@@ -25891,14 +25888,14 @@
       <c r="P54" s="36"/>
       <c r="R54" s="36"/>
       <c r="AA54" s="23" t="s">
+        <v>1948</v>
+      </c>
+      <c r="AT54" s="23" t="s">
         <v>1949</v>
-      </c>
-      <c r="AT54" s="23" t="s">
-        <v>1950</v>
       </c>
       <c r="AX54" s="36"/>
       <c r="AZ54" s="23" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="55" spans="1:54" x14ac:dyDescent="0.3">
@@ -25907,13 +25904,13 @@
         <v>Property Management -Approval/sign-off</v>
       </c>
       <c r="B55" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="C55" t="s">
         <v>493</v>
       </c>
       <c r="AW55" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="56" spans="1:54" x14ac:dyDescent="0.3">
@@ -25922,13 +25919,13 @@
         <v>Property Management -Form 8 - Notice of advanced payment </v>
       </c>
       <c r="B56" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="C56" t="s">
         <v>494</v>
       </c>
       <c r="AW56" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="57" spans="1:54" x14ac:dyDescent="0.3">
@@ -25937,13 +25934,13 @@
         <v>Property Management -Form 1 - Notice of expropriation </v>
       </c>
       <c r="B57" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="C57" t="s">
         <v>495</v>
       </c>
       <c r="AW57" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="58" spans="1:54" x14ac:dyDescent="0.3">
@@ -25958,7 +25955,7 @@
         <v>489</v>
       </c>
       <c r="AW58" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="59" spans="1:54" x14ac:dyDescent="0.3">
@@ -25973,7 +25970,7 @@
         <v>490</v>
       </c>
       <c r="AW59" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="60" spans="1:54" x14ac:dyDescent="0.3">
@@ -25988,7 +25985,7 @@
         <v>491</v>
       </c>
       <c r="AW60" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="61" spans="1:54" x14ac:dyDescent="0.3">
@@ -26018,7 +26015,7 @@
         <v>493</v>
       </c>
       <c r="AW62" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="63" spans="1:54" x14ac:dyDescent="0.3">
@@ -26036,16 +26033,16 @@
         <v>32874</v>
       </c>
       <c r="AA63" t="s">
+        <v>1954</v>
+      </c>
+      <c r="AO63" t="s">
         <v>1955</v>
-      </c>
-      <c r="AO63" t="s">
-        <v>1956</v>
       </c>
       <c r="AT63" t="s">
         <v>1380</v>
       </c>
       <c r="AZ63" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="64" spans="1:54" x14ac:dyDescent="0.3">
@@ -26054,18 +26051,18 @@
         <v>Property Management -Form 9 - Vesting notice (Form 9)</v>
       </c>
       <c r="B64" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="C64" t="s">
         <v>495</v>
       </c>
       <c r="AW64" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="65" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B65" s="23" t="s">
         <v>481</v>
@@ -26074,7 +26071,7 @@
         <v>489</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="36"/>
@@ -26082,7 +26079,7 @@
       <c r="P65" s="36"/>
       <c r="R65" s="36"/>
       <c r="AW65" s="23" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="AX65" s="36"/>
     </row>
@@ -26092,13 +26089,13 @@
         <v>Management File -Certificate of Compliance</v>
       </c>
       <c r="B66" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="C66" t="s">
         <v>490</v>
       </c>
       <c r="AW66" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="67" spans="1:54" x14ac:dyDescent="0.3">
@@ -26113,7 +26110,7 @@
         <v>491</v>
       </c>
       <c r="AW67" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="68" spans="1:54" x14ac:dyDescent="0.3">
@@ -26128,19 +26125,19 @@
         <v>494</v>
       </c>
       <c r="G68" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="I68" s="13">
         <v>32928</v>
       </c>
       <c r="AF68" t="s">
+        <v>2254</v>
+      </c>
+      <c r="AO68" t="s">
         <v>2255</v>
       </c>
-      <c r="AO68" t="s">
-        <v>2256</v>
-      </c>
       <c r="AW68" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="69" spans="1:54" x14ac:dyDescent="0.3">
@@ -26158,10 +26155,10 @@
         <v>30</v>
       </c>
       <c r="T69" t="s">
+        <v>2244</v>
+      </c>
+      <c r="AT69" t="s">
         <v>2245</v>
-      </c>
-      <c r="AT69" t="s">
-        <v>2246</v>
       </c>
     </row>
     <row r="70" spans="1:54" x14ac:dyDescent="0.3">
@@ -26176,18 +26173,18 @@
         <v>493</v>
       </c>
       <c r="K70" t="s">
+        <v>2246</v>
+      </c>
+      <c r="N70" t="s">
         <v>2247</v>
       </c>
-      <c r="N70" t="s">
+      <c r="W70" t="s">
         <v>2248</v>
-      </c>
-      <c r="W70" t="s">
-        <v>2249</v>
       </c>
     </row>
     <row r="71" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B71" s="23" t="s">
         <v>473</v>
@@ -26196,36 +26193,36 @@
         <v>495</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="I71" s="36"/>
       <c r="J71" s="36"/>
       <c r="M71" s="36"/>
       <c r="O71" s="23" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="P71" s="36"/>
       <c r="R71" s="36"/>
       <c r="X71" s="23" t="s">
+        <v>2251</v>
+      </c>
+      <c r="AA71" s="23" t="s">
         <v>2252</v>
       </c>
-      <c r="AA71" s="23" t="s">
+      <c r="AB71" s="23" t="s">
         <v>2253</v>
-      </c>
-      <c r="AB71" s="23" t="s">
-        <v>2254</v>
       </c>
       <c r="AP71" s="36">
         <v>45616</v>
       </c>
       <c r="AS71" s="23" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="AX71" s="36"/>
     </row>
     <row r="72" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B72" t="s">
         <v>737</v>
@@ -26234,12 +26231,12 @@
         <v>489</v>
       </c>
       <c r="AW72" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="73" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="B73" t="s">
         <v>455</v>
@@ -26248,13 +26245,13 @@
         <v>490</v>
       </c>
       <c r="G73" t="s">
+        <v>2349</v>
+      </c>
+      <c r="V73" t="s">
+        <v>2244</v>
+      </c>
+      <c r="AU73" t="s">
         <v>2350</v>
-      </c>
-      <c r="V73" t="s">
-        <v>2245</v>
-      </c>
-      <c r="AU73" t="s">
-        <v>2351</v>
       </c>
       <c r="BB73">
         <v>2025</v>
@@ -26262,7 +26259,7 @@
     </row>
     <row r="74" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B74" t="s">
         <v>457</v>
@@ -26271,10 +26268,10 @@
         <v>491</v>
       </c>
       <c r="F74" t="s">
+        <v>2351</v>
+      </c>
+      <c r="U74" t="s">
         <v>2352</v>
-      </c>
-      <c r="U74" t="s">
-        <v>2353</v>
       </c>
     </row>
   </sheetData>
@@ -26306,7 +26303,7 @@
         <v>338</v>
       </c>
       <c r="B2" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -26322,7 +26319,7 @@
         <v>340</v>
       </c>
       <c r="B4" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -26338,7 +26335,7 @@
         <v>645</v>
       </c>
       <c r="B6" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -26346,7 +26343,7 @@
         <v>1151</v>
       </c>
       <c r="B7" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -26370,7 +26367,7 @@
         <v>1376</v>
       </c>
       <c r="B10" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -26383,34 +26380,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B12" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B13" t="s">
         <v>2260</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2261</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="B14" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="B15" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
   </sheetData>
@@ -26482,7 +26479,7 @@
         <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>961</v>
@@ -27092,16 +27089,16 @@
         <v>508</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>509</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>1557</v>
@@ -27116,10 +27113,10 @@
         <v>512</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>1659</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>1660</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>513</v>
@@ -27158,43 +27155,43 @@
         <v>521</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AA1" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>1668</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>1669</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>1670</v>
       </c>
-      <c r="AD1" s="3" t="s">
-        <v>1671</v>
-      </c>
       <c r="AE1" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>2262</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>2263</v>
       </c>
       <c r="AG1" s="3" t="s">
         <v>1332</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AJ1" s="3" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AK1" s="3" t="s">
         <v>1806</v>
       </c>
-      <c r="AK1" s="3" t="s">
-        <v>1807</v>
-      </c>
       <c r="AL1" s="3" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="AM1" s="3" t="s">
         <v>523</v>
@@ -27203,7 +27200,7 @@
         <v>524</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="AP1" s="3" t="s">
         <v>525</v>
@@ -27215,13 +27212,13 @@
         <v>527</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="AT1" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AU1" s="3" t="s">
         <v>1768</v>
-      </c>
-      <c r="AU1" s="3" t="s">
-        <v>1769</v>
       </c>
       <c r="AV1" s="3" t="s">
         <v>528</v>
@@ -27353,25 +27350,25 @@
         <v>554</v>
       </c>
       <c r="CM1" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="CN1" s="3" t="s">
         <v>1736</v>
       </c>
-      <c r="CN1" s="3" t="s">
-        <v>1737</v>
-      </c>
       <c r="CO1" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="CP1" s="3" t="s">
         <v>1731</v>
       </c>
-      <c r="CP1" s="3" t="s">
-        <v>1732</v>
-      </c>
       <c r="CQ1" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="CR1" s="3" t="s">
         <v>1783</v>
       </c>
-      <c r="CR1" s="3" t="s">
+      <c r="CS1" s="3" t="s">
         <v>1784</v>
-      </c>
-      <c r="CS1" s="3" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="2" spans="1:97" x14ac:dyDescent="0.3">
@@ -27385,7 +27382,7 @@
         <v>1007</v>
       </c>
       <c r="D2" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="E2" t="s">
         <v>246</v>
@@ -27415,16 +27412,16 @@
         <v>7</v>
       </c>
       <c r="Q2" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="R2" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="T2" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="U2" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="V2" t="s">
         <v>559</v>
@@ -27439,7 +27436,7 @@
         <v>560</v>
       </c>
       <c r="Z2" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="AA2" t="s">
         <v>264</v>
@@ -27448,10 +27445,10 @@
         <v>264</v>
       </c>
       <c r="AC2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="AD2" t="s">
         <v>1672</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>1673</v>
       </c>
       <c r="AE2">
         <v>22</v>
@@ -27657,16 +27654,13 @@
         <v>1471</v>
       </c>
       <c r="E3" t="s">
-        <v>495</v>
+        <v>247</v>
       </c>
       <c r="F3" s="4">
         <v>45495</v>
       </c>
-      <c r="H3" t="s">
-        <v>1558</v>
-      </c>
       <c r="I3" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J3" s="4">
         <v>44614</v>
@@ -27684,13 +27678,13 @@
         <v>658</v>
       </c>
       <c r="T3" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="Y3" t="s">
         <v>578</v>
       </c>
       <c r="Z3" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="AA3" t="s">
         <v>266</v>
@@ -27699,10 +27693,10 @@
         <v>264</v>
       </c>
       <c r="AC3" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="AD3" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AE3">
         <v>24</v>
@@ -27812,7 +27806,7 @@
     </row>
     <row r="4" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="E4" t="s">
         <v>490</v>
@@ -27837,13 +27831,13 @@
         <v>190</v>
       </c>
       <c r="P4" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="R4" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="T4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -27930,7 +27924,7 @@
     </row>
     <row r="5" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="E5" t="s">
         <v>490</v>
@@ -27948,7 +27942,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -28035,13 +28029,13 @@
     </row>
     <row r="6" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="E6" t="s">
         <v>490</v>
       </c>
       <c r="I6" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J6" s="4">
         <v>45064</v>
@@ -28059,10 +28053,10 @@
         <v>190</v>
       </c>
       <c r="P6" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R6" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T6" t="s">
         <v>659</v>
@@ -28131,7 +28125,7 @@
         <v>44114</v>
       </c>
       <c r="BI6" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="CI6">
         <v>1</v>
@@ -28163,7 +28157,7 @@
     </row>
     <row r="7" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E7" t="s">
         <v>490</v>
@@ -28184,13 +28178,13 @@
         <v>192</v>
       </c>
       <c r="P7" t="s">
+        <v>1770</v>
+      </c>
+      <c r="R7" t="s">
         <v>1771</v>
       </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>1772</v>
-      </c>
-      <c r="T7" t="s">
-        <v>1773</v>
       </c>
       <c r="AE7">
         <v>0</v>
@@ -28276,7 +28270,7 @@
     </row>
     <row r="8" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E8" t="s">
         <v>490</v>
@@ -28296,13 +28290,13 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="Y8" t="s">
         <v>578</v>
       </c>
       <c r="Z8" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="AA8" t="s">
         <v>266</v>
@@ -28311,10 +28305,10 @@
         <v>264</v>
       </c>
       <c r="AC8" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="AD8" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AE8">
         <v>0</v>
@@ -28410,7 +28404,7 @@
     </row>
     <row r="9" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B9" t="s">
         <v>1008</v>
@@ -28419,13 +28413,13 @@
         <v>1007</v>
       </c>
       <c r="D9" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="E9" t="s">
         <v>490</v>
       </c>
       <c r="I9" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J9" s="4">
         <v>45209</v>
@@ -28440,13 +28434,13 @@
         <v>191</v>
       </c>
       <c r="P9" t="s">
+        <v>1786</v>
+      </c>
+      <c r="R9" t="s">
         <v>1787</v>
       </c>
-      <c r="R9" t="s">
+      <c r="T9" t="s">
         <v>1788</v>
-      </c>
-      <c r="T9" t="s">
-        <v>1789</v>
       </c>
       <c r="AA9" t="s">
         <v>297</v>
@@ -28544,13 +28538,13 @@
     </row>
     <row r="10" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="E10" t="s">
         <v>490</v>
       </c>
       <c r="I10" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J10" s="4">
         <v>45209</v>
@@ -28565,13 +28559,13 @@
         <v>191</v>
       </c>
       <c r="P10" t="s">
+        <v>1786</v>
+      </c>
+      <c r="R10" t="s">
         <v>1787</v>
       </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
         <v>1788</v>
-      </c>
-      <c r="T10" t="s">
-        <v>1789</v>
       </c>
       <c r="AE10">
         <v>0</v>
@@ -28660,7 +28654,7 @@
     </row>
     <row r="11" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="E11" t="s">
         <v>490</v>
@@ -28681,10 +28675,10 @@
         <v>190</v>
       </c>
       <c r="P11" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R11" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T11" t="s">
         <v>558</v>
@@ -28782,7 +28776,7 @@
     </row>
     <row r="12" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="E12" t="s">
         <v>247</v>
@@ -28803,10 +28797,10 @@
         <v>190</v>
       </c>
       <c r="P12" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R12" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T12" t="s">
         <v>558</v>
@@ -28904,13 +28898,13 @@
     </row>
     <row r="13" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="E13" t="s">
         <v>495</v>
       </c>
       <c r="H13" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="I13" t="s">
         <v>585</v>
@@ -28928,10 +28922,10 @@
         <v>190</v>
       </c>
       <c r="P13" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R13" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T13" t="s">
         <v>558</v>
@@ -29029,10 +29023,10 @@
     </row>
     <row r="14" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E14" t="s">
         <v>2178</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2179</v>
       </c>
       <c r="I14" t="s">
         <v>585</v>
@@ -29050,10 +29044,10 @@
         <v>190</v>
       </c>
       <c r="P14" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R14" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T14" t="s">
         <v>558</v>
@@ -29151,7 +29145,7 @@
     </row>
     <row r="15" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="E15" t="s">
         <v>678</v>
@@ -29172,10 +29166,10 @@
         <v>190</v>
       </c>
       <c r="P15" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R15" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T15" t="s">
         <v>558</v>
@@ -29273,16 +29267,16 @@
     </row>
     <row r="16" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="E16" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="F16" s="4">
         <v>45750</v>
       </c>
       <c r="G16" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="I16" t="s">
         <v>585</v>
@@ -29300,10 +29294,10 @@
         <v>190</v>
       </c>
       <c r="P16" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R16" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T16" t="s">
         <v>558</v>
@@ -29401,7 +29395,7 @@
     </row>
     <row r="17" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="E17" t="s">
         <v>246</v>
@@ -29425,10 +29419,10 @@
         <v>190</v>
       </c>
       <c r="P17" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R17" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T17" t="s">
         <v>558</v>
@@ -29526,7 +29520,7 @@
     </row>
     <row r="18" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="E18" t="s">
         <v>246</v>
@@ -29550,10 +29544,10 @@
         <v>190</v>
       </c>
       <c r="P18" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R18" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T18" t="s">
         <v>558</v>
@@ -29651,7 +29645,7 @@
     </row>
     <row r="19" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="B19" t="s">
         <v>1008</v>
@@ -29660,13 +29654,13 @@
         <v>1007</v>
       </c>
       <c r="D19" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="E19" t="s">
         <v>490</v>
       </c>
       <c r="I19" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J19" s="4">
         <v>45209</v>
@@ -29681,13 +29675,13 @@
         <v>191</v>
       </c>
       <c r="P19" t="s">
+        <v>1786</v>
+      </c>
+      <c r="R19" t="s">
         <v>1787</v>
       </c>
-      <c r="R19" t="s">
+      <c r="T19" t="s">
         <v>1788</v>
-      </c>
-      <c r="T19" t="s">
-        <v>1789</v>
       </c>
       <c r="AA19" t="s">
         <v>297</v>
@@ -29785,13 +29779,13 @@
     </row>
     <row r="20" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="E20" t="s">
         <v>490</v>
       </c>
       <c r="I20" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
@@ -29803,13 +29797,13 @@
         <v>191</v>
       </c>
       <c r="P20" t="s">
+        <v>1786</v>
+      </c>
+      <c r="R20" t="s">
         <v>1787</v>
       </c>
-      <c r="R20" t="s">
+      <c r="T20" t="s">
         <v>1788</v>
-      </c>
-      <c r="T20" t="s">
-        <v>1789</v>
       </c>
       <c r="AA20" t="s">
         <v>297</v>
@@ -29904,7 +29898,7 @@
     </row>
     <row r="21" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="E21" t="s">
         <v>246</v>
@@ -29928,13 +29922,13 @@
         <v>190</v>
       </c>
       <c r="P21" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="R21" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="T21" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="X21" s="4"/>
       <c r="AA21" t="s">
@@ -30037,7 +30031,7 @@
     </row>
     <row r="22" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="E22" t="s">
         <v>246</v>
@@ -30052,7 +30046,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="AA22" t="s">
         <v>297</v>
@@ -30148,7 +30142,7 @@
     </row>
     <row r="23" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="E23" t="s">
         <v>246</v>
@@ -30172,13 +30166,13 @@
         <v>190</v>
       </c>
       <c r="P23" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="R23" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="T23" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="X23" s="4"/>
       <c r="AA23" t="s">
@@ -30281,7 +30275,7 @@
     </row>
     <row r="24" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="E24" t="s">
         <v>246</v>
@@ -30305,13 +30299,13 @@
         <v>190</v>
       </c>
       <c r="P24" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="R24" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="T24" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="X24" s="4"/>
       <c r="AA24" t="s">
@@ -30441,7 +30435,7 @@
     </row>
     <row r="25" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E25" t="s">
         <v>246</v>
@@ -30458,10 +30452,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="T25" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AA25" t="s">
         <v>297</v>
@@ -30566,7 +30560,7 @@
     </row>
     <row r="26" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="E26" t="s">
         <v>246</v>
@@ -30590,13 +30584,13 @@
         <v>190</v>
       </c>
       <c r="P26" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="R26" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="T26" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="X26" s="4"/>
       <c r="AA26" t="s">
@@ -30779,7 +30773,7 @@
     </row>
     <row r="27" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="E27" t="s">
         <v>246</v>
@@ -30796,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="AA27" t="s">
         <v>297</v>
@@ -30903,7 +30897,7 @@
     </row>
     <row r="28" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="E28" t="s">
         <v>246</v>
@@ -30927,13 +30921,13 @@
         <v>190</v>
       </c>
       <c r="P28" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="R28" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="T28" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="X28" s="4"/>
       <c r="AA28" t="s">
@@ -31039,7 +31033,7 @@
     </row>
     <row r="29" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="F29" s="4"/>
       <c r="J29" s="4"/>
@@ -31053,7 +31047,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="AA29" t="s">
         <v>297</v>
@@ -31152,7 +31146,7 @@
     </row>
     <row r="30" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="E30" t="s">
         <v>246</v>
@@ -31179,10 +31173,10 @@
         <v>658</v>
       </c>
       <c r="R30" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="T30" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="X30" s="4"/>
       <c r="AA30" t="s">
@@ -31285,7 +31279,7 @@
     </row>
     <row r="31" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="F31" s="4"/>
       <c r="J31" s="4"/>
@@ -31395,7 +31389,7 @@
     </row>
     <row r="32" spans="1:97" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
@@ -31505,7 +31499,7 @@
         <v>490</v>
       </c>
       <c r="I33" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J33" s="4">
         <v>45064</v>
@@ -31523,10 +31517,10 @@
         <v>190</v>
       </c>
       <c r="P33" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="R33" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T33" t="s">
         <v>659</v>
@@ -31616,13 +31610,13 @@
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="E34" t="s">
         <v>490</v>
       </c>
       <c r="I34" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J34" s="4">
         <v>45064</v>
@@ -31640,13 +31634,13 @@
         <v>192</v>
       </c>
       <c r="P34" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="R34" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="T34" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -31753,21 +31747,21 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1653</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>1654</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B2" t="s">
         <v>264</v>
@@ -31779,12 +31773,12 @@
         <v>45412</v>
       </c>
       <c r="E2" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B3" t="s">
         <v>264</v>
@@ -31796,12 +31790,12 @@
         <v>45778</v>
       </c>
       <c r="E3" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B4" t="s">
         <v>266</v>
@@ -31813,12 +31807,12 @@
         <v>49431</v>
       </c>
       <c r="E4" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="B5" t="s">
         <v>264</v>
@@ -31830,7 +31824,7 @@
         <v>45412</v>
       </c>
       <c r="E5" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
   </sheetData>
@@ -31861,34 +31855,34 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1681</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1690</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>1682</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>1683</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>1684</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1685</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>1686</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>1687</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>1688</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -31896,28 +31890,28 @@
         <v>1470</v>
       </c>
       <c r="B2" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="C2" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D2" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="E2">
         <v>500</v>
       </c>
       <c r="F2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="I2" t="s">
         <v>1691</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>1692</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>1693</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -31925,31 +31919,31 @@
         <v>1470</v>
       </c>
       <c r="B3" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="D3" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="E3">
         <v>25</v>
       </c>
       <c r="F3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G3" t="s">
         <v>1696</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>1697</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>1698</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>1699</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -31957,22 +31951,22 @@
         <v>1470</v>
       </c>
       <c r="B4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F4" t="s">
         <v>1701</v>
       </c>
-      <c r="C4" t="s">
-        <v>1709</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>1702</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>1703</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>1704</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -31980,7 +31974,7 @@
         <v>1470</v>
       </c>
       <c r="K5" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -31988,10 +31982,10 @@
         <v>1470</v>
       </c>
       <c r="B6" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="K6" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -31999,25 +31993,25 @@
         <v>1471</v>
       </c>
       <c r="B7" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D7" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="E7">
         <v>900</v>
       </c>
       <c r="F7" t="s">
+        <v>1690</v>
+      </c>
+      <c r="I7" t="s">
         <v>1691</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>1692</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>1693</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1694</v>
       </c>
     </row>
   </sheetData>
@@ -32049,39 +32043,39 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1808</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>1809</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>1810</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>1811</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1812</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>1813</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>1814</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>1815</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B2" t="s">
         <v>522</v>
@@ -32093,7 +32087,7 @@
         <v>588</v>
       </c>
       <c r="F2" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2" t="s">
         <v>264</v>
@@ -32105,15 +32099,15 @@
         <v>1031</v>
       </c>
       <c r="K2" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B3" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="D3" s="4">
         <v>45544</v>
@@ -32122,25 +32116,25 @@
         <v>588</v>
       </c>
       <c r="F3" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H3" t="s">
         <v>266</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="K3" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="B4" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="D4" s="4">
         <v>45545</v>
@@ -32149,7 +32143,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H4" t="s">
         <v>264</v>
@@ -32158,18 +32152,18 @@
         <v>45563</v>
       </c>
       <c r="J4" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="K4" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B5" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="D5" s="4">
         <v>45546</v>
@@ -32178,7 +32172,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H5" t="s">
         <v>264</v>
@@ -32187,18 +32181,18 @@
         <v>45562</v>
       </c>
       <c r="J5" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="K5" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B6" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="D6" s="4">
         <v>45547</v>
@@ -32207,25 +32201,25 @@
         <v>588</v>
       </c>
       <c r="F6" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H6" t="s">
         <v>266</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="K6" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B7" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="D7" s="4">
         <v>45548</v>
@@ -32234,7 +32228,7 @@
         <v>588</v>
       </c>
       <c r="F7" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H7" t="s">
         <v>264</v>
@@ -32246,15 +32240,15 @@
         <v>1031</v>
       </c>
       <c r="K7" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B8" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="D8" s="4">
         <v>45549</v>
@@ -32275,21 +32269,21 @@
         <v>45559</v>
       </c>
       <c r="J8" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="K8" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="D9" s="4">
         <v>45550</v>
@@ -32308,18 +32302,18 @@
       </c>
       <c r="I9" s="4"/>
       <c r="J9" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="K9" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B10" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="D10" s="4">
         <v>45551</v>
@@ -32328,7 +32322,7 @@
         <v>588</v>
       </c>
       <c r="F10" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H10" t="s">
         <v>264</v>
@@ -32337,10 +32331,10 @@
         <v>45557</v>
       </c>
       <c r="J10" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="K10" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
   </sheetData>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76CFF24A-761C-4CF9-BD8F-7FFB1C75A529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9CE74F-956C-4F87-B318-F1501094476B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="19" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4417" uniqueCount="2441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="2441">
   <si>
     <t>FirstName</t>
   </si>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -19503,6 +19503,9 @@
       <c r="B34" t="s">
         <v>2181</v>
       </c>
+      <c r="V34" t="s">
+        <v>2181</v>
+      </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="52" t="s">
@@ -19578,12 +19581,18 @@
       <c r="B38" t="s">
         <v>2226</v>
       </c>
+      <c r="V38" t="s">
+        <v>2226</v>
+      </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
         <v>2392</v>
       </c>
       <c r="B39" t="s">
+        <v>2393</v>
+      </c>
+      <c r="V39" t="s">
         <v>2393</v>
       </c>
     </row>
@@ -20184,7 +20193,7 @@
         <v>1049</v>
       </c>
       <c r="B2" t="s">
-        <v>678</v>
+        <v>490</v>
       </c>
       <c r="C2" s="45">
         <v>5500100</v>
@@ -27385,7 +27394,7 @@
         <v>1968</v>
       </c>
       <c r="E2" t="s">
-        <v>246</v>
+        <v>490</v>
       </c>
       <c r="I2" t="s">
         <v>556</v>
@@ -27654,7 +27663,7 @@
         <v>1471</v>
       </c>
       <c r="E3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F3" s="4">
         <v>45495</v>
@@ -31398,7 +31407,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>658</v>
+        <v>2377</v>
       </c>
       <c r="AA32" t="s">
         <v>297</v>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2155D447-18A7-466A-85F3-46C6B8FB4DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46193B00-550F-4502-9BF0-5894803D468A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="21" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="3" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4418" uniqueCount="2445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="2447">
   <si>
     <t>FirstName</t>
   </si>
@@ -7418,6 +7418,12 @@
   </si>
   <si>
     <t>Updating existing improvement</t>
+  </si>
+  <si>
+    <t>Multiproperty plan number</t>
+  </si>
+  <si>
+    <t>LMS220</t>
   </si>
 </sst>
 </file>
@@ -10781,7 +10787,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -11025,7 +11031,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11250,7 +11256,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11823,7 +11829,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12166,7 +12172,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -16951,7 +16957,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -18999,7 +19005,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E382B1-281B-4434-81AA-04C8D5F3D2FB}">
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -19630,6 +19636,14 @@
       </c>
       <c r="V39" t="s">
         <v>2361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" s="52" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2446</v>
       </c>
     </row>
   </sheetData>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46193B00-550F-4502-9BF0-5894803D468A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA4A9A7-0774-46A3-9559-9FE00112EFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="2447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4422" uniqueCount="2449">
   <si>
     <t>FirstName</t>
   </si>
@@ -7424,6 +7424,12 @@
   </si>
   <si>
     <t>LMS220</t>
+  </si>
+  <si>
+    <t>Highway and Other Property Tabs</t>
+  </si>
+  <si>
+    <t>LMP16339</t>
   </si>
 </sst>
 </file>
@@ -10787,7 +10793,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -11031,7 +11037,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -11256,7 +11262,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -11829,7 +11835,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -12172,7 +12178,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -16957,7 +16963,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -19005,7 +19011,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E382B1-281B-4434-81AA-04C8D5F3D2FB}">
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -19644,6 +19650,14 @@
       </c>
       <c r="E40" t="s">
         <v>2446</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="52" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2448</v>
       </c>
     </row>
   </sheetData>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA4A9A7-0774-46A3-9559-9FE00112EFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC6EEF5-5DCC-48CB-B271-C21163730F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="950" firstSheet="31" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4422" uniqueCount="2449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4424" uniqueCount="2451">
   <si>
     <t>FirstName</t>
   </si>
@@ -7430,6 +7430,12 @@
   </si>
   <si>
     <t>LMP16339</t>
+  </si>
+  <si>
+    <t>PMBC and Crown Property Tabs</t>
+  </si>
+  <si>
+    <t>008-741-972</t>
   </si>
 </sst>
 </file>
@@ -19011,7 +19017,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E382B1-281B-4434-81AA-04C8D5F3D2FB}">
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -19658,6 +19664,14 @@
       </c>
       <c r="E41" t="s">
         <v>2448</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="52" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2450</v>
       </c>
     </row>
   </sheetData>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB00F49-D684-450D-9239-CD66B657DF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B649D93D-ED7B-42BA-9BCE-F7F3DC7752BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="30" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="30" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AcquisitionChecklist" sheetId="22" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4496" uniqueCount="2482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4512" uniqueCount="2492">
   <si>
     <t>FirstName</t>
   </si>
@@ -7529,6 +7529,36 @@
   </si>
   <si>
     <t>001-465-201</t>
+  </si>
+  <si>
+    <t>ImprovementName</t>
+  </si>
+  <si>
+    <t>ImprovementStatus</t>
+  </si>
+  <si>
+    <t>ImprovementDate</t>
+  </si>
+  <si>
+    <t>Property Improvement 001</t>
+  </si>
+  <si>
+    <t>Property Improvement 002</t>
+  </si>
+  <si>
+    <t>Property Improvement 003</t>
+  </si>
+  <si>
+    <t>Property Improvement Edited</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>10/12/2025</t>
+  </si>
+  <si>
+    <t>02/02/2026</t>
   </si>
 </sst>
 </file>
@@ -23389,70 +23419,119 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7262AB15-46E3-445C-B25C-563340BB9466}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2482</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2428</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>2427</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2430</v>
       </c>
       <c r="B2" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C2" t="s">
         <v>2432</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F2" t="s">
         <v>2434</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2430</v>
       </c>
       <c r="B3" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C3" t="s">
         <v>2433</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F3" t="s">
         <v>2435</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2430</v>
       </c>
       <c r="B4" t="s">
+        <v>2487</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2490</v>
+      </c>
+      <c r="F4" t="s">
         <v>2436</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2431</v>
       </c>
       <c r="B5" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C5" t="s">
         <v>2433</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F5" t="s">
         <v>2437</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -28279,7 +28358,9 @@
       <c r="A32" s="52" t="s">
         <v>2137</v>
       </c>
-      <c r="B32" s="14"/>
+      <c r="B32" t="s">
+        <v>2481</v>
+      </c>
       <c r="E32" t="s">
         <v>2334</v>
       </c>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B649D93D-ED7B-42BA-9BCE-F7F3DC7752BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61E1E7A-1C66-4553-8944-8E608BF8785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="30" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="23" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AcquisitionChecklist" sheetId="22" r:id="rId1"/>
@@ -63,6 +63,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">DocumentsDetails!$A$1:$BB$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -7234,9 +7235,6 @@
     <t>Alfred Grist</t>
   </si>
   <si>
-    <t>BC Hydro</t>
-  </si>
-  <si>
     <t>The Corporation of the City of Victoria</t>
   </si>
   <si>
@@ -7559,6 +7557,9 @@
   </si>
   <si>
     <t>02/02/2026</t>
+  </si>
+  <si>
+    <t>Ana I Agner</t>
   </si>
 </sst>
 </file>
@@ -8580,13 +8581,13 @@
         <v>2088</v>
       </c>
       <c r="Z1" s="19" t="s">
+        <v>2477</v>
+      </c>
+      <c r="AA1" s="19" t="s">
         <v>2478</v>
       </c>
-      <c r="AA1" s="19" t="s">
+      <c r="AB1" s="19" t="s">
         <v>2479</v>
-      </c>
-      <c r="AB1" s="19" t="s">
-        <v>2480</v>
       </c>
       <c r="AC1" s="19" t="s">
         <v>2089</v>
@@ -9043,10 +9044,10 @@
         <v>1415</v>
       </c>
       <c r="V1" s="3" t="s">
+        <v>2445</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>2446</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>2447</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>1323</v>
@@ -9355,7 +9356,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -10375,13 +10376,13 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B17" t="s">
         <v>246</v>
       </c>
       <c r="H17" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="J17" t="s">
         <v>1277</v>
@@ -10425,18 +10426,18 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="B18" t="s">
         <v>246</v>
       </c>
       <c r="F18" s="4">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="I18" t="s">
         <v>1331</v>
@@ -10884,7 +10885,7 @@
         <v>501</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1867</v>
@@ -11201,7 +11202,7 @@
         <v>489</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36"/>
@@ -11416,7 +11417,7 @@
         <v>491</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="I21" s="36"/>
       <c r="J21" s="36"/>
@@ -11654,7 +11655,7 @@
         <v>490</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="I34" s="36"/>
       <c r="J34" s="36"/>
@@ -11884,7 +11885,7 @@
         <v>486</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="I44" s="36"/>
       <c r="J44" s="36"/>
@@ -12054,7 +12055,7 @@
         <v>489</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="36">
@@ -12247,7 +12248,7 @@
         <v>486</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="36"/>
@@ -12369,7 +12370,7 @@
         <v>492</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="I71" s="36"/>
       <c r="J71" s="36"/>
@@ -13569,10 +13570,10 @@
         <v>509</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>2418</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>2419</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>2420</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>1626</v>
@@ -13677,7 +13678,7 @@
         <v>1619</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="AW1" s="3" t="s">
         <v>1735</v>
@@ -14086,7 +14087,7 @@
         <v>1946</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="N3" s="8">
         <v>4</v>
@@ -20358,7 +20359,7 @@
         <v>2165</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>2166</v>
@@ -20367,7 +20368,7 @@
         <v>2167</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>2168</v>
@@ -20376,10 +20377,10 @@
         <v>2169</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>2412</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>2413</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>2414</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>2170</v>
@@ -20435,10 +20436,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="P2" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -20494,10 +20495,10 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="P3" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -22959,13 +22960,13 @@
         <v>1549</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="Y1" s="3" t="s">
+        <v>2458</v>
+      </c>
+      <c r="Z1" s="3" t="s">
         <v>2459</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>2460</v>
       </c>
       <c r="AA1" s="3" t="s">
         <v>1550</v>
@@ -22980,19 +22981,19 @@
         <v>1553</v>
       </c>
       <c r="AE1" s="3" t="s">
+        <v>2421</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>2422</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>2423</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>2424</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>2425</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>2426</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
@@ -23207,13 +23208,13 @@
         <v>694</v>
       </c>
       <c r="X5" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="Y5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="Z5" t="s">
         <v>2461</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>2462</v>
       </c>
       <c r="AA5" s="30">
         <v>89.87</v>
@@ -23228,13 +23229,13 @@
         <v>670</v>
       </c>
       <c r="AE5" t="s">
+        <v>2456</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>2407</v>
+      </c>
+      <c r="AG5" t="s">
         <v>2457</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>2408</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>2458</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -23316,7 +23317,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="B7" t="s">
         <v>1568</v>
@@ -23435,67 +23436,67 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2427</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2482</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2428</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2483</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>2484</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="B2" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C2" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="D2" t="s">
         <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="F2" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="B3" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="C3" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="D3" t="s">
         <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="F3" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="B4" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -23504,30 +23505,30 @@
         <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="F4" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="B5" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="C5" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="D5" t="s">
         <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="F5" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
     </row>
   </sheetData>
@@ -23796,7 +23797,7 @@
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -23880,7 +23881,7 @@
         <v>1161</v>
       </c>
       <c r="D2" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="E2" t="s">
         <v>1185</v>
@@ -23933,7 +23934,7 @@
         <v>1162</v>
       </c>
       <c r="D3" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="E3" t="s">
         <v>1163</v>
@@ -24001,7 +24002,7 @@
         <v>1195</v>
       </c>
       <c r="J4" t="s">
-        <v>2383</v>
+        <v>2491</v>
       </c>
       <c r="K4" t="s">
         <v>1197</v>
@@ -24039,7 +24040,7 @@
         <v>1250</v>
       </c>
       <c r="D5" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="E5" t="s">
         <v>1185</v>
@@ -24054,7 +24055,7 @@
         <v>2191</v>
       </c>
       <c r="J5" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -24101,13 +24102,13 @@
         <v>2301</v>
       </c>
       <c r="J6" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="K6" t="s">
         <v>2302</v>
       </c>
       <c r="L6" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -24157,10 +24158,10 @@
         <v>2272</v>
       </c>
       <c r="J7" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="K7" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="L7" s="14" t="s">
         <v>2280</v>
@@ -24207,13 +24208,13 @@
         <v>2271</v>
       </c>
       <c r="I8" t="s">
+        <v>2390</v>
+      </c>
+      <c r="J8" t="s">
         <v>2391</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>2392</v>
-      </c>
-      <c r="K8" t="s">
-        <v>2393</v>
       </c>
       <c r="L8" t="s">
         <v>2281</v>
@@ -24636,10 +24637,10 @@
         <v>770</v>
       </c>
       <c r="AH1" s="38" t="s">
+        <v>2405</v>
+      </c>
+      <c r="AI1" s="38" t="s">
         <v>2406</v>
-      </c>
-      <c r="AI1" s="38" t="s">
-        <v>2407</v>
       </c>
       <c r="AJ1" s="38" t="s">
         <v>1303</v>
@@ -24788,10 +24789,10 @@
         <v>768</v>
       </c>
       <c r="AH2" t="s">
+        <v>2407</v>
+      </c>
+      <c r="AI2" t="s">
         <v>2408</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>2409</v>
       </c>
       <c r="AJ2">
         <v>15</v>
@@ -24881,7 +24882,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -24929,10 +24930,10 @@
         <v>981</v>
       </c>
       <c r="AH3" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="AI3" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -25125,7 +25126,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -25350,7 +25351,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -25923,7 +25924,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -26266,7 +26267,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -27939,7 +27940,7 @@
         <v>2326</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>2362</v>
@@ -28280,7 +28281,7 @@
         <v>2337</v>
       </c>
       <c r="V26" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
@@ -28359,13 +28360,13 @@
         <v>2137</v>
       </c>
       <c r="B32" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="E32" t="s">
         <v>2334</v>
       </c>
       <c r="V32" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -28404,7 +28405,7 @@
         <v>90172682</v>
       </c>
       <c r="D35" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="E35" t="s">
         <v>2194</v>
@@ -28434,7 +28435,7 @@
         <v>2259</v>
       </c>
       <c r="V35" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
@@ -28484,26 +28485,26 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="52" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E40" t="s">
         <v>2438</v>
-      </c>
-      <c r="E40" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="52" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E41" t="s">
         <v>2440</v>
-      </c>
-      <c r="E41" t="s">
-        <v>2441</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="52" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B42" t="s">
         <v>2442</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2443</v>
       </c>
     </row>
   </sheetData>
@@ -31865,10 +31866,10 @@
         <v>487</v>
       </c>
       <c r="H2" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="I2" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J2" s="4">
         <v>44440</v>
@@ -31912,10 +31913,10 @@
         <v>487</v>
       </c>
       <c r="H3" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="I3" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="J3" s="4">
         <v>44806</v>
@@ -31956,10 +31957,10 @@
         <v>492</v>
       </c>
       <c r="G4" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="H4" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="I4" t="s">
         <v>796</v>
@@ -32003,7 +32004,7 @@
         <v>487</v>
       </c>
       <c r="H5" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="I5" t="s">
         <v>797</v>
@@ -32047,7 +32048,7 @@
         <v>487</v>
       </c>
       <c r="H6" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="I6" t="s">
         <v>794</v>
@@ -32091,7 +32092,7 @@
         <v>487</v>
       </c>
       <c r="H7" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="I7" t="s">
         <v>794</v>
@@ -32135,10 +32136,10 @@
         <v>487</v>
       </c>
       <c r="H8" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="I8" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="J8" s="4">
         <v>45265</v>
@@ -32164,25 +32165,25 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="B9" t="s">
         <v>487</v>
       </c>
       <c r="D9" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="E9" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="F9" t="s">
         <v>487</v>
       </c>
       <c r="H9" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="I9" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="J9" s="4">
         <v>45658</v>
@@ -32208,25 +32209,25 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="B10" t="s">
         <v>487</v>
       </c>
       <c r="D10" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E10" t="s">
         <v>2451</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2452</v>
       </c>
       <c r="F10" t="s">
         <v>487</v>
       </c>
       <c r="H10" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="I10" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="J10" s="4">
         <v>45690</v>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61E1E7A-1C66-4553-8944-8E608BF8785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD03F98A-7138-4FB8-86B6-E417405C8E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="23" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="26" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AcquisitionChecklist" sheetId="22" r:id="rId1"/>
@@ -63,7 +63,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">DocumentsDetails!$A$1:$BB$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -84,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4512" uniqueCount="2492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4511" uniqueCount="2490">
   <si>
     <t>FirstName</t>
   </si>
@@ -7088,9 +7087,6 @@
     <t>Ali Thomson (Equitable Charge);Joe Ellicott (MoTT Solicitor)</t>
   </si>
   <si>
-    <t>VIP28994</t>
-  </si>
-  <si>
     <t>7888-000</t>
   </si>
   <si>
@@ -7103,9 +7099,6 @@
     <t>7888-0001</t>
   </si>
   <si>
-    <t>BCS862</t>
-  </si>
-  <si>
     <t>029-372-445;006-112-447</t>
   </si>
   <si>
@@ -7181,9 +7174,6 @@
     <t>010-764-135;015-069-940;007-095-333</t>
   </si>
   <si>
-    <t>026-172-674</t>
-  </si>
-  <si>
     <t>Property 01;Property 02;029-372-445</t>
   </si>
   <si>
@@ -7526,9 +7516,6 @@
     <t>DispDirectSaleRoadClosureSelect12</t>
   </si>
   <si>
-    <t>001-465-201</t>
-  </si>
-  <si>
     <t>ImprovementName</t>
   </si>
   <si>
@@ -7560,6 +7547,12 @@
   </si>
   <si>
     <t>Ana I Agner</t>
+  </si>
+  <si>
+    <t>012-562-602</t>
+  </si>
+  <si>
+    <t>013-215-469</t>
   </si>
 </sst>
 </file>
@@ -8581,13 +8574,13 @@
         <v>2088</v>
       </c>
       <c r="Z1" s="19" t="s">
-        <v>2477</v>
+        <v>2474</v>
       </c>
       <c r="AA1" s="19" t="s">
-        <v>2478</v>
+        <v>2475</v>
       </c>
       <c r="AB1" s="19" t="s">
-        <v>2479</v>
+        <v>2476</v>
       </c>
       <c r="AC1" s="19" t="s">
         <v>2089</v>
@@ -9044,10 +9037,10 @@
         <v>1415</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>2445</v>
+        <v>2442</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>2446</v>
+        <v>2443</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>1323</v>
@@ -9356,7 +9349,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -10376,13 +10369,13 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2443</v>
+        <v>2440</v>
       </c>
       <c r="B17" t="s">
         <v>246</v>
       </c>
       <c r="H17" t="s">
-        <v>2444</v>
+        <v>2441</v>
       </c>
       <c r="J17" t="s">
         <v>1277</v>
@@ -10426,18 +10419,18 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2452</v>
+        <v>2449</v>
       </c>
       <c r="B18" t="s">
         <v>246</v>
       </c>
       <c r="F18" s="4">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" t="s">
-        <v>2453</v>
+        <v>2450</v>
       </c>
       <c r="I18" t="s">
         <v>1331</v>
@@ -10809,7 +10802,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="B18">
         <v>71</v>
@@ -10820,12 +10813,12 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
     </row>
   </sheetData>
@@ -10885,7 +10878,7 @@
         <v>501</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2395</v>
+        <v>2392</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1867</v>
@@ -11202,7 +11195,7 @@
         <v>489</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>2396</v>
+        <v>2393</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36"/>
@@ -11417,7 +11410,7 @@
         <v>491</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
       <c r="I21" s="36"/>
       <c r="J21" s="36"/>
@@ -11655,7 +11648,7 @@
         <v>490</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>2398</v>
+        <v>2395</v>
       </c>
       <c r="I34" s="36"/>
       <c r="J34" s="36"/>
@@ -11885,7 +11878,7 @@
         <v>486</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>2399</v>
+        <v>2396</v>
       </c>
       <c r="I44" s="36"/>
       <c r="J44" s="36"/>
@@ -12055,7 +12048,7 @@
         <v>489</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="36">
@@ -12248,7 +12241,7 @@
         <v>486</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="36"/>
@@ -12370,7 +12363,7 @@
         <v>492</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>2402</v>
+        <v>2399</v>
       </c>
       <c r="I71" s="36"/>
       <c r="J71" s="36"/>
@@ -13570,10 +13563,10 @@
         <v>509</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>2419</v>
+        <v>2416</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>1626</v>
@@ -13678,7 +13671,7 @@
         <v>1619</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>2462</v>
+        <v>2459</v>
       </c>
       <c r="AW1" s="3" t="s">
         <v>1735</v>
@@ -14087,7 +14080,7 @@
         <v>1946</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>2420</v>
+        <v>2417</v>
       </c>
       <c r="N3" s="8">
         <v>4</v>
@@ -14445,7 +14438,7 @@
     </row>
     <row r="6" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="E6" t="s">
         <v>487</v>
@@ -14471,7 +14464,7 @@
         <v>190</v>
       </c>
       <c r="R6" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T6" t="s">
         <v>1682</v>
@@ -15086,7 +15079,7 @@
         <v>190</v>
       </c>
       <c r="R11" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T11" t="s">
         <v>1682</v>
@@ -15208,7 +15201,7 @@
         <v>190</v>
       </c>
       <c r="R12" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T12" t="s">
         <v>1682</v>
@@ -15333,7 +15326,7 @@
         <v>190</v>
       </c>
       <c r="R13" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T13" t="s">
         <v>1682</v>
@@ -15455,7 +15448,7 @@
         <v>190</v>
       </c>
       <c r="R14" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T14" t="s">
         <v>1682</v>
@@ -15577,7 +15570,7 @@
         <v>190</v>
       </c>
       <c r="R15" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T15" t="s">
         <v>1682</v>
@@ -15705,7 +15698,7 @@
         <v>190</v>
       </c>
       <c r="R16" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T16" t="s">
         <v>1682</v>
@@ -15832,7 +15825,7 @@
         <v>190</v>
       </c>
       <c r="R17" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T17" t="s">
         <v>1682</v>
@@ -15959,7 +15952,7 @@
         <v>190</v>
       </c>
       <c r="R18" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T18" t="s">
         <v>1682</v>
@@ -16060,7 +16053,7 @@
     </row>
     <row r="19" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="B19" t="s">
         <v>980</v>
@@ -16194,7 +16187,7 @@
     </row>
     <row r="20" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="E20" t="s">
         <v>487</v>
@@ -16313,7 +16306,7 @@
     </row>
     <row r="21" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
       <c r="E21" t="s">
         <v>246</v>
@@ -16448,7 +16441,7 @@
     </row>
     <row r="22" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
       <c r="E22" t="s">
         <v>246</v>
@@ -16561,7 +16554,7 @@
     </row>
     <row r="23" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="E23" t="s">
         <v>246</v>
@@ -16696,7 +16689,7 @@
     </row>
     <row r="24" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
       <c r="E24" t="s">
         <v>246</v>
@@ -16831,7 +16824,7 @@
     </row>
     <row r="25" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
       <c r="E25" t="s">
         <v>246</v>
@@ -16949,7 +16942,7 @@
     </row>
     <row r="26" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="E26" t="s">
         <v>246</v>
@@ -17164,7 +17157,7 @@
     </row>
     <row r="27" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="E27" t="s">
         <v>246</v>
@@ -17290,7 +17283,7 @@
     </row>
     <row r="28" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
       <c r="E28" t="s">
         <v>246</v>
@@ -17428,7 +17421,7 @@
     </row>
     <row r="29" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="F29" s="4"/>
       <c r="J29" s="4"/>
@@ -17543,7 +17536,7 @@
     </row>
     <row r="30" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="E30" t="s">
         <v>246</v>
@@ -17678,7 +17671,7 @@
     </row>
     <row r="31" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2377</v>
+        <v>2374</v>
       </c>
       <c r="F31" s="4"/>
       <c r="J31" s="4"/>
@@ -17790,7 +17783,7 @@
     </row>
     <row r="32" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
       <c r="N32" s="8">
         <v>0</v>
@@ -17799,7 +17792,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="AC32" t="s">
         <v>295</v>
@@ -17920,7 +17913,7 @@
         <v>190</v>
       </c>
       <c r="R33" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="T33" t="s">
         <v>1682</v>
@@ -18013,7 +18006,7 @@
     </row>
     <row r="34" spans="1:89" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
       <c r="E34" t="s">
         <v>487</v>
@@ -20359,7 +20352,7 @@
         <v>2165</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2410</v>
+        <v>2407</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>2166</v>
@@ -20368,7 +20361,7 @@
         <v>2167</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>2411</v>
+        <v>2408</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>2168</v>
@@ -20377,16 +20370,16 @@
         <v>2169</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>2412</v>
+        <v>2409</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>2413</v>
+        <v>2410</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>2170</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>2274</v>
@@ -20436,10 +20429,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>2414</v>
+        <v>2411</v>
       </c>
       <c r="P2" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -20495,10 +20488,10 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>2415</v>
+        <v>2412</v>
       </c>
       <c r="P3" t="s">
-        <v>2417</v>
+        <v>2414</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -20771,13 +20764,13 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="B12" t="s">
         <v>487</v>
       </c>
       <c r="G12" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="J12" t="s">
         <v>1754</v>
@@ -21205,15 +21198,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="B14" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="B15" t="s">
         <v>2226</v>
@@ -22960,13 +22953,13 @@
         <v>1549</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>2404</v>
+        <v>2401</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>2458</v>
+        <v>2455</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>2459</v>
+        <v>2456</v>
       </c>
       <c r="AA1" s="3" t="s">
         <v>1550</v>
@@ -22981,19 +22974,19 @@
         <v>1553</v>
       </c>
       <c r="AE1" s="3" t="s">
+        <v>2418</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>2419</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AH1" s="3" t="s">
         <v>2421</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>2422</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>2424</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>2425</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
@@ -23149,7 +23142,7 @@
         <v>1243</v>
       </c>
       <c r="W4" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="AA4" s="30">
         <v>65.898600000000002</v>
@@ -23208,13 +23201,13 @@
         <v>694</v>
       </c>
       <c r="X5" t="s">
-        <v>2455</v>
+        <v>2452</v>
       </c>
       <c r="Y5" t="s">
-        <v>2460</v>
+        <v>2457</v>
       </c>
       <c r="Z5" t="s">
-        <v>2461</v>
+        <v>2458</v>
       </c>
       <c r="AA5" s="30">
         <v>89.87</v>
@@ -23229,13 +23222,13 @@
         <v>670</v>
       </c>
       <c r="AE5" t="s">
-        <v>2456</v>
+        <v>2453</v>
       </c>
       <c r="AF5" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="AG5" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -23317,7 +23310,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2428</v>
+        <v>2425</v>
       </c>
       <c r="B7" t="s">
         <v>1568</v>
@@ -23436,67 +23429,67 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2427</v>
+        <v>2424</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2482</v>
+        <v>2478</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2483</v>
+        <v>2479</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2426</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2429</v>
+        <v>2426</v>
       </c>
       <c r="B2" t="s">
-        <v>2484</v>
+        <v>2480</v>
       </c>
       <c r="C2" t="s">
-        <v>2431</v>
+        <v>2428</v>
       </c>
       <c r="D2" t="s">
         <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="F2" t="s">
-        <v>2433</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C3" t="s">
         <v>2429</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2485</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2432</v>
       </c>
       <c r="D3" t="s">
         <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>2488</v>
+        <v>2484</v>
       </c>
       <c r="F3" t="s">
-        <v>2434</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2429</v>
+        <v>2426</v>
       </c>
       <c r="B4" t="s">
-        <v>2486</v>
+        <v>2482</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -23505,30 +23498,30 @@
         <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>2489</v>
+        <v>2485</v>
       </c>
       <c r="F4" t="s">
-        <v>2435</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2430</v>
+        <v>2427</v>
       </c>
       <c r="B5" t="s">
-        <v>2487</v>
+        <v>2483</v>
       </c>
       <c r="C5" t="s">
-        <v>2432</v>
+        <v>2429</v>
       </c>
       <c r="D5" t="s">
         <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>2490</v>
+        <v>2486</v>
       </c>
       <c r="F5" t="s">
-        <v>2436</v>
+        <v>2433</v>
       </c>
     </row>
   </sheetData>
@@ -23881,7 +23874,7 @@
         <v>1161</v>
       </c>
       <c r="D2" t="s">
-        <v>2386</v>
+        <v>2383</v>
       </c>
       <c r="E2" t="s">
         <v>1185</v>
@@ -23896,7 +23889,7 @@
         <v>2125</v>
       </c>
       <c r="J2" t="s">
-        <v>2381</v>
+        <v>2378</v>
       </c>
       <c r="K2" t="s">
         <v>1167</v>
@@ -23934,7 +23927,7 @@
         <v>1162</v>
       </c>
       <c r="D3" t="s">
-        <v>2387</v>
+        <v>2384</v>
       </c>
       <c r="E3" t="s">
         <v>1163</v>
@@ -23949,7 +23942,7 @@
         <v>1166</v>
       </c>
       <c r="J3" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="K3" t="s">
         <v>2124</v>
@@ -24002,7 +23995,7 @@
         <v>1195</v>
       </c>
       <c r="J4" t="s">
-        <v>2491</v>
+        <v>2487</v>
       </c>
       <c r="K4" t="s">
         <v>1197</v>
@@ -24040,7 +24033,7 @@
         <v>1250</v>
       </c>
       <c r="D5" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="E5" t="s">
         <v>1185</v>
@@ -24055,7 +24048,7 @@
         <v>2191</v>
       </c>
       <c r="J5" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -24102,13 +24095,13 @@
         <v>2301</v>
       </c>
       <c r="J6" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
       <c r="K6" t="s">
         <v>2302</v>
       </c>
       <c r="L6" t="s">
-        <v>2463</v>
+        <v>2460</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -24158,10 +24151,10 @@
         <v>2272</v>
       </c>
       <c r="J7" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
       <c r="K7" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="L7" s="14" t="s">
         <v>2280</v>
@@ -24208,13 +24201,13 @@
         <v>2271</v>
       </c>
       <c r="I8" t="s">
-        <v>2390</v>
+        <v>2387</v>
       </c>
       <c r="J8" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="K8" t="s">
-        <v>2392</v>
+        <v>2389</v>
       </c>
       <c r="L8" t="s">
         <v>2281</v>
@@ -24637,10 +24630,10 @@
         <v>770</v>
       </c>
       <c r="AH1" s="38" t="s">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="AI1" s="38" t="s">
-        <v>2406</v>
+        <v>2403</v>
       </c>
       <c r="AJ1" s="38" t="s">
         <v>1303</v>
@@ -24789,10 +24782,10 @@
         <v>768</v>
       </c>
       <c r="AH2" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="AI2" t="s">
-        <v>2408</v>
+        <v>2405</v>
       </c>
       <c r="AJ2">
         <v>15</v>
@@ -24882,7 +24875,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -24930,10 +24923,10 @@
         <v>981</v>
       </c>
       <c r="AH3" t="s">
-        <v>2454</v>
+        <v>2451</v>
       </c>
       <c r="AI3" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -25126,7 +25119,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -25351,7 +25344,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -25924,7 +25917,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -26267,7 +26260,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -27940,10 +27933,10 @@
         <v>2326</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>2403</v>
+        <v>2400</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -27981,7 +27974,7 @@
         <v>2259</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -27989,7 +27982,7 @@
         <v>325</v>
       </c>
       <c r="H3" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -27997,7 +27990,7 @@
         <v>278</v>
       </c>
       <c r="D4" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -28005,7 +27998,7 @@
         <v>276</v>
       </c>
       <c r="B5" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -28097,7 +28090,7 @@
         <v>1289</v>
       </c>
       <c r="G12" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="I12">
         <v>49</v>
@@ -28124,10 +28117,10 @@
         <v>2259</v>
       </c>
       <c r="Q12" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="V12" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -28177,7 +28170,7 @@
         <v>2327</v>
       </c>
       <c r="V16" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
@@ -28275,13 +28268,13 @@
         <v>1727</v>
       </c>
       <c r="F26" t="s">
+        <v>2335</v>
+      </c>
+      <c r="H26" t="s">
         <v>2336</v>
       </c>
-      <c r="H26" t="s">
-        <v>2337</v>
-      </c>
       <c r="V26" t="s">
-        <v>2464</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
@@ -28326,7 +28319,7 @@
         <v>1309</v>
       </c>
       <c r="F29" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
@@ -28360,13 +28353,10 @@
         <v>2137</v>
       </c>
       <c r="B32" t="s">
-        <v>2480</v>
-      </c>
-      <c r="E32" t="s">
-        <v>2334</v>
+        <v>2489</v>
       </c>
       <c r="V32" t="s">
-        <v>2480</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -28377,7 +28367,7 @@
         <v>2141</v>
       </c>
       <c r="F33" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="V33" s="14" t="s">
         <v>2141</v>
@@ -28405,7 +28395,7 @@
         <v>90172682</v>
       </c>
       <c r="D35" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="E35" t="s">
         <v>2194</v>
@@ -28435,7 +28425,7 @@
         <v>2259</v>
       </c>
       <c r="V35" t="s">
-        <v>2394</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
@@ -28453,12 +28443,11 @@
       <c r="A37" s="52" t="s">
         <v>2305</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="E37" t="s">
-        <v>2339</v>
-      </c>
-      <c r="V37" t="s">
-        <v>2365</v>
+      <c r="B37" s="14" t="s">
+        <v>2488</v>
+      </c>
+      <c r="V37" s="14" t="s">
+        <v>2488</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -28474,37 +28463,37 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="B39" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="V39" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="52" t="s">
-        <v>2437</v>
+        <v>2434</v>
       </c>
       <c r="E40" t="s">
-        <v>2438</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="52" t="s">
-        <v>2439</v>
+        <v>2436</v>
       </c>
       <c r="E41" t="s">
-        <v>2440</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="52" t="s">
-        <v>2441</v>
+        <v>2438</v>
       </c>
       <c r="B42" t="s">
-        <v>2442</v>
+        <v>2439</v>
       </c>
     </row>
   </sheetData>
@@ -31866,10 +31855,10 @@
         <v>487</v>
       </c>
       <c r="H2" t="s">
-        <v>2466</v>
+        <v>2463</v>
       </c>
       <c r="I2" t="s">
-        <v>2474</v>
+        <v>2471</v>
       </c>
       <c r="J2" s="4">
         <v>44440</v>
@@ -31913,10 +31902,10 @@
         <v>487</v>
       </c>
       <c r="H3" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
       <c r="I3" t="s">
-        <v>2475</v>
+        <v>2472</v>
       </c>
       <c r="J3" s="4">
         <v>44806</v>
@@ -31957,10 +31946,10 @@
         <v>492</v>
       </c>
       <c r="G4" t="s">
+        <v>2462</v>
+      </c>
+      <c r="H4" t="s">
         <v>2465</v>
-      </c>
-      <c r="H4" t="s">
-        <v>2468</v>
       </c>
       <c r="I4" t="s">
         <v>796</v>
@@ -32004,7 +31993,7 @@
         <v>487</v>
       </c>
       <c r="H5" t="s">
-        <v>2469</v>
+        <v>2466</v>
       </c>
       <c r="I5" t="s">
         <v>797</v>
@@ -32048,7 +32037,7 @@
         <v>487</v>
       </c>
       <c r="H6" t="s">
-        <v>2470</v>
+        <v>2467</v>
       </c>
       <c r="I6" t="s">
         <v>794</v>
@@ -32092,7 +32081,7 @@
         <v>487</v>
       </c>
       <c r="H7" t="s">
-        <v>2470</v>
+        <v>2467</v>
       </c>
       <c r="I7" t="s">
         <v>794</v>
@@ -32136,10 +32125,10 @@
         <v>487</v>
       </c>
       <c r="H8" t="s">
-        <v>2471</v>
+        <v>2468</v>
       </c>
       <c r="I8" t="s">
-        <v>2476</v>
+        <v>2473</v>
       </c>
       <c r="J8" s="4">
         <v>45265</v>
@@ -32165,25 +32154,25 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="B9" t="s">
         <v>487</v>
       </c>
       <c r="D9" t="s">
-        <v>2449</v>
+        <v>2446</v>
       </c>
       <c r="E9" t="s">
-        <v>2451</v>
+        <v>2448</v>
       </c>
       <c r="F9" t="s">
         <v>487</v>
       </c>
       <c r="H9" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
       <c r="I9" t="s">
-        <v>2451</v>
+        <v>2448</v>
       </c>
       <c r="J9" s="4">
         <v>45658</v>
@@ -32209,25 +32198,25 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2448</v>
+        <v>2445</v>
       </c>
       <c r="B10" t="s">
         <v>487</v>
       </c>
       <c r="D10" t="s">
-        <v>2450</v>
+        <v>2447</v>
       </c>
       <c r="E10" t="s">
-        <v>2451</v>
+        <v>2448</v>
       </c>
       <c r="F10" t="s">
         <v>487</v>
       </c>
       <c r="H10" t="s">
-        <v>2473</v>
+        <v>2470</v>
       </c>
       <c r="I10" t="s">
-        <v>2451</v>
+        <v>2448</v>
       </c>
       <c r="J10" s="4">
         <v>45690</v>
@@ -32800,7 +32789,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="B10" s="37"/>
       <c r="E10" t="s">
@@ -32813,7 +32802,7 @@
         <v>45569</v>
       </c>
       <c r="K10" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="L10" t="s">
         <v>1530</v>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD03F98A-7138-4FB8-86B6-E417405C8E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4768597-B1D0-4672-A7BE-9076FCEC39CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="26" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="30" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AcquisitionChecklist" sheetId="22" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4511" uniqueCount="2490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4517" uniqueCount="2491">
   <si>
     <t>FirstName</t>
   </si>
@@ -7006,9 +7006,6 @@
     <t>675 davie</t>
   </si>
   <si>
-    <t>1253 bradshaw</t>
-  </si>
-  <si>
     <t>MF Property Digital Documents and Props Documents</t>
   </si>
   <si>
@@ -7168,9 +7165,6 @@
     <t>DisplayingList</t>
   </si>
   <si>
-    <t>015-279-511;028-175-913;018-353-690</t>
-  </si>
-  <si>
     <t>010-764-135;015-069-940;007-095-333</t>
   </si>
   <si>
@@ -7553,6 +7547,15 @@
   </si>
   <si>
     <t>013-215-469</t>
+  </si>
+  <si>
+    <t>Crossing Agreement</t>
+  </si>
+  <si>
+    <t>1818 West Mall</t>
+  </si>
+  <si>
+    <t>015-279-511;015-891-909;018-353-690</t>
   </si>
 </sst>
 </file>
@@ -8486,8 +8489,8 @@
     <col min="6" max="9" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="16" width="30.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="23" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="31.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="31.21875" customWidth="1"/>
+    <col min="24" max="25" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="31.33203125" customWidth="1"/>
     <col min="29" max="29" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="32" max="33" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -8574,13 +8577,13 @@
         <v>2088</v>
       </c>
       <c r="Z1" s="19" t="s">
+        <v>2472</v>
+      </c>
+      <c r="AA1" s="19" t="s">
+        <v>2473</v>
+      </c>
+      <c r="AB1" s="19" t="s">
         <v>2474</v>
-      </c>
-      <c r="AA1" s="19" t="s">
-        <v>2475</v>
-      </c>
-      <c r="AB1" s="19" t="s">
-        <v>2476</v>
       </c>
       <c r="AC1" s="19" t="s">
         <v>2089</v>
@@ -9037,10 +9040,10 @@
         <v>1415</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>1323</v>
@@ -9349,7 +9352,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -10369,13 +10372,13 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="B17" t="s">
         <v>246</v>
       </c>
       <c r="H17" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="J17" t="s">
         <v>1277</v>
@@ -10419,18 +10422,18 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="B18" t="s">
         <v>246</v>
       </c>
       <c r="F18" s="4">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="I18" t="s">
         <v>1331</v>
@@ -10791,7 +10794,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B17">
         <v>71</v>
@@ -10802,7 +10805,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="B18">
         <v>71</v>
@@ -10813,12 +10816,12 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
     </row>
   </sheetData>
@@ -10878,7 +10881,7 @@
         <v>501</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1867</v>
@@ -11195,7 +11198,7 @@
         <v>489</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36"/>
@@ -11410,7 +11413,7 @@
         <v>491</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="I21" s="36"/>
       <c r="J21" s="36"/>
@@ -11648,7 +11651,7 @@
         <v>490</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="I34" s="36"/>
       <c r="J34" s="36"/>
@@ -11878,7 +11881,7 @@
         <v>486</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="I44" s="36"/>
       <c r="J44" s="36"/>
@@ -12048,7 +12051,7 @@
         <v>489</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="36">
@@ -12241,7 +12244,7 @@
         <v>486</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="36"/>
@@ -12363,7 +12366,7 @@
         <v>492</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="I71" s="36"/>
       <c r="J71" s="36"/>
@@ -12389,7 +12392,7 @@
     </row>
     <row r="72" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="B72" t="s">
         <v>710</v>
@@ -12398,12 +12401,12 @@
         <v>486</v>
       </c>
       <c r="AW72" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="73" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B73" t="s">
         <v>452</v>
@@ -12412,13 +12415,13 @@
         <v>487</v>
       </c>
       <c r="G73" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="V73" t="s">
         <v>2211</v>
       </c>
       <c r="AU73" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="BB73">
         <v>2025</v>
@@ -12426,7 +12429,7 @@
     </row>
     <row r="74" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="B74" t="s">
         <v>454</v>
@@ -12435,10 +12438,10 @@
         <v>488</v>
       </c>
       <c r="F74" t="s">
+        <v>2315</v>
+      </c>
+      <c r="U74" t="s">
         <v>2316</v>
-      </c>
-      <c r="U74" t="s">
-        <v>2317</v>
       </c>
     </row>
   </sheetData>
@@ -13563,10 +13566,10 @@
         <v>509</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>1626</v>
@@ -13671,7 +13674,7 @@
         <v>1619</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="AW1" s="3" t="s">
         <v>1735</v>
@@ -14068,7 +14071,7 @@
         <v>45495</v>
       </c>
       <c r="I3" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J3" s="4">
         <v>44614</v>
@@ -14080,7 +14083,7 @@
         <v>1946</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="N3" s="8">
         <v>4</v>
@@ -14088,8 +14091,14 @@
       <c r="O3" s="8">
         <v>1</v>
       </c>
+      <c r="Q3" t="s">
+        <v>192</v>
+      </c>
       <c r="R3" t="s">
         <v>634</v>
+      </c>
+      <c r="T3" t="s">
+        <v>2488</v>
       </c>
       <c r="V3" t="s">
         <v>1725</v>
@@ -14438,13 +14447,13 @@
     </row>
     <row r="6" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="E6" t="s">
         <v>487</v>
       </c>
       <c r="I6" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J6" s="4">
         <v>45064</v>
@@ -14464,7 +14473,7 @@
         <v>190</v>
       </c>
       <c r="R6" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T6" t="s">
         <v>1682</v>
@@ -14823,7 +14832,7 @@
         <v>487</v>
       </c>
       <c r="I9" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J9" s="4">
         <v>45209</v>
@@ -14948,7 +14957,7 @@
         <v>487</v>
       </c>
       <c r="I10" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J10" s="4">
         <v>45209</v>
@@ -15079,7 +15088,7 @@
         <v>190</v>
       </c>
       <c r="R11" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T11" t="s">
         <v>1682</v>
@@ -15201,7 +15210,7 @@
         <v>190</v>
       </c>
       <c r="R12" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T12" t="s">
         <v>1682</v>
@@ -15326,7 +15335,7 @@
         <v>190</v>
       </c>
       <c r="R13" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T13" t="s">
         <v>1682</v>
@@ -15448,7 +15457,7 @@
         <v>190</v>
       </c>
       <c r="R14" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T14" t="s">
         <v>1682</v>
@@ -15570,7 +15579,7 @@
         <v>190</v>
       </c>
       <c r="R15" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T15" t="s">
         <v>1682</v>
@@ -15698,7 +15707,7 @@
         <v>190</v>
       </c>
       <c r="R16" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T16" t="s">
         <v>1682</v>
@@ -15825,7 +15834,7 @@
         <v>190</v>
       </c>
       <c r="R17" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T17" t="s">
         <v>1682</v>
@@ -15952,7 +15961,7 @@
         <v>190</v>
       </c>
       <c r="R18" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T18" t="s">
         <v>1682</v>
@@ -16053,7 +16062,7 @@
     </row>
     <row r="19" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="B19" t="s">
         <v>980</v>
@@ -16068,7 +16077,7 @@
         <v>487</v>
       </c>
       <c r="I19" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J19" s="4">
         <v>45209</v>
@@ -16187,13 +16196,13 @@
     </row>
     <row r="20" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="E20" t="s">
         <v>487</v>
       </c>
       <c r="I20" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -16306,7 +16315,7 @@
     </row>
     <row r="21" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="E21" t="s">
         <v>246</v>
@@ -16441,7 +16450,7 @@
     </row>
     <row r="22" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="E22" t="s">
         <v>246</v>
@@ -16554,7 +16563,7 @@
     </row>
     <row r="23" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="E23" t="s">
         <v>246</v>
@@ -16689,7 +16698,7 @@
     </row>
     <row r="24" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="E24" t="s">
         <v>246</v>
@@ -16824,7 +16833,7 @@
     </row>
     <row r="25" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="E25" t="s">
         <v>246</v>
@@ -16942,7 +16951,7 @@
     </row>
     <row r="26" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="E26" t="s">
         <v>246</v>
@@ -17157,7 +17166,7 @@
     </row>
     <row r="27" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="E27" t="s">
         <v>246</v>
@@ -17283,7 +17292,7 @@
     </row>
     <row r="28" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="E28" t="s">
         <v>246</v>
@@ -17421,7 +17430,7 @@
     </row>
     <row r="29" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="F29" s="4"/>
       <c r="J29" s="4"/>
@@ -17536,7 +17545,7 @@
     </row>
     <row r="30" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="E30" t="s">
         <v>246</v>
@@ -17671,7 +17680,7 @@
     </row>
     <row r="31" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="F31" s="4"/>
       <c r="J31" s="4"/>
@@ -17783,7 +17792,7 @@
     </row>
     <row r="32" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="N32" s="8">
         <v>0</v>
@@ -17792,7 +17801,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="AC32" t="s">
         <v>295</v>
@@ -17893,7 +17902,7 @@
         <v>487</v>
       </c>
       <c r="I33" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J33" s="4">
         <v>45064</v>
@@ -17913,7 +17922,7 @@
         <v>190</v>
       </c>
       <c r="R33" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="T33" t="s">
         <v>1682</v>
@@ -18006,13 +18015,13 @@
     </row>
     <row r="34" spans="1:89" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="E34" t="s">
         <v>487</v>
       </c>
       <c r="I34" t="s">
-        <v>2320</v>
+        <v>567</v>
       </c>
       <c r="J34" s="4">
         <v>45064</v>
@@ -20352,7 +20361,7 @@
         <v>2165</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>2166</v>
@@ -20361,7 +20370,7 @@
         <v>2167</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>2168</v>
@@ -20370,16 +20379,16 @@
         <v>2169</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>2170</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>2274</v>
@@ -20429,10 +20438,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
+        <v>2409</v>
+      </c>
+      <c r="P2" t="s">
         <v>2411</v>
-      </c>
-      <c r="P2" t="s">
-        <v>2413</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -20488,10 +20497,10 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
+        <v>2410</v>
+      </c>
+      <c r="P3" t="s">
         <v>2412</v>
-      </c>
-      <c r="P3" t="s">
-        <v>2414</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -20764,13 +20773,13 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="B12" t="s">
         <v>487</v>
       </c>
       <c r="G12" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="J12" t="s">
         <v>1754</v>
@@ -21198,15 +21207,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B14" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B15" t="s">
         <v>2226</v>
@@ -22858,7 +22867,7 @@
     <col min="23" max="23" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -22953,13 +22962,13 @@
         <v>1549</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="AA1" s="3" t="s">
         <v>1550</v>
@@ -22974,19 +22983,19 @@
         <v>1553</v>
       </c>
       <c r="AE1" s="3" t="s">
+        <v>2416</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>2417</v>
+      </c>
+      <c r="AG1" s="3" t="s">
         <v>2418</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>2419</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>2420</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>2421</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>2422</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
@@ -23002,6 +23011,9 @@
       <c r="M2">
         <v>0</v>
       </c>
+      <c r="O2" t="s">
+        <v>190</v>
+      </c>
       <c r="AB2" s="16" t="b">
         <v>1</v>
       </c>
@@ -23142,7 +23154,7 @@
         <v>1243</v>
       </c>
       <c r="W4" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="AA4" s="30">
         <v>65.898600000000002</v>
@@ -23201,13 +23213,13 @@
         <v>694</v>
       </c>
       <c r="X5" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="Y5" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="Z5" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="AA5" s="30">
         <v>89.87</v>
@@ -23222,13 +23234,13 @@
         <v>670</v>
       </c>
       <c r="AE5" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="AF5" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="AG5" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -23310,7 +23322,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="B7" t="s">
         <v>1568</v>
@@ -23321,11 +23333,20 @@
       <c r="M7">
         <v>0</v>
       </c>
+      <c r="O7" t="s">
+        <v>190</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="AA7" s="30">
+        <v>65.898600000000002</v>
+      </c>
       <c r="AB7" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="AC7" s="32" t="s">
+        <v>1597</v>
       </c>
       <c r="AD7" t="s">
         <v>268</v>
@@ -23417,8 +23438,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -23429,67 +23449,67 @@
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2422</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2477</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2424</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2478</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>2479</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C2" t="s">
         <v>2426</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2480</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2428</v>
       </c>
       <c r="D2" t="s">
         <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="F2" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B3" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="C3" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="D3" t="s">
         <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="F3" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B4" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -23498,30 +23518,30 @@
         <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="F4" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C5" t="s">
         <v>2427</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2483</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2429</v>
       </c>
       <c r="D5" t="s">
         <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="F5" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
     </row>
   </sheetData>
@@ -23874,7 +23894,7 @@
         <v>1161</v>
       </c>
       <c r="D2" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="E2" t="s">
         <v>1185</v>
@@ -23889,7 +23909,7 @@
         <v>2125</v>
       </c>
       <c r="J2" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="K2" t="s">
         <v>1167</v>
@@ -23927,7 +23947,7 @@
         <v>1162</v>
       </c>
       <c r="D3" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="E3" t="s">
         <v>1163</v>
@@ -23942,7 +23962,7 @@
         <v>1166</v>
       </c>
       <c r="J3" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="K3" t="s">
         <v>2124</v>
@@ -23995,7 +24015,7 @@
         <v>1195</v>
       </c>
       <c r="J4" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="K4" t="s">
         <v>1197</v>
@@ -24033,7 +24053,7 @@
         <v>1250</v>
       </c>
       <c r="D5" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="E5" t="s">
         <v>1185</v>
@@ -24048,7 +24068,7 @@
         <v>2191</v>
       </c>
       <c r="J5" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -24095,13 +24115,13 @@
         <v>2301</v>
       </c>
       <c r="J6" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="K6" t="s">
         <v>2302</v>
       </c>
       <c r="L6" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -24151,10 +24171,10 @@
         <v>2272</v>
       </c>
       <c r="J7" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="K7" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="L7" s="14" t="s">
         <v>2280</v>
@@ -24201,13 +24221,13 @@
         <v>2271</v>
       </c>
       <c r="I8" t="s">
+        <v>2385</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2386</v>
+      </c>
+      <c r="K8" t="s">
         <v>2387</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2388</v>
-      </c>
-      <c r="K8" t="s">
-        <v>2389</v>
       </c>
       <c r="L8" t="s">
         <v>2281</v>
@@ -24630,10 +24650,10 @@
         <v>770</v>
       </c>
       <c r="AH1" s="38" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="AI1" s="38" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="AJ1" s="38" t="s">
         <v>1303</v>
@@ -24782,10 +24802,10 @@
         <v>768</v>
       </c>
       <c r="AH2" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="AI2" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="AJ2">
         <v>15</v>
@@ -24875,7 +24895,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -24923,10 +24943,10 @@
         <v>981</v>
       </c>
       <c r="AH3" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="AI3" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -25119,7 +25139,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -25344,7 +25364,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -25917,7 +25937,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -26260,7 +26280,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -27888,13 +27908,13 @@
         <v>239</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1471</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2250</v>
@@ -27921,22 +27941,22 @@
         <v>2257</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>2323</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>2324</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>2325</v>
       </c>
-      <c r="T1" s="3" t="s">
-        <v>2326</v>
-      </c>
       <c r="U1" s="3" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -27947,7 +27967,7 @@
         <v>4361431</v>
       </c>
       <c r="D2" t="s">
-        <v>2307</v>
+        <v>2489</v>
       </c>
       <c r="I2">
         <v>48</v>
@@ -27974,7 +27994,7 @@
         <v>2259</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>2361</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -27982,7 +28002,7 @@
         <v>325</v>
       </c>
       <c r="H3" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -27990,7 +28010,7 @@
         <v>278</v>
       </c>
       <c r="D4" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -27998,7 +28018,7 @@
         <v>276</v>
       </c>
       <c r="B5" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -28090,7 +28110,7 @@
         <v>1289</v>
       </c>
       <c r="G12" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="I12">
         <v>49</v>
@@ -28117,10 +28137,10 @@
         <v>2259</v>
       </c>
       <c r="Q12" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="V12" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -28158,19 +28178,19 @@
         <v>1821391</v>
       </c>
       <c r="D16" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="E16" t="s">
         <v>1714</v>
       </c>
       <c r="H16" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="Q16" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="V16" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
@@ -28268,13 +28288,13 @@
         <v>1727</v>
       </c>
       <c r="F26" t="s">
+        <v>2334</v>
+      </c>
+      <c r="H26" t="s">
         <v>2335</v>
       </c>
-      <c r="H26" t="s">
-        <v>2336</v>
-      </c>
       <c r="V26" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
@@ -28311,7 +28331,7 @@
         <v>1308</v>
       </c>
       <c r="H28" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
@@ -28319,7 +28339,7 @@
         <v>1309</v>
       </c>
       <c r="F29" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
@@ -28353,10 +28373,10 @@
         <v>2137</v>
       </c>
       <c r="B32" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="V32" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -28367,7 +28387,7 @@
         <v>2141</v>
       </c>
       <c r="F33" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="V33" s="14" t="s">
         <v>2141</v>
@@ -28395,7 +28415,7 @@
         <v>90172682</v>
       </c>
       <c r="D35" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="E35" t="s">
         <v>2194</v>
@@ -28425,7 +28445,7 @@
         <v>2259</v>
       </c>
       <c r="V35" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
@@ -28444,15 +28464,15 @@
         <v>2305</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="V37" s="14" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="B38" t="s">
         <v>2193</v>
@@ -28463,37 +28483,37 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B39" t="s">
         <v>2355</v>
       </c>
-      <c r="B39" t="s">
-        <v>2356</v>
-      </c>
       <c r="V39" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="52" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="E40" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="52" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="E41" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="52" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="B42" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
     </row>
   </sheetData>
@@ -30656,7 +30676,7 @@
         <v>650</v>
       </c>
       <c r="B2" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="C2" t="s">
         <v>250</v>
@@ -30746,7 +30766,7 @@
         <v>863</v>
       </c>
       <c r="B8" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="C8" t="s">
         <v>864</v>
@@ -30777,7 +30797,7 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>1061</v>
@@ -30791,7 +30811,7 @@
         <v>1209</v>
       </c>
       <c r="B11" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="C11" t="s">
         <v>2102</v>
@@ -30819,7 +30839,7 @@
         <v>1312</v>
       </c>
       <c r="B13" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="C13" t="s">
         <v>1313</v>
@@ -30833,7 +30853,7 @@
         <v>1312</v>
       </c>
       <c r="B14" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="C14" t="s">
         <v>1314</v>
@@ -31776,8 +31796,8 @@
     <col min="4" max="4" width="46.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.21875" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
     <col min="9" max="9" width="50.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
@@ -31855,10 +31875,10 @@
         <v>487</v>
       </c>
       <c r="H2" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="I2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="J2" s="4">
         <v>44440</v>
@@ -31902,10 +31922,10 @@
         <v>487</v>
       </c>
       <c r="H3" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="I3" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="J3" s="4">
         <v>44806</v>
@@ -31946,10 +31966,10 @@
         <v>492</v>
       </c>
       <c r="G4" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="H4" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="I4" t="s">
         <v>796</v>
@@ -31993,7 +32013,7 @@
         <v>487</v>
       </c>
       <c r="H5" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="I5" t="s">
         <v>797</v>
@@ -32037,7 +32057,7 @@
         <v>487</v>
       </c>
       <c r="H6" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="I6" t="s">
         <v>794</v>
@@ -32081,7 +32101,7 @@
         <v>487</v>
       </c>
       <c r="H7" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="I7" t="s">
         <v>794</v>
@@ -32125,10 +32145,10 @@
         <v>487</v>
       </c>
       <c r="H8" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="I8" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="J8" s="4">
         <v>45265</v>
@@ -32154,25 +32174,25 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="B9" t="s">
         <v>487</v>
       </c>
       <c r="D9" t="s">
+        <v>2444</v>
+      </c>
+      <c r="E9" t="s">
         <v>2446</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2448</v>
       </c>
       <c r="F9" t="s">
         <v>487</v>
       </c>
       <c r="H9" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="I9" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="J9" s="4">
         <v>45658</v>
@@ -32198,25 +32218,25 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="B10" t="s">
         <v>487</v>
       </c>
       <c r="D10" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="E10" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="F10" t="s">
         <v>487</v>
       </c>
       <c r="H10" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="I10" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="J10" s="4">
         <v>45690</v>
@@ -32390,7 +32410,7 @@
         <v>858</v>
       </c>
       <c r="P2" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="Q2" t="s">
         <v>2104</v>
@@ -32431,7 +32451,7 @@
         <v>974</v>
       </c>
       <c r="P3" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="Q3" t="s">
         <v>2105</v>
@@ -32493,7 +32513,7 @@
         <v>858</v>
       </c>
       <c r="P4" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="Q4" t="s">
         <v>2102</v>
@@ -32655,7 +32675,7 @@
         <v>858</v>
       </c>
       <c r="P7" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="Q7" t="s">
         <v>2106</v>
@@ -32789,7 +32809,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B10" s="37"/>
       <c r="E10" t="s">
@@ -32802,7 +32822,7 @@
         <v>45569</v>
       </c>
       <c r="K10" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="L10" t="s">
         <v>1530</v>

--- a/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
+++ b/testing/PIMS.Tests.Automation/Data/PIMS_Testing_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\testing\PIMS.Tests.Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4768597-B1D0-4672-A7BE-9076FCEC39CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0892DB49-77FF-46E7-9120-A4237B71DCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="945" firstSheet="30" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="2124" windowWidth="23256" windowHeight="13896" tabRatio="945" firstSheet="35" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AcquisitionChecklist" sheetId="22" r:id="rId1"/>
@@ -7390,9 +7390,6 @@
     <t>Highway and Other Property Tabs</t>
   </si>
   <si>
-    <t>LMP16339</t>
-  </si>
-  <si>
     <t>PMBC and Crown Property Tabs</t>
   </si>
   <si>
@@ -7556,6 +7553,9 @@
   </si>
   <si>
     <t>015-279-511;015-891-909;018-353-690</t>
+  </si>
+  <si>
+    <t>NWP68848</t>
   </si>
 </sst>
 </file>
@@ -8020,21 +8020,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD9027E-311F-43F3-971B-D6244D52A1F4}">
   <dimension ref="A1:AV3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="23" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="35" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="44" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="26.5546875" customWidth="1"/>
-    <col min="48" max="48" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="35" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="44" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="26.5703125" customWidth="1"/>
+    <col min="48" max="48" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -8180,7 +8180,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>762</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1218</v>
       </c>
@@ -8482,25 +8482,25 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB97DE91-D06A-49E3-B99F-D9DAA9CCEAD0}">
   <dimension ref="A1:AM4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="23" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="31.33203125" customWidth="1"/>
-    <col min="29" max="29" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="23" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="31.28515625" customWidth="1"/>
+    <col min="29" max="29" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>104</v>
       </c>
@@ -8577,13 +8577,13 @@
         <v>2088</v>
       </c>
       <c r="Z1" s="19" t="s">
+        <v>2471</v>
+      </c>
+      <c r="AA1" s="19" t="s">
         <v>2472</v>
       </c>
-      <c r="AA1" s="19" t="s">
+      <c r="AB1" s="19" t="s">
         <v>2473</v>
-      </c>
-      <c r="AB1" s="19" t="s">
-        <v>2474</v>
       </c>
       <c r="AC1" s="19" t="s">
         <v>2089</v>
@@ -8619,7 +8619,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>762</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>765</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>1218</v>
       </c>
@@ -8920,62 +8920,62 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63446AF6-E41F-4CAA-9C6A-F4588DBEF458}">
   <dimension ref="A1:AZ18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="57.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.28515625" customWidth="1"/>
     <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" customWidth="1"/>
-    <col min="14" max="14" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.44140625" customWidth="1"/>
-    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" customWidth="1"/>
-    <col min="18" max="18" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="20.5546875" customWidth="1"/>
-    <col min="39" max="39" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" customWidth="1"/>
+    <col min="14" max="14" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.42578125" customWidth="1"/>
+    <col min="16" max="16" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" customWidth="1"/>
+    <col min="18" max="18" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="20.5703125" customWidth="1"/>
+    <col min="39" max="39" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="12" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="12" customWidth="1"/>
-    <col min="47" max="47" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -9040,10 +9040,10 @@
         <v>1415</v>
       </c>
       <c r="V1" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>2440</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>2441</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>1323</v>
@@ -9133,7 +9133,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1266</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>1988.87</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1265</v>
       </c>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="AP3" s="6"/>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1264</v>
       </c>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" t="s">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AP4" s="6"/>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1267</v>
       </c>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AP5" s="6"/>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1321</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1320</v>
       </c>
@@ -9556,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1324</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>1369</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>1988.87</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>1370</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1343</v>
       </c>
@@ -9895,7 +9895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1344</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1380</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2137</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>1988.87</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2138</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>1988.87</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2303</v>
       </c>
@@ -10370,15 +10370,15 @@
         <v>1988.87</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="B17" t="s">
         <v>246</v>
       </c>
       <c r="H17" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="J17" t="s">
         <v>1277</v>
@@ -10420,20 +10420,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="B18" t="s">
         <v>246</v>
       </c>
       <c r="F18" s="4">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="I18" t="s">
         <v>1331</v>
@@ -10488,18 +10488,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE90B83-E126-4D39-94E6-B33283C8DC5D}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>104</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1362</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>1362</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>1367</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20"/>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -10609,14 +10609,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED69AB3B-3A11-477C-A201-8388519D3807}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="69.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>721</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>722</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>446</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>449</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>448</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>447</v>
       </c>
@@ -10693,7 +10693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>450</v>
       </c>
@@ -10704,7 +10704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>723</v>
       </c>
@@ -10715,7 +10715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>758</v>
       </c>
@@ -10726,7 +10726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1203</v>
       </c>
@@ -10737,7 +10737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1244</v>
       </c>
@@ -10748,7 +10748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1341</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1342</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2206</v>
       </c>
@@ -10781,7 +10781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2207</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>2308</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2351</v>
       </c>
@@ -10814,12 +10814,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>2352</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>2353</v>
       </c>
@@ -10833,44 +10833,44 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2665AEC9-C942-4A65-984C-CAD52F4E2CCE}">
   <dimension ref="A1:BB74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="103.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="103.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="83" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="19.33203125" customWidth="1"/>
-    <col min="9" max="10" width="19.33203125" style="13" customWidth="1"/>
-    <col min="11" max="12" width="19.33203125" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" style="13" customWidth="1"/>
-    <col min="14" max="15" width="19.33203125" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.33203125" customWidth="1"/>
-    <col min="18" max="18" width="20.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="19.33203125" customWidth="1"/>
-    <col min="21" max="21" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="32" width="19.33203125" customWidth="1"/>
-    <col min="33" max="33" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="19.33203125" customWidth="1"/>
-    <col min="37" max="37" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="19.33203125" customWidth="1"/>
-    <col min="40" max="40" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="19.33203125" customWidth="1"/>
-    <col min="43" max="43" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.33203125" customWidth="1"/>
-    <col min="46" max="46" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.33203125" customWidth="1"/>
-    <col min="48" max="48" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="84.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="19.28515625" customWidth="1"/>
+    <col min="9" max="10" width="19.28515625" style="13" customWidth="1"/>
+    <col min="11" max="12" width="19.28515625" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" style="13" customWidth="1"/>
+    <col min="14" max="15" width="19.28515625" customWidth="1"/>
+    <col min="16" max="16" width="19.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" customWidth="1"/>
+    <col min="18" max="18" width="20.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="19.28515625" customWidth="1"/>
+    <col min="21" max="21" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="32" width="19.28515625" customWidth="1"/>
+    <col min="33" max="33" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="19.28515625" customWidth="1"/>
+    <col min="37" max="37" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="19.28515625" customWidth="1"/>
+    <col min="40" max="40" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="19.28515625" customWidth="1"/>
+    <col min="43" max="43" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.28515625" customWidth="1"/>
+    <col min="46" max="46" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.28515625" customWidth="1"/>
+    <col min="48" max="48" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="84.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>CONCATENATE("Lease &amp; Licenses - ",B2)</f>
         <v>Lease &amp; Licenses - Appraisals/Reviews</v>
@@ -11049,7 +11049,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A10" si="0">CONCATENATE("Lease &amp; Licenses - ",B3)</f>
         <v>Lease &amp; Licenses - BC assessment search</v>
@@ -11073,7 +11073,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Canada lands survey</v>
@@ -11091,7 +11091,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Certificate of Insurance (H0111)</v>
@@ -11106,7 +11106,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Company search</v>
@@ -11121,7 +11121,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Conveyance closing documents (ex: PTT forms, Form A transfer etc.)</v>
@@ -11136,7 +11136,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Professional reports (ex: engineering/environmental etc.)</v>
@@ -11151,7 +11151,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Tax notices and assessments</v>
@@ -11166,7 +11166,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>Lease &amp; Licenses - Title search / Historical title</v>
@@ -11187,7 +11187,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="11" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
         <v>1842</v>
       </c>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AX11" s="36"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" ref="A12:A17" si="1">CONCATENATE("Research File - ",B12)</f>
         <v>Research File - Condition of entry (H0443)</v>
@@ -11225,7 +11225,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="1"/>
         <v>Research File - Crown grant</v>
@@ -11240,7 +11240,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="1"/>
         <v>Research File - District road register</v>
@@ -11261,7 +11261,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="1"/>
         <v>Research File - Field notes</v>
@@ -11282,7 +11282,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="1"/>
         <v>Research File - First nations consultation</v>
@@ -11297,7 +11297,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="1"/>
         <v>Research File - Form 12</v>
@@ -11321,7 +11321,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" ref="A18:A20" si="2">CONCATENATE("Research File - ",B18)</f>
         <v>Research File - Gazette</v>
@@ -11360,7 +11360,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="2"/>
         <v>Research File - Historical file</v>
@@ -11387,7 +11387,7 @@
         <v>42988</v>
       </c>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="2"/>
         <v>Research File - Lease / License agreement</v>
@@ -11402,7 +11402,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="21" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:53" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
         <v>1840</v>
       </c>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="AX21" s="36"/>
     </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1206</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>CONCATENATE("Acquisition File - ",B23)</f>
         <v>Acquisition File - Affidavit of service</v>
@@ -11463,7 +11463,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>CONCATENATE("Acquisition File - ",B24)</f>
         <v>Acquisition File - Agricultural Land Commission (ALC)</v>
@@ -11481,7 +11481,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>CONCATENATE("Acquisition File - ",B25)</f>
         <v>Acquisition File - Form 5 - Approval of expropriation</v>
@@ -11496,7 +11496,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="26" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>CONCATENATE("Acquisition File - ",B26)</f>
         <v>Acquisition File - Compensation cheque</v>
@@ -11511,7 +11511,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" ref="A27:A33" si="3">CONCATENATE("Acquisition File - ",B27)</f>
         <v>Acquisition File - Compensation requisition (H-120)</v>
@@ -11526,7 +11526,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Land Act Tenure/Reserves</v>
@@ -11547,7 +11547,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Legal correspondence (ex: to AG/external lawyers)</v>
@@ -11562,7 +11562,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="30" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Legal survey plan</v>
@@ -11583,7 +11583,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - LTSA documents and plans (except title search)</v>
@@ -11598,7 +11598,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Ministerial order</v>
@@ -11625,7 +11625,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="3"/>
         <v>Acquisition File - Form 7 - Notice of abandonement</v>
@@ -11640,7 +11640,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="34" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
         <v>1843</v>
       </c>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="AX34" s="36"/>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>_xlfn.CONCAT("Project -",B35)</f>
         <v>Project -Briefing notes</v>
@@ -11678,7 +11678,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" ref="A36:A43" si="4">_xlfn.CONCAT("Project -",B36)</f>
         <v>Project -Correspondence</v>
@@ -11705,7 +11705,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="4"/>
         <v>Project -Financial records (invoices, journal vouchers, received cheques etc.)</v>
@@ -11720,7 +11720,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="4"/>
         <v>Project -MoTI plan</v>
@@ -11750,7 +11750,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="4"/>
         <v>Project -Other</v>
@@ -11771,7 +11771,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="4"/>
         <v>Project -PA plans / Design drawings</v>
@@ -11801,7 +11801,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="4"/>
         <v>Project -Photos / Images / Video</v>
@@ -11840,7 +11840,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f t="shared" si="4"/>
         <v>Project -Spending authority approval (SAA)</v>
@@ -11855,7 +11855,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f t="shared" si="4"/>
         <v>Project -Surplus property declaration</v>
@@ -11870,7 +11870,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="44" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:50" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="23" t="s">
         <v>1841</v>
       </c>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="AX44" s="36"/>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>_xlfn.CONCAT("Disposition File -",B45)</f>
         <v>Disposition File -Certificate of Compliance</v>
@@ -11908,7 +11908,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f t="shared" ref="A46:A53" si="5">_xlfn.CONCAT("Disposition File -",B46)</f>
         <v>Disposition File -Enhanced Referral Records</v>
@@ -11923,7 +11923,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -First Nations Strength of Claim Report</v>
@@ -11938,7 +11938,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Miscellaneous notes (LTSA)</v>
@@ -11953,7 +11953,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Notice of claims/Litigation documents</v>
@@ -11968,7 +11968,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Order in Council (OIC)</v>
@@ -11995,7 +11995,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Purchase and Sale Agreement</v>
@@ -12010,7 +12010,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Record of negotiation</v>
@@ -12025,7 +12025,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f t="shared" si="5"/>
         <v>Disposition File -Release of claims</v>
@@ -12040,7 +12040,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="54" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
         <v>1844</v>
       </c>
@@ -12071,7 +12071,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>_xlfn.CONCAT("Property Management -",B55)</f>
         <v>Property Management -Approval/sign-off</v>
@@ -12086,7 +12086,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f t="shared" ref="A56:A64" si="6">_xlfn.CONCAT("Property Management -",B56)</f>
         <v>Property Management -Form 8 - Notice of advanced payment </v>
@@ -12101,7 +12101,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Form 1 - Notice of expropriation </v>
@@ -12116,7 +12116,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Notice of possible entry (H0224)</v>
@@ -12131,7 +12131,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Other Land Agreement (Indemnity Letter, Letter of Intended Use, Assumption Agreement, etc)</v>
@@ -12146,7 +12146,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Owner agreement/offer</v>
@@ -12161,7 +12161,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Privy council</v>
@@ -12176,7 +12176,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Temporary license for construction access (H0074)</v>
@@ -12191,7 +12191,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Transfer of administration</v>
@@ -12218,7 +12218,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f t="shared" si="6"/>
         <v>Property Management -Form 9 - Vesting notice (Form 9)</v>
@@ -12233,7 +12233,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="65" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="23" t="s">
         <v>1845</v>
       </c>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="AX65" s="36"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>_xlfn.CONCAT("Management File -",B66)</f>
         <v>Management File -Certificate of Compliance</v>
@@ -12271,7 +12271,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A70" si="7">_xlfn.CONCAT("Management File -",B67)</f>
         <v>Management File -Company search</v>
@@ -12286,7 +12286,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>_xlfn.CONCAT("Management File -",B68)</f>
         <v>Management File -Correspondence</v>
@@ -12313,7 +12313,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f t="shared" si="7"/>
         <v>Management File -District road register</v>
@@ -12334,7 +12334,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f t="shared" si="7"/>
         <v>Management File -Field notes</v>
@@ -12355,7 +12355,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="71" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="23" t="s">
         <v>2208</v>
       </c>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AX71" s="36"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2309</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2310</v>
       </c>
@@ -12427,7 +12427,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2311</v>
       </c>
@@ -12454,17 +12454,17 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9467DD6-431B-4487-B73A-065D683A7274}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1087</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>82939.5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1087</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>828.86</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1087</v>
       </c>
@@ -12544,7 +12544,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1088</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>8989.8700000000008</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1089</v>
       </c>
@@ -12584,7 +12584,7 @@
         <v>1890.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1231</v>
       </c>
@@ -12614,18 +12614,18 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9776329E-4018-44A5-82B8-B8248C5C0C9C}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="78.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -12648,7 +12648,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>396</v>
       </c>
@@ -12668,7 +12668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>397</v>
       </c>
@@ -12688,55 +12688,55 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5546875" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="28.44140625" customWidth="1"/>
-    <col min="15" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.44140625" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="28.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.42578125" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="18" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="23" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="21" bestFit="1" customWidth="1"/>
-    <col min="40" max="42" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="42" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="21" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="66.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="66.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -13025,7 +13025,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>734</v>
       </c>
@@ -13046,7 +13046,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>107</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1097</v>
       </c>
@@ -13208,7 +13208,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -13288,7 +13288,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>734</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -13404,7 +13404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -13439,99 +13439,99 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C49A716-1E6E-4D56-8BE1-20B354C9F88C}">
   <dimension ref="A1:CL34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.33203125" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.44140625" customWidth="1"/>
-    <col min="22" max="22" width="39.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.42578125" customWidth="1"/>
+    <col min="22" max="22" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="47" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="28.5546875" customWidth="1"/>
-    <col min="32" max="32" width="39.44140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="25.44140625" customWidth="1"/>
-    <col min="36" max="36" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.33203125" customWidth="1"/>
-    <col min="44" max="44" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="18.5546875" customWidth="1"/>
-    <col min="62" max="62" width="61.33203125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="48.6640625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="53.33203125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="28.5703125" customWidth="1"/>
+    <col min="32" max="32" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="25.42578125" customWidth="1"/>
+    <col min="36" max="36" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.28515625" customWidth="1"/>
+    <col min="44" max="44" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="18.5703125" customWidth="1"/>
+    <col min="62" max="62" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="38.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:90" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:90" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>1619</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="AW1" s="3" t="s">
         <v>1735</v>
@@ -13803,7 +13803,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="2" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1441</v>
       </c>
@@ -14060,7 +14060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1442</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>634</v>
       </c>
       <c r="T3" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="V3" t="s">
         <v>1725</v>
@@ -14218,7 +14218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1644</v>
       </c>
@@ -14338,7 +14338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1647</v>
       </c>
@@ -14445,7 +14445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2374</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1737</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1741</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1753</v>
       </c>
@@ -14949,7 +14949,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="10" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1770</v>
       </c>
@@ -15065,7 +15065,7 @@
         <v>122000</v>
       </c>
     </row>
-    <row r="11" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2145</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2145</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2145</v>
       </c>
@@ -15434,7 +15434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2145</v>
       </c>
@@ -15556,7 +15556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2145</v>
       </c>
@@ -15678,7 +15678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2145</v>
       </c>
@@ -15806,7 +15806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>2145</v>
       </c>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2145</v>
       </c>
@@ -16060,7 +16060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>2349</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="20" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>2350</v>
       </c>
@@ -16313,7 +16313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2362</v>
       </c>
@@ -16448,7 +16448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>2367</v>
       </c>
@@ -16561,7 +16561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>2363</v>
       </c>
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2364</v>
       </c>
@@ -16831,7 +16831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>2368</v>
       </c>
@@ -16949,7 +16949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>2365</v>
       </c>
@@ -17164,7 +17164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>2369</v>
       </c>
@@ -17290,7 +17290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>2366</v>
       </c>
@@ -17428,7 +17428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>2370</v>
       </c>
@@ -17543,7 +17543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>2371</v>
       </c>
@@ -17678,7 +17678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>2372</v>
       </c>
@@ -17790,7 +17790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>2373</v>
       </c>
@@ -17894,7 +17894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:89" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>566</v>
       </c>
@@ -18013,7 +18013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:89" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>2375</v>
       </c>
@@ -18140,23 +18140,23 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D768FFA-9157-46E5-A299-3BA154C5EE53}">
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.5546875" customWidth="1"/>
-    <col min="2" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5703125" customWidth="1"/>
+    <col min="2" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="32" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -18251,7 +18251,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1591</v>
       </c>
@@ -18346,7 +18346,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1592</v>
       </c>
@@ -18451,16 +18451,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A88259B-EC69-4055-A25D-A02165BA35F2}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -18477,7 +18477,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1068</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v>44623</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1068</v>
       </c>
@@ -18511,7 +18511,7 @@
         <v>44084</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1068</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>36443</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1072</v>
       </c>
@@ -18545,7 +18545,7 @@
         <v>42986</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1221</v>
       </c>
@@ -18568,22 +18568,22 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408261CA-1BB0-4036-BE95-18F8D8636D54}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1784</v>
       </c>
@@ -18647,7 +18647,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1785</v>
       </c>
@@ -18674,7 +18674,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1786</v>
       </c>
@@ -18703,7 +18703,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1787</v>
       </c>
@@ -18732,7 +18732,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1788</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1789</v>
       </c>
@@ -18788,7 +18788,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1790</v>
       </c>
@@ -18820,7 +18820,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1791</v>
       </c>
@@ -18853,7 +18853,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1797</v>
       </c>
@@ -18891,24 +18891,24 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59063E35-2744-4A83-A0B3-24C7FD044C62}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -18949,7 +18949,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>549</v>
       </c>
@@ -18987,7 +18987,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>549</v>
       </c>
@@ -19028,7 +19028,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>582</v>
       </c>
@@ -19066,7 +19066,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>566</v>
       </c>
@@ -19113,22 +19113,22 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4E3335-5C1A-476B-8F34-CC44F557D991}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -19163,7 +19163,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>619</v>
       </c>
@@ -19198,7 +19198,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>619</v>
       </c>
@@ -19233,7 +19233,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>619</v>
       </c>
@@ -19268,7 +19268,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>619</v>
       </c>
@@ -19303,7 +19303,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>619</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>624</v>
       </c>
@@ -19382,34 +19382,34 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DC2A471-385A-4133-9FB5-E00CEEFCFD2D}">
   <dimension ref="A1:V6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" customWidth="1"/>
-    <col min="12" max="12" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="33" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -19477,7 +19477,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>549</v>
       </c>
@@ -19546,7 +19546,7 @@
         <v>210.82</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>549</v>
       </c>
@@ -19603,7 +19603,7 @@
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>549</v>
       </c>
@@ -19652,7 +19652,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>549</v>
       </c>
@@ -19704,7 +19704,7 @@
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>611</v>
       </c>
@@ -19782,21 +19782,21 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95CAF2C3-907F-4E43-96B2-4A95A3C2BD94}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="103.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="103.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1441</v>
       </c>
@@ -19860,7 +19860,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1441</v>
       </c>
@@ -19892,7 +19892,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1441</v>
       </c>
@@ -19915,7 +19915,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1441</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1441</v>
       </c>
@@ -19934,7 +19934,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1442</v>
       </c>
@@ -19969,16 +19969,16 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6145A9-5B51-4FBF-8D69-3E7C17635F2F}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1628</v>
       </c>
@@ -20012,7 +20012,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1628</v>
       </c>
@@ -20029,7 +20029,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1628</v>
       </c>
@@ -20046,7 +20046,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1629</v>
       </c>
@@ -20072,16 +20072,16 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E3AF99-B285-4872-B012-0C94F438EBF8}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1734</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1734</v>
       </c>
@@ -20132,7 +20132,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1734</v>
       </c>
@@ -20149,7 +20149,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1734</v>
       </c>
@@ -20166,7 +20166,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>582</v>
       </c>
@@ -20183,7 +20183,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>583</v>
       </c>
@@ -20200,7 +20200,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1733</v>
       </c>
@@ -20217,7 +20217,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1733</v>
       </c>
@@ -20234,7 +20234,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1733</v>
       </c>
@@ -20251,7 +20251,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1733</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1733</v>
       </c>
@@ -20285,7 +20285,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1742</v>
       </c>
@@ -20311,31 +20311,31 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718AA1BD-8944-4A5E-BDA4-69421020A1DE}">
   <dimension ref="A1:T12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="66.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="29" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="32" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>104</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1021</v>
       </c>
@@ -20456,7 +20456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1022</v>
       </c>
@@ -20515,7 +20515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1028</v>
       </c>
@@ -20547,7 +20547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1029</v>
       </c>
@@ -20579,7 +20579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2295</v>
       </c>
@@ -20611,7 +20611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2200</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2201</v>
       </c>
@@ -20675,7 +20675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2276</v>
       </c>
@@ -20707,7 +20707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2277</v>
       </c>
@@ -20739,7 +20739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2296</v>
       </c>
@@ -20771,7 +20771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2356</v>
       </c>
@@ -20812,20 +20812,20 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD92D06B-F8ED-4433-B13A-26AE77A867A4}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -20854,7 +20854,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1170</v>
       </c>
@@ -20883,7 +20883,7 @@
         <v>1385.43</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1170</v>
       </c>
@@ -20912,7 +20912,7 @@
         <v>10762.5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2282</v>
       </c>
@@ -20941,7 +20941,7 @@
         <v>10641.09</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2282</v>
       </c>
@@ -20970,7 +20970,7 @@
         <v>163.63</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2282</v>
       </c>
@@ -20999,7 +20999,7 @@
         <v>16886861.48</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2282</v>
       </c>
@@ -21028,7 +21028,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2282</v>
       </c>
@@ -21057,7 +21057,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2292</v>
       </c>
@@ -21095,13 +21095,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E0191B-A695-44B6-B8DB-539DF91B46C4}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>335</v>
       </c>
@@ -21109,7 +21109,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>336</v>
       </c>
@@ -21117,7 +21117,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>337</v>
       </c>
@@ -21125,7 +21125,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>338</v>
       </c>
@@ -21133,7 +21133,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>339</v>
       </c>
@@ -21141,7 +21141,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>627</v>
       </c>
@@ -21149,7 +21149,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1123</v>
       </c>
@@ -21157,7 +21157,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1124</v>
       </c>
@@ -21165,7 +21165,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1207</v>
       </c>
@@ -21173,7 +21173,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1347</v>
       </c>
@@ -21181,7 +21181,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1348</v>
       </c>
@@ -21189,7 +21189,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2224</v>
       </c>
@@ -21197,7 +21197,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2225</v>
       </c>
@@ -21205,7 +21205,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2348</v>
       </c>
@@ -21213,7 +21213,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2347</v>
       </c>
@@ -21230,18 +21230,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE31339F-895D-48D8-9AD6-CFA457625F2E}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.6640625" customWidth="1"/>
-    <col min="4" max="4" width="57.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.7109375" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -21264,7 +21264,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1068</v>
       </c>
@@ -21287,7 +21287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1068</v>
       </c>
@@ -21310,7 +21310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1068</v>
       </c>
@@ -21333,7 +21333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1072</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1221</v>
       </c>
@@ -21388,53 +21388,53 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC9B3A8-42C1-4A9C-B1C1-5E5E07CE0539}">
   <dimension ref="A1:AT7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="18.44140625" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="18.6640625" customWidth="1"/>
-    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="18.7109375" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="20.33203125" customWidth="1"/>
-    <col min="31" max="31" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="18.33203125" customWidth="1"/>
-    <col min="40" max="40" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="20.28515625" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="18.28515625" customWidth="1"/>
+    <col min="40" max="40" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="55.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:46" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -21574,7 +21574,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -21705,7 +21705,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1099</v>
       </c>
@@ -21734,7 +21734,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -21805,7 +21805,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1103</v>
       </c>
@@ -21865,7 +21865,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>115</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>154</v>
       </c>
@@ -21947,24 +21947,24 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12A4D20-CBEC-42E3-9A24-C9C857FE01F3}">
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="22.6640625" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="5" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="72.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="22.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="72.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>160</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -22053,7 +22053,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>172</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>171</v>
       </c>
@@ -22179,7 +22179,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>342</v>
       </c>
@@ -22218,7 +22218,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1126</v>
       </c>
@@ -22254,7 +22254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1127</v>
       </c>
@@ -22290,7 +22290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2127</v>
       </c>
@@ -22345,20 +22345,20 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C337DBF-8E87-4911-96F1-55478D7291E8}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -22387,7 +22387,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>327</v>
       </c>
@@ -22416,7 +22416,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>328</v>
       </c>
@@ -22445,7 +22445,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>329</v>
       </c>
@@ -22474,7 +22474,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>343</v>
       </c>
@@ -22500,7 +22500,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>344</v>
       </c>
@@ -22526,7 +22526,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>345</v>
       </c>
@@ -22552,7 +22552,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>346</v>
       </c>
@@ -22578,7 +22578,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>347</v>
       </c>
@@ -22604,7 +22604,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>348</v>
       </c>
@@ -22627,7 +22627,7 @@
         <v>43953</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>349</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>350</v>
       </c>
@@ -22679,7 +22679,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>351</v>
       </c>
@@ -22705,7 +22705,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>352</v>
       </c>
@@ -22731,7 +22731,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>353</v>
       </c>
@@ -22757,7 +22757,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>330</v>
       </c>
@@ -22786,7 +22786,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>331</v>
       </c>
@@ -22809,7 +22809,7 @@
         <v>44969</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>332</v>
       </c>
@@ -22842,56 +22842,56 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AFC28AC-6E43-4E72-BAB6-024FC197C5A5}">
   <dimension ref="A1:AI7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="46" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="46" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -22965,10 +22965,10 @@
         <v>2399</v>
       </c>
       <c r="Y1" s="3" t="s">
+        <v>2452</v>
+      </c>
+      <c r="Z1" s="3" t="s">
         <v>2453</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>2454</v>
       </c>
       <c r="AA1" s="3" t="s">
         <v>1550</v>
@@ -22998,7 +22998,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -23024,7 +23024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>262</v>
       </c>
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>390</v>
       </c>
@@ -23175,7 +23175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>649</v>
       </c>
@@ -23213,13 +23213,13 @@
         <v>694</v>
       </c>
       <c r="X5" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="Y5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Z5" t="s">
         <v>2455</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>2456</v>
       </c>
       <c r="AA5" s="30">
         <v>89.87</v>
@@ -23234,13 +23234,13 @@
         <v>670</v>
       </c>
       <c r="AE5" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="AF5" t="s">
         <v>2402</v>
       </c>
       <c r="AG5" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -23249,7 +23249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1332</v>
       </c>
@@ -23320,7 +23320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2423</v>
       </c>
@@ -23368,15 +23368,15 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D71059-3190-4481-8715-17FF76C75B91}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -23390,7 +23390,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1562</v>
       </c>
@@ -23401,7 +23401,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1562</v>
       </c>
@@ -23412,7 +23412,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1562</v>
       </c>
@@ -23435,41 +23435,41 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7262AB15-46E3-445C-B25C-563340BB9466}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2422</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2476</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>2477</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2421</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2424</v>
       </c>
       <c r="B2" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="C2" t="s">
         <v>2426</v>
@@ -23484,12 +23484,12 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2424</v>
       </c>
       <c r="B3" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="C3" t="s">
         <v>2427</v>
@@ -23498,18 +23498,18 @@
         <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="F3" t="s">
         <v>2429</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2424</v>
       </c>
       <c r="B4" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -23518,18 +23518,18 @@
         <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="F4" t="s">
         <v>2430</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2425</v>
       </c>
       <c r="B5" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="C5" t="s">
         <v>2427</v>
@@ -23538,7 +23538,7 @@
         <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="F5" t="s">
         <v>2431</v>
@@ -23553,20 +23553,20 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5F40B5-89DA-4741-9D93-0338FA3A7E2C}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -23595,7 +23595,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1135</v>
       </c>
@@ -23624,7 +23624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1186</v>
       </c>
@@ -23653,7 +23653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1187</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1248</v>
       </c>
@@ -23702,15 +23702,15 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28F1C7F-C3A7-4EC8-A468-AE1E52A9CDFA}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="24.7109375" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1154</v>
       </c>
@@ -23744,7 +23744,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1154</v>
       </c>
@@ -23761,7 +23761,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1154</v>
       </c>
@@ -23778,7 +23778,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1189</v>
       </c>
@@ -23805,29 +23805,29 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{900FA95B-8B00-4597-9C9C-B9D179841747}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.5546875" customWidth="1"/>
-    <col min="11" max="11" width="43.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.5703125" customWidth="1"/>
+    <col min="11" max="11" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1160</v>
       </c>
@@ -23936,7 +23936,7 @@
         <v>12147.93</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1160</v>
       </c>
@@ -23989,7 +23989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1191</v>
       </c>
@@ -24015,7 +24015,7 @@
         <v>1195</v>
       </c>
       <c r="J4" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="K4" t="s">
         <v>1197</v>
@@ -24042,7 +24042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1249</v>
       </c>
@@ -24089,7 +24089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2261</v>
       </c>
@@ -24121,7 +24121,7 @@
         <v>2302</v>
       </c>
       <c r="L6" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -24142,7 +24142,7 @@
         <v>16897666.199999999</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2261</v>
       </c>
@@ -24198,7 +24198,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2262</v>
       </c>
@@ -24260,18 +24260,18 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56704E8-1DAE-4D99-86A6-0D11D370D1F9}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="63.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="63.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -24294,7 +24294,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>286</v>
       </c>
@@ -24317,7 +24317,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>286</v>
       </c>
@@ -24340,7 +24340,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>286</v>
       </c>
@@ -24363,7 +24363,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>286</v>
       </c>
@@ -24386,7 +24386,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -24409,7 +24409,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>308</v>
       </c>
@@ -24432,7 +24432,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>319</v>
       </c>
@@ -24455,7 +24455,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1199</v>
       </c>
@@ -24478,7 +24478,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>2155</v>
       </c>
@@ -24493,63 +24493,63 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ABE440-1217-4524-8B92-D6A2E8FC0332}">
   <dimension ref="A1:BA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="24.44140625" customWidth="1"/>
-    <col min="18" max="18" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="24.42578125" customWidth="1"/>
+    <col min="18" max="18" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="21" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="46" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="41" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="45.5703125" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="37" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="44.44140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>104</v>
       </c>
@@ -24710,7 +24710,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1021</v>
       </c>
@@ -24856,7 +24856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1022</v>
       </c>
@@ -24895,7 +24895,7 @@
       </c>
       <c r="N3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="O3" s="4">
         <v>45318</v>
@@ -24943,7 +24943,7 @@
         <v>981</v>
       </c>
       <c r="AH3" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="AI3" t="s">
         <v>2404</v>
@@ -24997,7 +24997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1028</v>
       </c>
@@ -25115,7 +25115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1029</v>
       </c>
@@ -25139,7 +25139,7 @@
       </c>
       <c r="N5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="O5" s="4">
         <v>45318</v>
@@ -25225,7 +25225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1027</v>
       </c>
@@ -25340,7 +25340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1022</v>
       </c>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="N7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="O7" s="4">
         <v>45318</v>
@@ -25450,7 +25450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1031</v>
       </c>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1033</v>
       </c>
@@ -25683,7 +25683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1035</v>
       </c>
@@ -25798,7 +25798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1037</v>
       </c>
@@ -25913,7 +25913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1038</v>
       </c>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="O12" s="4">
         <v>45318</v>
@@ -26026,7 +26026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1041</v>
       </c>
@@ -26141,7 +26141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1043</v>
       </c>
@@ -26256,7 +26256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1044</v>
       </c>
@@ -26280,7 +26280,7 @@
       </c>
       <c r="N15" s="4">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="O15" s="4">
         <v>45318</v>
@@ -26366,7 +26366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>769</v>
       </c>
@@ -26453,7 +26453,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>800</v>
       </c>
@@ -26531,7 +26531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>673</v>
       </c>
@@ -26615,7 +26615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:53" s="46" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:53" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="46" t="s">
         <v>674</v>
       </c>
@@ -26707,7 +26707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1473</v>
       </c>
@@ -26785,7 +26785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1503</v>
       </c>
@@ -26870,7 +26870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1504</v>
       </c>
@@ -26955,7 +26955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1954</v>
       </c>
@@ -27056,7 +27056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1953</v>
       </c>
@@ -27200,7 +27200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1964</v>
       </c>
@@ -27331,15 +27331,15 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAD653A-DB80-460C-86DB-ACD85A6EF957}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>104</v>
       </c>
@@ -27353,7 +27353,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1387</v>
       </c>
@@ -27367,7 +27367,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1387</v>
       </c>
@@ -27378,7 +27378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1387</v>
       </c>
@@ -27392,7 +27392,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1387</v>
       </c>
@@ -27403,7 +27403,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1387</v>
       </c>
@@ -27414,7 +27414,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1388</v>
       </c>
@@ -27437,29 +27437,29 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3C62D2-095D-41C7-8E12-52D5164F6230}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="60.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="63.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -27518,7 +27518,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>984</v>
       </c>
@@ -27574,7 +27574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>985</v>
       </c>
@@ -27602,7 +27602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1016</v>
       </c>
@@ -27627,7 +27627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>987</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>986</v>
       </c>
@@ -27695,7 +27695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>242</v>
       </c>
@@ -27751,7 +27751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>277</v>
       </c>
@@ -27774,7 +27774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>334</v>
       </c>
@@ -27800,7 +27800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1198</v>
       </c>
@@ -27823,7 +27823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1198</v>
       </c>
@@ -27862,36 +27862,36 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E382B1-281B-4434-81AA-04C8D5F3D2FB}">
   <dimension ref="A1:V42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="30.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="30.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.44140625" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.42578125" customWidth="1"/>
+    <col min="23" max="23" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -27959,7 +27959,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>273</v>
       </c>
@@ -27967,7 +27967,7 @@
         <v>4361431</v>
       </c>
       <c r="D2" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="I2">
         <v>48</v>
@@ -27994,10 +27994,10 @@
         <v>2259</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>325</v>
       </c>
@@ -28005,7 +28005,7 @@
         <v>2341</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -28013,7 +28013,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>276</v>
       </c>
@@ -28021,7 +28021,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>279</v>
       </c>
@@ -28029,7 +28029,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1598</v>
       </c>
@@ -28040,7 +28040,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>271</v>
       </c>
@@ -28048,7 +28048,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>272</v>
       </c>
@@ -28056,7 +28056,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1458</v>
       </c>
@@ -28097,7 +28097,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>394</v>
       </c>
@@ -28105,7 +28105,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1289</v>
       </c>
@@ -28143,7 +28143,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1287</v>
       </c>
@@ -28151,7 +28151,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1290</v>
       </c>
@@ -28159,7 +28159,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1288</v>
       </c>
@@ -28167,7 +28167,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>664</v>
       </c>
@@ -28193,7 +28193,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1291</v>
       </c>
@@ -28204,7 +28204,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1292</v>
       </c>
@@ -28215,7 +28215,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>671</v>
       </c>
@@ -28223,7 +28223,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1293</v>
       </c>
@@ -28231,7 +28231,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1294</v>
       </c>
@@ -28242,7 +28242,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1295</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1296</v>
       </c>
@@ -28261,7 +28261,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1297</v>
       </c>
@@ -28269,7 +28269,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1298</v>
       </c>
@@ -28280,7 +28280,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1306</v>
       </c>
@@ -28294,10 +28294,10 @@
         <v>2335</v>
       </c>
       <c r="V26" t="s">
-        <v>2459</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1307</v>
       </c>
@@ -28326,7 +28326,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1308</v>
       </c>
@@ -28334,7 +28334,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1309</v>
       </c>
@@ -28342,7 +28342,7 @@
         <v>2336</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1457</v>
       </c>
@@ -28359,7 +28359,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A31" s="52" t="s">
         <v>1472</v>
       </c>
@@ -28368,18 +28368,18 @@
       </c>
       <c r="H31" s="14"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
         <v>2137</v>
       </c>
       <c r="B32" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="V32" t="s">
-        <v>2487</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="52" t="s">
         <v>2140</v>
       </c>
@@ -28393,7 +28393,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
         <v>2150</v>
       </c>
@@ -28404,7 +28404,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="52" t="s">
         <v>2177</v>
       </c>
@@ -28448,7 +28448,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
         <v>2178</v>
       </c>
@@ -28459,18 +28459,18 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="52" t="s">
         <v>2305</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="V37" s="14" t="s">
-        <v>2486</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="52" t="s">
         <v>2307</v>
       </c>
@@ -28481,7 +28481,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="52" t="s">
         <v>2354</v>
       </c>
@@ -28492,7 +28492,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="52" t="s">
         <v>2432</v>
       </c>
@@ -28500,20 +28500,20 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="52" t="s">
         <v>2434</v>
       </c>
       <c r="E41" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="52" t="s">
         <v>2435</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A42" s="52" t="s">
+      <c r="B42" t="s">
         <v>2436</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2437</v>
       </c>
     </row>
   </sheetData>
@@ -28526,17 +28526,17 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76AD87F-398D-4043-9616-B8AC430B9A08}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="64.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -28556,7 +28556,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1449</v>
       </c>
@@ -28576,7 +28576,7 @@
         <v>5941.7103999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>1450</v>
       </c>
@@ -28596,7 +28596,7 @@
         <v>8200.5959999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>1450</v>
       </c>
@@ -28616,7 +28616,7 @@
         <v>323479.56</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1451</v>
       </c>
@@ -28636,7 +28636,7 @@
         <v>633156.69999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1461</v>
       </c>
@@ -28656,7 +28656,7 @@
         <v>633156.69999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1461</v>
       </c>
@@ -28676,7 +28676,7 @@
         <v>633301.1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>1464</v>
       </c>
@@ -28690,7 +28690,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>1465</v>
       </c>
@@ -28704,7 +28704,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>1465</v>
       </c>
@@ -28718,7 +28718,7 @@
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1462</v>
       </c>
@@ -28738,7 +28738,7 @@
         <v>863.15020000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1462</v>
       </c>
@@ -28758,7 +28758,7 @@
         <v>320510.62</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1463</v>
       </c>
@@ -28778,7 +28778,7 @@
         <v>329688.28000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>1466</v>
       </c>
@@ -28798,7 +28798,7 @@
         <v>274328.40000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>1466</v>
       </c>
@@ -28818,7 +28818,7 @@
         <v>642614.75</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>1467</v>
       </c>
@@ -28838,7 +28838,7 @@
         <v>274328.40000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1468</v>
       </c>
@@ -28849,7 +28849,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1468</v>
       </c>
@@ -28860,7 +28860,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1469</v>
       </c>
@@ -28872,7 +28872,7 @@
       </c>
       <c r="J19" s="11"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>1493</v>
       </c>
@@ -28886,7 +28886,7 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>1493</v>
       </c>
@@ -28900,7 +28900,7 @@
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>1469</v>
       </c>
@@ -28914,7 +28914,7 @@
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1494</v>
       </c>
@@ -28925,7 +28925,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1495</v>
       </c>
@@ -28933,7 +28933,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1496</v>
       </c>
@@ -28944,7 +28944,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>1497</v>
       </c>
@@ -28958,7 +28958,7 @@
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>1498</v>
       </c>
@@ -28972,7 +28972,7 @@
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>1498</v>
       </c>
@@ -28986,7 +28986,7 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1499</v>
       </c>
@@ -28997,7 +28997,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1500</v>
       </c>
@@ -29008,7 +29008,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1500</v>
       </c>
@@ -29016,7 +29016,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>2144</v>
       </c>
@@ -29030,7 +29030,7 @@
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>2144</v>
       </c>
@@ -29044,7 +29044,7 @@
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
         <v>2144</v>
       </c>
@@ -29065,34 +29065,34 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA05679-694C-4F3E-B058-118DE368DBE0}">
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5546875" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="18" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -29172,7 +29172,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1001</v>
       </c>
@@ -29228,7 +29228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1001</v>
       </c>
@@ -29302,7 +29302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1001</v>
       </c>
@@ -29360,7 +29360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1001</v>
       </c>
@@ -29412,7 +29412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1001</v>
       </c>
@@ -29475,7 +29475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1006</v>
       </c>
@@ -29536,7 +29536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1216</v>
       </c>
@@ -29589,7 +29589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>1475</v>
       </c>
@@ -29638,7 +29638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1475</v>
       </c>
@@ -29687,7 +29687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1475</v>
       </c>
@@ -29736,7 +29736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1475</v>
       </c>
@@ -29785,7 +29785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1475</v>
       </c>
@@ -29837,7 +29837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1475</v>
       </c>
@@ -29889,7 +29889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1475</v>
       </c>
@@ -29944,7 +29944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1475</v>
       </c>
@@ -29999,7 +29999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1475</v>
       </c>
@@ -30054,7 +30054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1475</v>
       </c>
@@ -30109,7 +30109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1475</v>
       </c>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1475</v>
       </c>
@@ -30217,7 +30217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1475</v>
       </c>
@@ -30270,7 +30270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1475</v>
       </c>
@@ -30324,7 +30324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1475</v>
       </c>
@@ -30378,7 +30378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1475</v>
       </c>
@@ -30427,7 +30427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1475</v>
       </c>
@@ -30476,7 +30476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1475</v>
       </c>
@@ -30531,7 +30531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1475</v>
       </c>
@@ -30580,7 +30580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1475</v>
       </c>
@@ -30645,16 +30645,16 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5EAAF30-BD78-4D23-AEBC-1D6C37D138A6}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -30671,7 +30671,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>650</v>
       </c>
@@ -30685,7 +30685,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>650</v>
       </c>
@@ -30699,7 +30699,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>650</v>
       </c>
@@ -30713,7 +30713,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>650</v>
       </c>
@@ -30730,7 +30730,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>650</v>
       </c>
@@ -30747,7 +30747,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>672</v>
       </c>
@@ -30761,7 +30761,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>863</v>
       </c>
@@ -30775,7 +30775,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1060</v>
       </c>
@@ -30792,7 +30792,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1060</v>
       </c>
@@ -30806,7 +30806,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1209</v>
       </c>
@@ -30820,7 +30820,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1312</v>
       </c>
@@ -30834,7 +30834,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1312</v>
       </c>
@@ -30848,7 +30848,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1312</v>
       </c>
@@ -30862,7 +30862,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1312</v>
       </c>
@@ -30879,7 +30879,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1312</v>
       </c>
@@ -30896,7 +30896,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1312</v>
       </c>
@@ -30913,7 +30913,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1312</v>
       </c>
@@ -30930,7 +30930,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1318</v>
       </c>
@@ -30944,7 +30944,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>2176</v>
       </c>
@@ -30961,7 +30961,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2176</v>
       </c>
@@ -30975,7 +30975,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>2192</v>
       </c>
@@ -30989,7 +30989,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>2229</v>
       </c>
@@ -31006,7 +31006,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2229</v>
       </c>
@@ -31020,7 +31020,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>2230</v>
       </c>
@@ -31046,29 +31046,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5453F532-21B6-4188-9011-0BA56E95151F}">
   <dimension ref="A1:S8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -31127,7 +31127,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>650</v>
       </c>
@@ -31165,7 +31165,7 @@
         <v>4568853286</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>650</v>
       </c>
@@ -31215,7 +31215,7 @@
         <v>2348876890</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>672</v>
       </c>
@@ -31253,7 +31253,7 @@
         <v>6780909654</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>865</v>
       </c>
@@ -31294,7 +31294,7 @@
         <v>7896778787</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>865</v>
       </c>
@@ -31335,7 +31335,7 @@
         <v>7780991098</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1060</v>
       </c>
@@ -31376,7 +31376,7 @@
         <v>7089090655</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1209</v>
       </c>
@@ -31435,19 +31435,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2073F58F-6509-4BF3-843F-237D06AC55C6}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -31473,7 +31473,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>805</v>
       </c>
@@ -31496,7 +31496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>805</v>
       </c>
@@ -31519,7 +31519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>805</v>
       </c>
@@ -31542,7 +31542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>805</v>
       </c>
@@ -31565,7 +31565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>805</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>805</v>
       </c>
@@ -31605,7 +31605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>805</v>
       </c>
@@ -31622,7 +31622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>805</v>
       </c>
@@ -31639,7 +31639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>805</v>
       </c>
@@ -31656,7 +31656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>805</v>
       </c>
@@ -31673,7 +31673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>879</v>
       </c>
@@ -31690,7 +31690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>879</v>
       </c>
@@ -31713,7 +31713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1068</v>
       </c>
@@ -31730,7 +31730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1068</v>
       </c>
@@ -31753,7 +31753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1221</v>
       </c>
@@ -31788,27 +31788,27 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247DFAE7-4496-4934-B20F-D611E033A94F}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.33203125" customWidth="1"/>
-    <col min="9" max="9" width="50.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.28515625" customWidth="1"/>
+    <col min="9" max="9" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -31858,7 +31858,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>783</v>
       </c>
@@ -31875,10 +31875,10 @@
         <v>487</v>
       </c>
       <c r="H2" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="I2" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J2" s="4">
         <v>44440</v>
@@ -31902,7 +31902,7 @@
         <v>1000000.99</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>784</v>
       </c>
@@ -31922,10 +31922,10 @@
         <v>487</v>
       </c>
       <c r="H3" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="I3" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="J3" s="4">
         <v>44806</v>
@@ -31949,7 +31949,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>785</v>
       </c>
@@ -31966,10 +31966,10 @@
         <v>492</v>
       </c>
       <c r="G4" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="H4" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="I4" t="s">
         <v>796</v>
@@ -31996,7 +31996,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>786</v>
       </c>
@@ -32013,7 +32013,7 @@
         <v>487</v>
       </c>
       <c r="H5" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="I5" t="s">
         <v>797</v>
@@ -32040,7 +32040,7 @@
         <v>1200.5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>788</v>
       </c>
@@ -32057,7 +32057,7 @@
         <v>487</v>
       </c>
       <c r="H6" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="I6" t="s">
         <v>794</v>
@@ -32084,7 +32084,7 @@
         <v>190000.95</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>787</v>
       </c>
@@ -32101,7 +32101,7 @@
         <v>487</v>
       </c>
       <c r="H7" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="I7" t="s">
         <v>794</v>
@@ -32128,7 +32128,7 @@
         <v>12000.89</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1219</v>
       </c>
@@ -32145,10 +32145,10 @@
         <v>487</v>
       </c>
       <c r="H8" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="I8" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="J8" s="4">
         <v>45265</v>
@@ -32172,27 +32172,27 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="B9" t="s">
         <v>487</v>
       </c>
       <c r="D9" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="E9" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="F9" t="s">
         <v>487</v>
       </c>
       <c r="H9" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="I9" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="J9" s="4">
         <v>45658</v>
@@ -32216,27 +32216,27 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="B10" t="s">
         <v>487</v>
       </c>
       <c r="D10" t="s">
+        <v>2444</v>
+      </c>
+      <c r="E10" t="s">
         <v>2445</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2446</v>
       </c>
       <c r="F10" t="s">
         <v>487</v>
       </c>
       <c r="H10" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="I10" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="J10" s="4">
         <v>45690</v>
@@ -32269,33 +32269,33 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CC3795-F36B-4D0F-8244-A4F4C3935686}">
   <dimension ref="A1:V10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.6640625" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="61.6640625" customWidth="1"/>
-    <col min="12" max="12" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="61.7109375" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="39.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="122.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="83.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="122.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="83.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -32363,7 +32363,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>829</v>
       </c>
@@ -32431,7 +32431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>885</v>
       </c>
@@ -32466,7 +32466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1221</v>
       </c>
@@ -32534,7 +32534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>1757</v>
       </c>
@@ -32593,7 +32593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>1769</v>
       </c>
@@ -32628,7 +32628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1988</v>
       </c>
@@ -32696,7 +32696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1971</v>
       </c>
@@ -32753,7 +32753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1972</v>
       </c>
@@ -32807,7 +32807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2344</v>
       </c>
@@ -32867,17 +32867,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A39253E-76F9-426F-AB51-5E3DB6377515}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -32897,7 +32897,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>850</v>
       </c>
@@ -32917,7 +32917,7 @@
         <v>135.33000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>851</v>
       </c>
@@ -32934,7 +32934,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>852</v>
       </c>
@@ -32954,7 +32954,7 @@
         <v>59629.48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>975</v>
       </c>
@@ -32971,7 +32971,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1226</v>
       </c>
@@ -32991,7 +32991,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1758</v>
       </c>
@@ -33012,7 +33012,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1759</v>
       </c>
@@ -33030,7 +33030,7 @@
         <v>1200.8900000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1760</v>
       </c>
@@ -33051,7 +33051,7 @@
         <v>53025</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1761</v>
       </c>
@@ -33069,7 +33069,7 @@
         <v>1505.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1990</v>
       </c>
@@ -33089,7 +33089,7 @@
         <v>59629.48</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1989</v>
       </c>
@@ -33109,7 +33109,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1977</v>
       </c>
